--- a/Official Whitelist.xlsx
+++ b/Official Whitelist.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bigba\aa Personal Projects\Letterboxd-List-Scraping\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD7BBEAF-67EA-4561-823D-30AABA2C3C1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E020EF68-3684-42A3-BD5D-4C59ABB3A091}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="680" yWindow="760" windowWidth="14400" windowHeight="8170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="711" uniqueCount="711">
   <si>
     <t>Title</t>
   </si>
@@ -64,6 +64,2100 @@
   </si>
   <si>
     <t>https://letterboxd.com/film/the-godfather-part-ii/</t>
+  </si>
+  <si>
+    <t>The Human Condition I No Greater Love</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-human-condition-i-no-greater-love/</t>
+  </si>
+  <si>
+    <t>The Lord Of The Rings The Return Of The King</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-lord-of-the-rings-the-return-of-the-king/</t>
+  </si>
+  <si>
+    <t>Schindlers List</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/schindlers-list/</t>
+  </si>
+  <si>
+    <t>Yi Yi</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/yi-yi/</t>
+  </si>
+  <si>
+    <t>The Godfather</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-godfather/</t>
+  </si>
+  <si>
+    <t>Ran</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/ran/</t>
+  </si>
+  <si>
+    <t>The Good The Bad And The Ugly</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-good-the-bad-and-the-ugly/</t>
+  </si>
+  <si>
+    <t>Cinema Paradiso</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/cinema-paradiso/</t>
+  </si>
+  <si>
+    <t>A Brighter Summer Day</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/a-brighter-summer-day/</t>
+  </si>
+  <si>
+    <t>The Dark Knight</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-dark-knight/</t>
+  </si>
+  <si>
+    <t>The Human Condition Ii Road To Eternity</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-human-condition-ii-road-to-eternity/</t>
+  </si>
+  <si>
+    <t>There Will Be Blood</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/there-will-be-blood/</t>
+  </si>
+  <si>
+    <t>Andrei Rublev</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/andrei-rublev/</t>
+  </si>
+  <si>
+    <t>Interstellar</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/interstellar/</t>
+  </si>
+  <si>
+    <t>The Lord Of The Rings The Two Towers</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-lord-of-the-rings-the-two-towers/</t>
+  </si>
+  <si>
+    <t>Fanny And Alexander</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/fanny-and-alexander/</t>
+  </si>
+  <si>
+    <t>Red Beard</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/red-beard/</t>
+  </si>
+  <si>
+    <t>Barry Lyndon</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/barry-lyndon/</t>
+  </si>
+  <si>
+    <t>The Pianist</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-pianist/</t>
+  </si>
+  <si>
+    <t>Stalker</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/stalker/</t>
+  </si>
+  <si>
+    <t>A Woman Under The Influence</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/a-woman-under-the-influence/</t>
+  </si>
+  <si>
+    <t>Lawrence Of Arabia</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/lawrence-of-arabia/</t>
+  </si>
+  <si>
+    <t>Farewell My Concubine</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/farewell-my-concubine/</t>
+  </si>
+  <si>
+    <t>Love Exposure</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/love-exposure/</t>
+  </si>
+  <si>
+    <t>Once Upon A Time In The West</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/once-upon-a-time-in-the-west/</t>
+  </si>
+  <si>
+    <t>Satantango</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/satantango/</t>
+  </si>
+  <si>
+    <t>The Lord Of The Rings The Fellowship Of The Ring</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-lord-of-the-rings-the-fellowship-of-the-ring/</t>
+  </si>
+  <si>
+    <t>An Elephant Sitting Still</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/an-elephant-sitting-still/</t>
+  </si>
+  <si>
+    <t>Dune Part Two</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/dune-part-two/</t>
+  </si>
+  <si>
+    <t>Inglourious Basterds</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/inglourious-basterds/</t>
+  </si>
+  <si>
+    <t>The Wages of Fear</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-wages-of-fear/</t>
+  </si>
+  <si>
+    <t>Judgment At Nuremberg</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/judgment-at-nuremberg/</t>
+  </si>
+  <si>
+    <t>Amadeus</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/amadeus/</t>
+  </si>
+  <si>
+    <t>The Departed</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-departed/</t>
+  </si>
+  <si>
+    <t>Das Boot</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/das-boot/</t>
+  </si>
+  <si>
+    <t>Django Unchained</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/django-unchained/</t>
+  </si>
+  <si>
+    <t>Prisoners</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/prisoners/</t>
+  </si>
+  <si>
+    <t>Rocco And His Brothers</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/rocco-and-his-brothers/</t>
+  </si>
+  <si>
+    <t>The Best Of Youth</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-best-of-youth/</t>
+  </si>
+  <si>
+    <t>The Weeping Meadow</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-weeping-meadow/</t>
+  </si>
+  <si>
+    <t>Underground 1995</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/underground-1995/</t>
+  </si>
+  <si>
+    <t>Heat</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/heat-1995/</t>
+  </si>
+  <si>
+    <t>Edvard Munch</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/edvard-munch/</t>
+  </si>
+  <si>
+    <t>Children Of Paradise</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/children-of-paradise/</t>
+  </si>
+  <si>
+    <t>Evangelion 3010 Thrice Upon A Time</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/evangelion-3010-thrice-upon-a-time/</t>
+  </si>
+  <si>
+    <t>Malcolm X 1992</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/malcolm-x-1992/</t>
+  </si>
+  <si>
+    <t>Eureka</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/eureka-2000/</t>
+  </si>
+  <si>
+    <t>The Green Mile</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-green-mile/</t>
+  </si>
+  <si>
+    <t>La Dolce Vita</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/la-dolce-vita/</t>
+  </si>
+  <si>
+    <t>Jeanne Dielman 23 Quai Du Commerce 1080 Bruxelles</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/jeanne-dielman-23-quai-du-commerce-1080-bruxelles/</t>
+  </si>
+  <si>
+    <t>Saving Private Ryan</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/saving-private-ryan/</t>
+  </si>
+  <si>
+    <t>The Best Years Of Our Lives</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-best-years-of-our-lives/</t>
+  </si>
+  <si>
+    <t>Anatomy Of A Murder</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/anatomy-of-a-murder/</t>
+  </si>
+  <si>
+    <t>Happy Hour</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/happy-hour-2015-1/</t>
+  </si>
+  <si>
+    <t>The Bridge On The River Kwai</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-bridge-on-the-river-kwai/</t>
+  </si>
+  <si>
+    <t>The Disappearance Of Haruhi Suzumiya</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-disappearance-of-haruhi-suzumiya/</t>
+  </si>
+  <si>
+    <t>Kwaidan</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/kwaidan/</t>
+  </si>
+  <si>
+    <t>Nayakan</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/nayakan/</t>
+  </si>
+  <si>
+    <t>Pulp Fiction</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/pulp-fiction/</t>
+  </si>
+  <si>
+    <t>Vada Chennai</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/vada-chennai/</t>
+  </si>
+  <si>
+    <t>Napoleon</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/napoleon/</t>
+  </si>
+  <si>
+    <t>The Sound Of Music</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-sound-of-music/</t>
+  </si>
+  <si>
+    <t>The Life And Death Of Colonel Blimp</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-life-and-death-of-colonel-blimp/</t>
+  </si>
+  <si>
+    <t>The Turin Horse</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-turin-horse/</t>
+  </si>
+  <si>
+    <t>Kagemusha</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/kagemusha/</t>
+  </si>
+  <si>
+    <t>Solaris</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/solaris/</t>
+  </si>
+  <si>
+    <t>Magnolia</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/magnolia/</t>
+  </si>
+  <si>
+    <t>Once Upon a Time in America</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/once-upon-a-time-in-america/</t>
+  </si>
+  <si>
+    <t>La Belle Noiseuse</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/la-belle-noiseuse/</t>
+  </si>
+  <si>
+    <t>The Deer Hunter</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-deer-hunter/</t>
+  </si>
+  <si>
+    <t>The Emigrants</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-emigrants/</t>
+  </si>
+  <si>
+    <t>Winter Sleep</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/winter-sleep/</t>
+  </si>
+  <si>
+    <t>Virumaandi</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/virumaandi/</t>
+  </si>
+  <si>
+    <t>Casino</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/casino/</t>
+  </si>
+  <si>
+    <t>Meiyazhagan</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/meiyazhagan/</t>
+  </si>
+  <si>
+    <t>Boogie Nights</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/boogie-nights/</t>
+  </si>
+  <si>
+    <t>Drive My Car</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/drive-my-car/</t>
+  </si>
+  <si>
+    <t>Rrr</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/rrr/</t>
+  </si>
+  <si>
+    <t>Anbe Sivam</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/anbe-sivam/</t>
+  </si>
+  <si>
+    <t>Marketa LazarovÃ¡</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/marketa-lazarova/</t>
+  </si>
+  <si>
+    <t>Ulysses Gaze</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/ulysses-gaze/</t>
+  </si>
+  <si>
+    <t>Gangs Of Wasseypur Part 2</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/gangs-of-wasseypur-part-2/</t>
+  </si>
+  <si>
+    <t>Dogville</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/dogville/</t>
+  </si>
+  <si>
+    <t>A Prophet</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/a-prophet/</t>
+  </si>
+  <si>
+    <t>One Battle After Another</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/one-battle-after-another/</t>
+  </si>
+  <si>
+    <t>Celine And Julie Go Boating</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/celine-and-julie-go-boating/</t>
+  </si>
+  <si>
+    <t>Pariyerum Perumal</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/pariyerum-perumal/</t>
+  </si>
+  <si>
+    <t>Amores Perros</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/amores-perros/</t>
+  </si>
+  <si>
+    <t>The Mother and the Whore</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-mother-and-the-whore/</t>
+  </si>
+  <si>
+    <t>Once Upon A Time In Anatolia</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/once-upon-a-time-in-anatolia/</t>
+  </si>
+  <si>
+    <t>Gladiator 2000</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/gladiator-2000/</t>
+  </si>
+  <si>
+    <t>Nashville</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/nashville/</t>
+  </si>
+  <si>
+    <t>Thalapathi</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/thalapathi/</t>
+  </si>
+  <si>
+    <t>Oppenheimer 2023</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/oppenheimer-2023/</t>
+  </si>
+  <si>
+    <t>The Great Escape</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-great-escape/</t>
+  </si>
+  <si>
+    <t>So Long, My Son</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/so-long-my-son/</t>
+  </si>
+  <si>
+    <t>The Travelling Players</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-travelling-players/</t>
+  </si>
+  <si>
+    <t>A City Of Sadness</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/a-city-of-sadness/</t>
+  </si>
+  <si>
+    <t>The Leopard</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-leopard/</t>
+  </si>
+  <si>
+    <t>Breaking the Waves</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/breaking-the-waves/</t>
+  </si>
+  <si>
+    <t>Marty Supreme</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/marty-supreme/</t>
+  </si>
+  <si>
+    <t>Scarface</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/scarface-1983/</t>
+  </si>
+  <si>
+    <t>3 Idiots</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/3-idiots/</t>
+  </si>
+  <si>
+    <t>Fitzcarraldo</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/fitzcarraldo/</t>
+  </si>
+  <si>
+    <t>Short Cuts</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/short-cuts/</t>
+  </si>
+  <si>
+    <t>Repentance</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/repentance/</t>
+  </si>
+  <si>
+    <t>Fiddler On The Roof</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/fiddler-on-the-roof/</t>
+  </si>
+  <si>
+    <t>Anatomy Of A Fall</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/anatomy-of-a-fall/</t>
+  </si>
+  <si>
+    <t>Downfall</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/downfall/</t>
+  </si>
+  <si>
+    <t>A Touch Of Zen</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/a-touch-of-zen/</t>
+  </si>
+  <si>
+    <t>The Bad Sleep Well</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-bad-sleep-well/</t>
+  </si>
+  <si>
+    <t>Hey Ram</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/hey-ram/</t>
+  </si>
+  <si>
+    <t>Blade Runner 2049</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/blade-runner-2049/</t>
+  </si>
+  <si>
+    <t>The Count Of Monte Cristo 2024</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-count-of-monte-cristo-2024/</t>
+  </si>
+  <si>
+    <t>The Tree of Wooden Clogs</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-tree-of-wooden-clogs/</t>
+  </si>
+  <si>
+    <t>Pudhupettai</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/pudhupettai/</t>
+  </si>
+  <si>
+    <t>The Insider</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-insider/</t>
+  </si>
+  <si>
+    <t>The Thin Red Line</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-thin-red-line/</t>
+  </si>
+  <si>
+    <t>Ben Hur</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/ben-hur-1959/</t>
+  </si>
+  <si>
+    <t>A Bride For Rip Van Winkle</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/a-bride-for-rip-van-winkle/</t>
+  </si>
+  <si>
+    <t>Drishyam</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/drishyam/</t>
+  </si>
+  <si>
+    <t>The Death Of Mr Lazarescu</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-death-of-mr-lazarescu/</t>
+  </si>
+  <si>
+    <t>Platform</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/platform/</t>
+  </si>
+  <si>
+    <t>The Saragossa Manuscript</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-saragossa-manuscript/</t>
+  </si>
+  <si>
+    <t>The Wild Pear Tree</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-wild-pear-tree/</t>
+  </si>
+  <si>
+    <t>Jfk</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/jfk/</t>
+  </si>
+  <si>
+    <t>A Hidden Life 2019</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/a-hidden-life-2019/</t>
+  </si>
+  <si>
+    <t>Bahubali The Epic</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/bahubali-the-epic/</t>
+  </si>
+  <si>
+    <t>Haider</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/haider/</t>
+  </si>
+  <si>
+    <t>Jigarthanda</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/jigarthanda/</t>
+  </si>
+  <si>
+    <t>Norte, The End of History</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/norte-the-end-of-history/</t>
+  </si>
+  <si>
+    <t>Super Deluxe</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/super-deluxe/</t>
+  </si>
+  <si>
+    <t>Satya</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/satya/</t>
+  </si>
+  <si>
+    <t>Premam</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/premam/</t>
+  </si>
+  <si>
+    <t>Laurence Anyways</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/laurence-anyways/</t>
+  </si>
+  <si>
+    <t>Gangs Of Wasseypur Part 1</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/gangs-of-wasseypur-part-1/</t>
+  </si>
+  <si>
+    <t>The Raid 2</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-raid-2/</t>
+  </si>
+  <si>
+    <t>Vaaranam Aayiram</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/vaaranam-aayiram/</t>
+  </si>
+  <si>
+    <t>Manichitrathazhu</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/manichitrathazhu/</t>
+  </si>
+  <si>
+    <t>On the Silver Globe</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/on-the-silver-globe/</t>
+  </si>
+  <si>
+    <t>Demon Slayer Kimetsu No Yaiba Infinity Castle</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/demon-slayer-kimetsu-no-yaiba-infinity-castle/</t>
+  </si>
+  <si>
+    <t>Papillon</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/papillon/</t>
+  </si>
+  <si>
+    <t>La Terra Trema</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/la-terra-trema/</t>
+  </si>
+  <si>
+    <t>The Big Country</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-big-country/</t>
+  </si>
+  <si>
+    <t>Like Stars On Earth</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/like-stars-on-earth/</t>
+  </si>
+  <si>
+    <t>The Assassination Of Jesse James By The Coward Robert Ford</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-assassination-of-jesse-james-by-the-coward-robert-ford/</t>
+  </si>
+  <si>
+    <t>That Day, on the Beach</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/that-day-on-the-beach/</t>
+  </si>
+  <si>
+    <t>Ford V Ferrari</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/ford-v-ferrari/</t>
+  </si>
+  <si>
+    <t>The Legend Of 1900</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-legend-of-1900/</t>
+  </si>
+  <si>
+    <t>The Right Stuff</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-right-stuff/</t>
+  </si>
+  <si>
+    <t>About Dry Grasses</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/about-dry-grasses/</t>
+  </si>
+  <si>
+    <t>Killers Of The Flower Moon</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/killers-of-the-flower-moon/</t>
+  </si>
+  <si>
+    <t>Jersey</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/jersey/</t>
+  </si>
+  <si>
+    <t>Zodiac</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/zodiac/</t>
+  </si>
+  <si>
+    <t>The Batman</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-batman/</t>
+  </si>
+  <si>
+    <t>The Hateful Eight</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-hateful-eight/</t>
+  </si>
+  <si>
+    <t>Bound By Honor</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/bound-by-honor/</t>
+  </si>
+  <si>
+    <t>Sarpatta Parambarai</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/sarpatta-parambarai/</t>
+  </si>
+  <si>
+    <t>Om Shanti Om</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/om-shanti-om/</t>
+  </si>
+  <si>
+    <t>Kings Of The Road</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/kings-of-the-road/</t>
+  </si>
+  <si>
+    <t>Dilwale Dulhania Le Jayenge</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/dilwale-dulhania-le-jayenge/</t>
+  </si>
+  <si>
+    <t>Sardar Udham</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/sardar-udham/</t>
+  </si>
+  <si>
+    <t>Silence</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/silence/</t>
+  </si>
+  <si>
+    <t>The Fabelmans</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-fabelmans/</t>
+  </si>
+  <si>
+    <t>Resurrection 2025</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/resurrection-2025/</t>
+  </si>
+  <si>
+    <t>Green Border</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/green-border/</t>
+  </si>
+  <si>
+    <t>Trenque Lauquen</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/trenque-lauquen/</t>
+  </si>
+  <si>
+    <t>The Wolf Of Wall Street</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-wolf-of-wall-street/</t>
+  </si>
+  <si>
+    <t>Eyes Wide Shut</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/eyes-wide-shut/</t>
+  </si>
+  <si>
+    <t>Aadukalam</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/aadukalam/</t>
+  </si>
+  <si>
+    <t>Close Your Eyes 2023</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/close-your-eyes-2023/</t>
+  </si>
+  <si>
+    <t>Doctor Zhivago</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/doctor-zhivago/</t>
+  </si>
+  <si>
+    <t>Lust Caution</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/lust-caution/</t>
+  </si>
+  <si>
+    <t>Le Deuxieme Souffle</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/le-deuxieme-souffle/</t>
+  </si>
+  <si>
+    <t>Zindagi Na Milegi Dobara</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/zindagi-na-milegi-dobara/</t>
+  </si>
+  <si>
+    <t>Athadu</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/athadu/</t>
+  </si>
+  <si>
+    <t>Bangalore Days</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/bangalore-days/</t>
+  </si>
+  <si>
+    <t>The Wailing</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-wailing/</t>
+  </si>
+  <si>
+    <t>Dr Mabuse The Gambler</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/dr-mabuse-the-gambler/</t>
+  </si>
+  <si>
+    <t>Jigarthanda Doublex</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/jigarthanda-doublex/</t>
+  </si>
+  <si>
+    <t>What The Day Owes The Night</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/what-the-day-owes-the-night/</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/96-2018/</t>
+  </si>
+  <si>
+    <t>Funny Girl</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/funny-girl/</t>
+  </si>
+  <si>
+    <t>Hanagatami</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/hanagatami/</t>
+  </si>
+  <si>
+    <t>Guardians Of The Galaxy Vol 3</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/guardians-of-the-galaxy-vol-3/</t>
+  </si>
+  <si>
+    <t>Office Romance</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/office-romance/</t>
+  </si>
+  <si>
+    <t>Toni Erdmann</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/toni-erdmann/</t>
+  </si>
+  <si>
+    <t>Awaara</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/awaara/</t>
+  </si>
+  <si>
+    <t>The Seed Of The Sacred Fig</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-seed-of-the-sacred-fig/</t>
+  </si>
+  <si>
+    <t>Ustad Hotel</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/ustad-hotel/</t>
+  </si>
+  <si>
+    <t>Ghilli</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/ghilli/</t>
+  </si>
+  <si>
+    <t>Black Friday</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/black-friday-2004/</t>
+  </si>
+  <si>
+    <t>Duck You Sucker</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/duck-you-sucker/</t>
+  </si>
+  <si>
+    <t>Do Not Expect Too Much from the End of the World</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/do-not-expect-too-much-from-the-end-of-the-world/</t>
+  </si>
+  <si>
+    <t>Avengers Endgame</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/avengers-endgame/</t>
+  </si>
+  <si>
+    <t>Iraivi</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/iraivi/</t>
+  </si>
+  <si>
+    <t>A Sun</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/a-sun/</t>
+  </si>
+  <si>
+    <t>Scent Of A Woman</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/scent-of-a-woman/</t>
+  </si>
+  <si>
+    <t>Ludwig</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/ludwig/</t>
+  </si>
+  <si>
+    <t>Never Look Away</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/never-look-away/</t>
+  </si>
+  <si>
+    <t>Until The End Of The World</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/until-the-end-of-the-world/</t>
+  </si>
+  <si>
+    <t>The Last Emperor</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-last-emperor/</t>
+  </si>
+  <si>
+    <t>Swades</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/swades/</t>
+  </si>
+  <si>
+    <t>The Banishment</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-banishment/</t>
+  </si>
+  <si>
+    <t>Omkara</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/omkara/</t>
+  </si>
+  <si>
+    <t>Papanasam</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/papanasam/</t>
+  </si>
+  <si>
+    <t>Dangal</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/dangal/</t>
+  </si>
+  <si>
+    <t>The Color Purple</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-color-purple/</t>
+  </si>
+  <si>
+    <t>Tar 2022</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/tar-2022/</t>
+  </si>
+  <si>
+    <t>American Gangster</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/american-gangster/</t>
+  </si>
+  <si>
+    <t>Reds</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/reds/</t>
+  </si>
+  <si>
+    <t>The Secret Of The Grain</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-secret-of-the-grain/</t>
+  </si>
+  <si>
+    <t>Lion Of The Desert</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/lion-of-the-desert/</t>
+  </si>
+  <si>
+    <t>The Big Parade</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-big-parade/</t>
+  </si>
+  <si>
+    <t>Aayirathil Oruvan</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/aayirathil-oruvan-2010/</t>
+  </si>
+  <si>
+    <t>The Last Temptation of Christ</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-last-temptation-of-christ/</t>
+  </si>
+  <si>
+    <t>Veer-Zaara</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/veer-zaara/</t>
+  </si>
+  <si>
+    <t>Sholay</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/sholay/</t>
+  </si>
+  <si>
+    <t>Dances with Wolves</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/dances-with-wolves/</t>
+  </si>
+  <si>
+    <t>Labyrinth Of Cinema</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/labyrinth-of-cinema/</t>
+  </si>
+  <si>
+    <t>Braveheart</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/braveheart/</t>
+  </si>
+  <si>
+    <t>Sieranevada</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/sieranevada/</t>
+  </si>
+  <si>
+    <t>Margaret</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/margaret/</t>
+  </si>
+  <si>
+    <t>The Message 1976 1</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-message-1976-1/</t>
+  </si>
+  <si>
+    <t>Alaipayuthey</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/alaipayuthey/</t>
+  </si>
+  <si>
+    <t>The Irishman 2019</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-irishman-2019/</t>
+  </si>
+  <si>
+    <t>Beyond the Hills</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/beyond-the-hills/</t>
+  </si>
+  <si>
+    <t>The Revenant 2015</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-revenant-2015/</t>
+  </si>
+  <si>
+    <t>Lagaan Once Upon A Time In India</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/lagaan-once-upon-a-time-in-india/</t>
+  </si>
+  <si>
+    <t>The Girl With The Dragon Tattoo 2011</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-girl-with-the-dragon-tattoo-2011/</t>
+  </si>
+  <si>
+    <t>Patton</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/patton/</t>
+  </si>
+  <si>
+    <t>Fabian Going To The Dogs</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/fabian-going-to-the-dogs/</t>
+  </si>
+  <si>
+    <t>The Brutalist</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-brutalist/</t>
+  </si>
+  <si>
+    <t>Mahanati</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/mahanati/</t>
+  </si>
+  <si>
+    <t>Giant</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/giant/</t>
+  </si>
+  <si>
+    <t>Kabhi Khushi Kabhie Gham</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/kabhi-khushi-kabhie-gham/</t>
+  </si>
+  <si>
+    <t>John Wick Chapter 4</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/john-wick-chapter-4/</t>
+  </si>
+  <si>
+    <t>Inland Empire</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/inland-empire/</t>
+  </si>
+  <si>
+    <t>A Star Is Born</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/a-star-is-born-1954/</t>
+  </si>
+  <si>
+    <t>Kammatti Paadam</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/kammatti-paadam/</t>
+  </si>
+  <si>
+    <t>Dune 2021</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/dune-2021/</t>
+  </si>
+  <si>
+    <t>Garuda Gamana Vrishabha Vahana</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/garuda-gamana-vrishabha-vahana/</t>
+  </si>
+  <si>
+    <t>Jackie Brown</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/jackie-brown/</t>
+  </si>
+  <si>
+    <t>Pokiri</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/pokiri/</t>
+  </si>
+  <si>
+    <t>Thuppakki</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/thuppakki/</t>
+  </si>
+  <si>
+    <t>Harry Potter And The Goblet Of Fire</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/harry-potter-and-the-goblet-of-fire/</t>
+  </si>
+  <si>
+    <t>Thani Oruvan</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/thani-oruvan/</t>
+  </si>
+  <si>
+    <t>Gangubai Kathiawadi</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/gangubai-kathiawadi/</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/1900/</t>
+  </si>
+  <si>
+    <t>Spartacus</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/spartacus/</t>
+  </si>
+  <si>
+    <t>Anniyan</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/anniyan/</t>
+  </si>
+  <si>
+    <t>Babylon</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/babylon-2022/</t>
+  </si>
+  <si>
+    <t>12 Angry Men</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/12-angry-men/</t>
+  </si>
+  <si>
+    <t>La Haine</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/la-haine/</t>
+  </si>
+  <si>
+    <t>Autumn Sonata</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/autumn-sonata/</t>
+  </si>
+  <si>
+    <t>Grave Of The Fireflies</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/grave-of-the-fireflies/</t>
+  </si>
+  <si>
+    <t>Neon Genesis Evangelion The End Of Evangelion</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/neon-genesis-evangelion-the-end-of-evangelion/</t>
+  </si>
+  <si>
+    <t>The Cranes Are Flying</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-cranes-are-flying/</t>
+  </si>
+  <si>
+    <t>Paths Of Glory</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/paths-of-glory/</t>
+  </si>
+  <si>
+    <t>The Passion Of Joan Of Arc</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-passion-of-joan-of-arc/</t>
+  </si>
+  <si>
+    <t>Close Up</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/close-up/</t>
+  </si>
+  <si>
+    <t>Persona</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/persona/</t>
+  </si>
+  <si>
+    <t>Perfect Blue</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/perfect-blue/</t>
+  </si>
+  <si>
+    <t>In The Mood For Love</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/in-the-mood-for-love/</t>
+  </si>
+  <si>
+    <t>Where Is The Friends House</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/where-is-the-friends-house/</t>
+  </si>
+  <si>
+    <t>Sherlock Jr</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/sherlock-jr/</t>
+  </si>
+  <si>
+    <t>Its Such A Beautiful Day</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/its-such-a-beautiful-day/</t>
+  </si>
+  <si>
+    <t>Chainsaw Man The Movie Reze Arc</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/chainsaw-man-the-movie-reze-arc/</t>
+  </si>
+  <si>
+    <t>Three Colours Red</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/three-colours-red/</t>
+  </si>
+  <si>
+    <t>To Be Or Not To Be</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/to-be-or-not-to-be/</t>
+  </si>
+  <si>
+    <t>Wild Strawberries</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/wild-strawberries/</t>
+  </si>
+  <si>
+    <t>City Lights</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/city-lights/</t>
+  </si>
+  <si>
+    <t>The Seventh Seal</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-seventh-seal/</t>
+  </si>
+  <si>
+    <t>Brief Encounter</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/brief-encounter/</t>
+  </si>
+  <si>
+    <t>Taste Of Cherry</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/taste-of-cherry/</t>
+  </si>
+  <si>
+    <t>Before Sunset</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/before-sunset/</t>
+  </si>
+  <si>
+    <t>The 400 Blows</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-400-blows/</t>
+  </si>
+  <si>
+    <t>Dr. Strangelove or: How I Learned to Stop Worrying and Love the Bomb</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/dr-strangelove-or-how-i-learned-to-stop-worrying-and-love-the-bomb/</t>
+  </si>
+  <si>
+    <t>Fantastic Mr Fox</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/fantastic-mr-fox/</t>
+  </si>
+  <si>
+    <t>The Father</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-father-2020/</t>
+  </si>
+  <si>
+    <t>Bicycle Thieves</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/bicycle-thieves/</t>
+  </si>
+  <si>
+    <t>Azur Asmar The Princes Quest</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/azur-asmar-the-princes-quest/</t>
+  </si>
+  <si>
+    <t>Life And Nothing More</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/life-and-nothing-more/</t>
+  </si>
+  <si>
+    <t>The Iron Giant</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-iron-giant/</t>
+  </si>
+  <si>
+    <t>Casablanca</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/casablanca/</t>
+  </si>
+  <si>
+    <t>Look Back 2024</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/look-back-2024/</t>
+  </si>
+  <si>
+    <t>Song Of The Sea</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/song-of-the-sea/</t>
+  </si>
+  <si>
+    <t>Interstella 5555 The 5Tory Of The 5Ecret 5Tar 5Ystem</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/interstella-5555-the-5tory-of-the-5ecret-5tar-5ystem/</t>
+  </si>
+  <si>
+    <t>Mary And Max</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/mary-and-max/</t>
+  </si>
+  <si>
+    <t>Ugetsu</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/ugetsu/</t>
+  </si>
+  <si>
+    <t>Modern Times</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/modern-times/</t>
+  </si>
+  <si>
+    <t>The Night Of The Hunter</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-night-of-the-hunter/</t>
+  </si>
+  <si>
+    <t>Umberto D</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/umberto-d/</t>
+  </si>
+  <si>
+    <t>Winter Light</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/winter-light/</t>
+  </si>
+  <si>
+    <t>Tokyo Godfathers</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/tokyo-godfathers/</t>
+  </si>
+  <si>
+    <t>A Moment Of Innocence</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/a-moment-of-innocence/</t>
+  </si>
+  <si>
+    <t>Marcel The Shell With Shoes On</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/marcel-the-shell-with-shoes-on-2021/</t>
+  </si>
+  <si>
+    <t>Sweet Smell Of Success</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/sweet-smell-of-success/</t>
+  </si>
+  <si>
+    <t>The Grand Budapest Hotel</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-grand-budapest-hotel/</t>
+  </si>
+  <si>
+    <t>Son Of The White Mare</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/son-of-the-white-mare/</t>
+  </si>
+  <si>
+    <t>Macario</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/macario/</t>
+  </si>
+  <si>
+    <t>Kizumonogatari Part 3 Reiketsu</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/kizumonogatari-part-3-reiketsu/</t>
+  </si>
+  <si>
+    <t>Walle</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/walle/</t>
+  </si>
+  <si>
+    <t>Millennium Actress</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/millennium-actress/</t>
+  </si>
+  <si>
+    <t>Make Way For Tomorrow</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/make-way-for-tomorrow/</t>
+  </si>
+  <si>
+    <t>Trainspotting</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/trainspotting/</t>
+  </si>
+  <si>
+    <t>The Lion King</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-lion-king/</t>
+  </si>
+  <si>
+    <t>Yearning</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/yearning/</t>
+  </si>
+  <si>
+    <t>The Man Who Sleeps</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-man-who-sleeps/</t>
+  </si>
+  <si>
+    <t>The Young and the Damned</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-young-and-the-damned/</t>
+  </si>
+  <si>
+    <t>The Given Word</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-given-word/</t>
+  </si>
+  <si>
+    <t>Happy Together</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/happy-together-1997/</t>
+  </si>
+  <si>
+    <t>Cries And Whispers</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/cries-and-whispers/</t>
+  </si>
+  <si>
+    <t>Rio, Northern Zone</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/rio-northern-zone/</t>
+  </si>
+  <si>
+    <t>Persepolis</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/persepolis/</t>
+  </si>
+  <si>
+    <t>The Kid</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-kid/</t>
+  </si>
+  <si>
+    <t>Children Of Heaven</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/children-of-heaven/</t>
+  </si>
+  <si>
+    <t>Good Morning</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/good-morning/</t>
+  </si>
+  <si>
+    <t>Rashomon</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/rashomon/</t>
+  </si>
+  <si>
+    <t>Night Is Short Walk On Girl</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/night-is-short-walk-on-girl/</t>
+  </si>
+  <si>
+    <t>In A Lonely Place</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/in-a-lonely-place/</t>
+  </si>
+  <si>
+    <t>Turtles Can Fly</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/turtles-can-fly/</t>
+  </si>
+  <si>
+    <t>The General</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-general/</t>
+  </si>
+  <si>
+    <t>Ivan's Childhood</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/ivans-childhood/</t>
+  </si>
+  <si>
+    <t>Day Of Wrath</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/day-of-wrath/</t>
+  </si>
+  <si>
+    <t>My Neighbor Totoro</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/my-neighbor-totoro/</t>
+  </si>
+  <si>
+    <t>My Life As A Zucchini</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/my-life-as-a-zucchini/</t>
+  </si>
+  <si>
+    <t>Who Killed Captain Alex</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/who-killed-captain-alex/</t>
+  </si>
+  <si>
+    <t>Klaus</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/klaus/</t>
+  </si>
+  <si>
+    <t>Coraline</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/coraline/</t>
+  </si>
+  <si>
+    <t>The Shop Around The Corner</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-shop-around-the-corner/</t>
+  </si>
+  <si>
+    <t>ClÃ©o from 5 to 7</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/cleo-from-5-to-7/</t>
+  </si>
+  <si>
+    <t>Stand By Me</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/stand-by-me/</t>
+  </si>
+  <si>
+    <t>Sunrise: A Song of Two Humans</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/sunrise-a-song-of-two-humans/</t>
+  </si>
+  <si>
+    <t>Ali Fear Eats The Soul</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/ali-fear-eats-the-soul/</t>
+  </si>
+  <si>
+    <t>The Exterminating Angel</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-exterminating-angel/</t>
+  </si>
+  <si>
+    <t>Ernest Celestine</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/ernest-celestine/</t>
+  </si>
+  <si>
+    <t>The Naked Island</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-naked-island/</t>
+  </si>
+  <si>
+    <t>Revolutionary Girl Utena The Movie</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/revolutionary-girl-utena-the-movie/</t>
+  </si>
+  <si>
+    <t>The Spirit of the Beehive</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-spirit-of-the-beehive/</t>
+  </si>
+  <si>
+    <t>The Green Ray</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-green-ray/</t>
+  </si>
+  <si>
+    <t>Short Term 12</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/short-term-12-2013/</t>
+  </si>
+  <si>
+    <t>Fallen Angels</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/fallen-angels/</t>
+  </si>
+  <si>
+    <t>Memoir Of A Snail</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/memoir-of-a-snail/</t>
+  </si>
+  <si>
+    <t>Through a Glass Darkly</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/through-a-glass-darkly/</t>
+  </si>
+  <si>
+    <t>Hiroshima Mon Amour</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/hiroshima-mon-amour/</t>
+  </si>
+  <si>
+    <t>The Virgin Spring</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-virgin-spring/</t>
+  </si>
+  <si>
+    <t>El Sur</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/el-sur/</t>
+  </si>
+  <si>
+    <t>Three Colours Blue</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/three-colours-blue/</t>
+  </si>
+  <si>
+    <t>The Wolf House</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-wolf-house/</t>
   </si>
 </sst>
 </file>
@@ -404,8 +2498,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D355"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="46.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="71.90625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
@@ -465,6 +2565,3856 @@
         <v>12</v>
       </c>
     </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6">
+        <v>1959</v>
+      </c>
+      <c r="D6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7">
+        <v>2003</v>
+      </c>
+      <c r="D7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8">
+        <v>1993</v>
+      </c>
+      <c r="D8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9">
+        <v>2000</v>
+      </c>
+      <c r="D9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10">
+        <v>1972</v>
+      </c>
+      <c r="D10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11">
+        <v>1985</v>
+      </c>
+      <c r="D11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12">
+        <v>1966</v>
+      </c>
+      <c r="D12" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13">
+        <v>1988</v>
+      </c>
+      <c r="D13" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14">
+        <v>1991</v>
+      </c>
+      <c r="D14" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>31</v>
+      </c>
+      <c r="B15">
+        <v>2008</v>
+      </c>
+      <c r="D15" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>33</v>
+      </c>
+      <c r="B16">
+        <v>1959</v>
+      </c>
+      <c r="D16" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>35</v>
+      </c>
+      <c r="B17">
+        <v>2007</v>
+      </c>
+      <c r="D17" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>37</v>
+      </c>
+      <c r="B18">
+        <v>1966</v>
+      </c>
+      <c r="D18" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19">
+        <v>2014</v>
+      </c>
+      <c r="D19" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20">
+        <v>2002</v>
+      </c>
+      <c r="D20" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>43</v>
+      </c>
+      <c r="B21">
+        <v>1982</v>
+      </c>
+      <c r="D21" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>45</v>
+      </c>
+      <c r="B22">
+        <v>1965</v>
+      </c>
+      <c r="D22" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>47</v>
+      </c>
+      <c r="B23">
+        <v>1975</v>
+      </c>
+      <c r="D23" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>49</v>
+      </c>
+      <c r="B24">
+        <v>2002</v>
+      </c>
+      <c r="D24" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>51</v>
+      </c>
+      <c r="B25">
+        <v>1979</v>
+      </c>
+      <c r="D25" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>53</v>
+      </c>
+      <c r="B26">
+        <v>1974</v>
+      </c>
+      <c r="D26" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>55</v>
+      </c>
+      <c r="B27">
+        <v>1962</v>
+      </c>
+      <c r="D27" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>57</v>
+      </c>
+      <c r="B28">
+        <v>1993</v>
+      </c>
+      <c r="D28" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>59</v>
+      </c>
+      <c r="B29">
+        <v>2008</v>
+      </c>
+      <c r="D29" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>61</v>
+      </c>
+      <c r="B30">
+        <v>1968</v>
+      </c>
+      <c r="D30" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>63</v>
+      </c>
+      <c r="B31">
+        <v>1994</v>
+      </c>
+      <c r="D31" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>65</v>
+      </c>
+      <c r="B32">
+        <v>2001</v>
+      </c>
+      <c r="D32" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>67</v>
+      </c>
+      <c r="B33">
+        <v>2018</v>
+      </c>
+      <c r="D33" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>69</v>
+      </c>
+      <c r="B34">
+        <v>2024</v>
+      </c>
+      <c r="D34" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>71</v>
+      </c>
+      <c r="B35">
+        <v>2009</v>
+      </c>
+      <c r="D35" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>73</v>
+      </c>
+      <c r="B36">
+        <v>1953</v>
+      </c>
+      <c r="D36" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>75</v>
+      </c>
+      <c r="B37">
+        <v>1961</v>
+      </c>
+      <c r="D37" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>77</v>
+      </c>
+      <c r="B38">
+        <v>1984</v>
+      </c>
+      <c r="D38" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>79</v>
+      </c>
+      <c r="B39">
+        <v>2006</v>
+      </c>
+      <c r="D39" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>81</v>
+      </c>
+      <c r="B40">
+        <v>1981</v>
+      </c>
+      <c r="D40" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>83</v>
+      </c>
+      <c r="B41">
+        <v>2012</v>
+      </c>
+      <c r="D41" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>85</v>
+      </c>
+      <c r="B42">
+        <v>2013</v>
+      </c>
+      <c r="D42" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>87</v>
+      </c>
+      <c r="B43">
+        <v>1960</v>
+      </c>
+      <c r="D43" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>89</v>
+      </c>
+      <c r="B44">
+        <v>2003</v>
+      </c>
+      <c r="D44" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>91</v>
+      </c>
+      <c r="B45">
+        <v>2004</v>
+      </c>
+      <c r="D45" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>93</v>
+      </c>
+      <c r="B46">
+        <v>1995</v>
+      </c>
+      <c r="D46" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>95</v>
+      </c>
+      <c r="B47">
+        <v>1995</v>
+      </c>
+      <c r="D47" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
+        <v>97</v>
+      </c>
+      <c r="B48">
+        <v>1974</v>
+      </c>
+      <c r="D48" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
+        <v>99</v>
+      </c>
+      <c r="B49">
+        <v>1945</v>
+      </c>
+      <c r="D49" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>101</v>
+      </c>
+      <c r="B50">
+        <v>2021</v>
+      </c>
+      <c r="D50" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
+        <v>103</v>
+      </c>
+      <c r="B51">
+        <v>1992</v>
+      </c>
+      <c r="D51" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
+        <v>105</v>
+      </c>
+      <c r="B52">
+        <v>2000</v>
+      </c>
+      <c r="D52" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
+        <v>107</v>
+      </c>
+      <c r="B53">
+        <v>1999</v>
+      </c>
+      <c r="D53" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
+        <v>109</v>
+      </c>
+      <c r="B54">
+        <v>1960</v>
+      </c>
+      <c r="D54" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
+        <v>111</v>
+      </c>
+      <c r="B55">
+        <v>1975</v>
+      </c>
+      <c r="D55" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
+        <v>113</v>
+      </c>
+      <c r="B56">
+        <v>1998</v>
+      </c>
+      <c r="D56" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
+        <v>115</v>
+      </c>
+      <c r="B57">
+        <v>1946</v>
+      </c>
+      <c r="D57" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
+        <v>117</v>
+      </c>
+      <c r="B58">
+        <v>1959</v>
+      </c>
+      <c r="D58" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
+        <v>119</v>
+      </c>
+      <c r="B59">
+        <v>2015</v>
+      </c>
+      <c r="D59" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
+        <v>121</v>
+      </c>
+      <c r="B60">
+        <v>1957</v>
+      </c>
+      <c r="D60" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
+        <v>123</v>
+      </c>
+      <c r="B61">
+        <v>2010</v>
+      </c>
+      <c r="D61" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
+        <v>125</v>
+      </c>
+      <c r="B62">
+        <v>1964</v>
+      </c>
+      <c r="D62" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
+        <v>127</v>
+      </c>
+      <c r="B63">
+        <v>1987</v>
+      </c>
+      <c r="D63" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
+        <v>129</v>
+      </c>
+      <c r="B64">
+        <v>1994</v>
+      </c>
+      <c r="D64" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
+        <v>131</v>
+      </c>
+      <c r="B65">
+        <v>2018</v>
+      </c>
+      <c r="D65" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
+        <v>133</v>
+      </c>
+      <c r="B66">
+        <v>1927</v>
+      </c>
+      <c r="D66" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
+        <v>135</v>
+      </c>
+      <c r="B67">
+        <v>1965</v>
+      </c>
+      <c r="D67" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A68" t="s">
+        <v>137</v>
+      </c>
+      <c r="B68">
+        <v>1943</v>
+      </c>
+      <c r="D68" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A69" t="s">
+        <v>139</v>
+      </c>
+      <c r="B69">
+        <v>2011</v>
+      </c>
+      <c r="D69" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A70" t="s">
+        <v>141</v>
+      </c>
+      <c r="B70">
+        <v>1980</v>
+      </c>
+      <c r="D70" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A71" t="s">
+        <v>143</v>
+      </c>
+      <c r="B71">
+        <v>1972</v>
+      </c>
+      <c r="D71" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A72" t="s">
+        <v>145</v>
+      </c>
+      <c r="B72">
+        <v>1999</v>
+      </c>
+      <c r="D72" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A73" t="s">
+        <v>147</v>
+      </c>
+      <c r="B73">
+        <v>1984</v>
+      </c>
+      <c r="D73" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A74" t="s">
+        <v>149</v>
+      </c>
+      <c r="B74">
+        <v>1991</v>
+      </c>
+      <c r="D74" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A75" t="s">
+        <v>151</v>
+      </c>
+      <c r="B75">
+        <v>1978</v>
+      </c>
+      <c r="D75" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A76" t="s">
+        <v>153</v>
+      </c>
+      <c r="B76">
+        <v>1971</v>
+      </c>
+      <c r="D76" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A77" t="s">
+        <v>155</v>
+      </c>
+      <c r="B77">
+        <v>2014</v>
+      </c>
+      <c r="D77" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A78" t="s">
+        <v>157</v>
+      </c>
+      <c r="B78">
+        <v>2004</v>
+      </c>
+      <c r="D78" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A79" t="s">
+        <v>159</v>
+      </c>
+      <c r="B79">
+        <v>1995</v>
+      </c>
+      <c r="D79" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A80" t="s">
+        <v>161</v>
+      </c>
+      <c r="B80">
+        <v>2024</v>
+      </c>
+      <c r="D80" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A81" t="s">
+        <v>163</v>
+      </c>
+      <c r="B81">
+        <v>1997</v>
+      </c>
+      <c r="D81" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A82" t="s">
+        <v>165</v>
+      </c>
+      <c r="B82">
+        <v>2021</v>
+      </c>
+      <c r="D82" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A83" t="s">
+        <v>167</v>
+      </c>
+      <c r="B83">
+        <v>2022</v>
+      </c>
+      <c r="D83" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A84" t="s">
+        <v>169</v>
+      </c>
+      <c r="B84">
+        <v>2003</v>
+      </c>
+      <c r="D84" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A85" t="s">
+        <v>171</v>
+      </c>
+      <c r="B85">
+        <v>1967</v>
+      </c>
+      <c r="D85" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A86" t="s">
+        <v>173</v>
+      </c>
+      <c r="B86">
+        <v>1995</v>
+      </c>
+      <c r="D86" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A87" t="s">
+        <v>175</v>
+      </c>
+      <c r="B87">
+        <v>2012</v>
+      </c>
+      <c r="D87" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A88" t="s">
+        <v>177</v>
+      </c>
+      <c r="B88">
+        <v>2003</v>
+      </c>
+      <c r="D88" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A89" t="s">
+        <v>179</v>
+      </c>
+      <c r="B89">
+        <v>2009</v>
+      </c>
+      <c r="D89" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A90" t="s">
+        <v>181</v>
+      </c>
+      <c r="B90">
+        <v>2025</v>
+      </c>
+      <c r="D90" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A91" t="s">
+        <v>183</v>
+      </c>
+      <c r="B91">
+        <v>1974</v>
+      </c>
+      <c r="D91" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A92" t="s">
+        <v>185</v>
+      </c>
+      <c r="B92">
+        <v>2018</v>
+      </c>
+      <c r="D92" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A93" t="s">
+        <v>187</v>
+      </c>
+      <c r="B93">
+        <v>2000</v>
+      </c>
+      <c r="D93" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A94" t="s">
+        <v>189</v>
+      </c>
+      <c r="B94">
+        <v>1973</v>
+      </c>
+      <c r="D94" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A95" t="s">
+        <v>191</v>
+      </c>
+      <c r="B95">
+        <v>2011</v>
+      </c>
+      <c r="D95" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A96" t="s">
+        <v>193</v>
+      </c>
+      <c r="B96">
+        <v>2000</v>
+      </c>
+      <c r="D96" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A97" t="s">
+        <v>195</v>
+      </c>
+      <c r="B97">
+        <v>1975</v>
+      </c>
+      <c r="D97" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A98" t="s">
+        <v>197</v>
+      </c>
+      <c r="B98">
+        <v>1991</v>
+      </c>
+      <c r="D98" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A99" t="s">
+        <v>199</v>
+      </c>
+      <c r="B99">
+        <v>2023</v>
+      </c>
+      <c r="D99" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A100" t="s">
+        <v>201</v>
+      </c>
+      <c r="B100">
+        <v>1963</v>
+      </c>
+      <c r="D100" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A101" t="s">
+        <v>203</v>
+      </c>
+      <c r="B101">
+        <v>2019</v>
+      </c>
+      <c r="D101" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A102" t="s">
+        <v>205</v>
+      </c>
+      <c r="B102">
+        <v>1975</v>
+      </c>
+      <c r="D102" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A103" t="s">
+        <v>207</v>
+      </c>
+      <c r="B103">
+        <v>1989</v>
+      </c>
+      <c r="D103" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A104" t="s">
+        <v>209</v>
+      </c>
+      <c r="B104">
+        <v>1963</v>
+      </c>
+      <c r="D104" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A105" t="s">
+        <v>211</v>
+      </c>
+      <c r="B105">
+        <v>1996</v>
+      </c>
+      <c r="D105" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A106" t="s">
+        <v>213</v>
+      </c>
+      <c r="B106">
+        <v>2025</v>
+      </c>
+      <c r="D106" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A107" t="s">
+        <v>215</v>
+      </c>
+      <c r="B107">
+        <v>1983</v>
+      </c>
+      <c r="D107" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A108" t="s">
+        <v>217</v>
+      </c>
+      <c r="B108">
+        <v>2009</v>
+      </c>
+      <c r="D108" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A109" t="s">
+        <v>219</v>
+      </c>
+      <c r="B109">
+        <v>1982</v>
+      </c>
+      <c r="D109" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A110" t="s">
+        <v>221</v>
+      </c>
+      <c r="B110">
+        <v>1993</v>
+      </c>
+      <c r="D110" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A111" t="s">
+        <v>223</v>
+      </c>
+      <c r="B111">
+        <v>1984</v>
+      </c>
+      <c r="D111" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A112" t="s">
+        <v>225</v>
+      </c>
+      <c r="B112">
+        <v>1971</v>
+      </c>
+      <c r="D112" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A113" t="s">
+        <v>227</v>
+      </c>
+      <c r="B113">
+        <v>2023</v>
+      </c>
+      <c r="D113" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A114" t="s">
+        <v>229</v>
+      </c>
+      <c r="B114">
+        <v>2004</v>
+      </c>
+      <c r="D114" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A115" t="s">
+        <v>231</v>
+      </c>
+      <c r="B115">
+        <v>1970</v>
+      </c>
+      <c r="D115" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A116" t="s">
+        <v>233</v>
+      </c>
+      <c r="B116">
+        <v>1960</v>
+      </c>
+      <c r="D116" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A117" t="s">
+        <v>235</v>
+      </c>
+      <c r="B117">
+        <v>2000</v>
+      </c>
+      <c r="D117" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A118" t="s">
+        <v>237</v>
+      </c>
+      <c r="B118">
+        <v>2017</v>
+      </c>
+      <c r="D118" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A119" t="s">
+        <v>239</v>
+      </c>
+      <c r="B119">
+        <v>2024</v>
+      </c>
+      <c r="D119" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A120" t="s">
+        <v>241</v>
+      </c>
+      <c r="B120">
+        <v>1978</v>
+      </c>
+      <c r="D120" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A121" t="s">
+        <v>243</v>
+      </c>
+      <c r="B121">
+        <v>2006</v>
+      </c>
+      <c r="D121" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A122" t="s">
+        <v>245</v>
+      </c>
+      <c r="B122">
+        <v>1999</v>
+      </c>
+      <c r="D122" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A123" t="s">
+        <v>247</v>
+      </c>
+      <c r="B123">
+        <v>1998</v>
+      </c>
+      <c r="D123" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A124" t="s">
+        <v>249</v>
+      </c>
+      <c r="B124">
+        <v>1959</v>
+      </c>
+      <c r="D124" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A125" t="s">
+        <v>251</v>
+      </c>
+      <c r="B125">
+        <v>2016</v>
+      </c>
+      <c r="D125" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A126" t="s">
+        <v>253</v>
+      </c>
+      <c r="B126">
+        <v>2013</v>
+      </c>
+      <c r="D126" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A127" t="s">
+        <v>255</v>
+      </c>
+      <c r="B127">
+        <v>2005</v>
+      </c>
+      <c r="D127" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A128" t="s">
+        <v>257</v>
+      </c>
+      <c r="B128">
+        <v>2000</v>
+      </c>
+      <c r="D128" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A129" t="s">
+        <v>259</v>
+      </c>
+      <c r="B129">
+        <v>1965</v>
+      </c>
+      <c r="D129" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A130" t="s">
+        <v>261</v>
+      </c>
+      <c r="B130">
+        <v>2018</v>
+      </c>
+      <c r="D130" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A131" t="s">
+        <v>263</v>
+      </c>
+      <c r="B131">
+        <v>1991</v>
+      </c>
+      <c r="D131" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A132" t="s">
+        <v>265</v>
+      </c>
+      <c r="B132">
+        <v>2019</v>
+      </c>
+      <c r="D132" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A133" t="s">
+        <v>267</v>
+      </c>
+      <c r="B133">
+        <v>2025</v>
+      </c>
+      <c r="D133" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A134" t="s">
+        <v>269</v>
+      </c>
+      <c r="B134">
+        <v>2014</v>
+      </c>
+      <c r="D134" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A135" t="s">
+        <v>271</v>
+      </c>
+      <c r="B135">
+        <v>2014</v>
+      </c>
+      <c r="D135" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A136" t="s">
+        <v>273</v>
+      </c>
+      <c r="B136">
+        <v>2013</v>
+      </c>
+      <c r="D136" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A137" t="s">
+        <v>275</v>
+      </c>
+      <c r="B137">
+        <v>2019</v>
+      </c>
+      <c r="D137" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A138" t="s">
+        <v>277</v>
+      </c>
+      <c r="B138">
+        <v>1998</v>
+      </c>
+      <c r="D138" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A139" t="s">
+        <v>279</v>
+      </c>
+      <c r="B139">
+        <v>2015</v>
+      </c>
+      <c r="D139" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A140" t="s">
+        <v>281</v>
+      </c>
+      <c r="B140">
+        <v>2012</v>
+      </c>
+      <c r="D140" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A141" t="s">
+        <v>283</v>
+      </c>
+      <c r="B141">
+        <v>2012</v>
+      </c>
+      <c r="D141" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A142" t="s">
+        <v>285</v>
+      </c>
+      <c r="B142">
+        <v>2014</v>
+      </c>
+      <c r="D142" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A143" t="s">
+        <v>287</v>
+      </c>
+      <c r="B143">
+        <v>2008</v>
+      </c>
+      <c r="D143" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A144" t="s">
+        <v>289</v>
+      </c>
+      <c r="B144">
+        <v>1993</v>
+      </c>
+      <c r="D144" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A145" t="s">
+        <v>291</v>
+      </c>
+      <c r="B145">
+        <v>1988</v>
+      </c>
+      <c r="D145" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A146" t="s">
+        <v>293</v>
+      </c>
+      <c r="B146">
+        <v>2025</v>
+      </c>
+      <c r="D146" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A147" t="s">
+        <v>295</v>
+      </c>
+      <c r="B147">
+        <v>1973</v>
+      </c>
+      <c r="D147" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A148" t="s">
+        <v>297</v>
+      </c>
+      <c r="B148">
+        <v>1948</v>
+      </c>
+      <c r="D148" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A149" t="s">
+        <v>299</v>
+      </c>
+      <c r="B149">
+        <v>1958</v>
+      </c>
+      <c r="D149" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A150" t="s">
+        <v>301</v>
+      </c>
+      <c r="B150">
+        <v>2007</v>
+      </c>
+      <c r="D150" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A151" t="s">
+        <v>303</v>
+      </c>
+      <c r="B151">
+        <v>2007</v>
+      </c>
+      <c r="D151" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A152" t="s">
+        <v>305</v>
+      </c>
+      <c r="B152">
+        <v>1983</v>
+      </c>
+      <c r="D152" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A153" t="s">
+        <v>307</v>
+      </c>
+      <c r="B153">
+        <v>2019</v>
+      </c>
+      <c r="D153" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A154" t="s">
+        <v>309</v>
+      </c>
+      <c r="B154">
+        <v>1998</v>
+      </c>
+      <c r="D154" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A155" t="s">
+        <v>311</v>
+      </c>
+      <c r="B155">
+        <v>1983</v>
+      </c>
+      <c r="D155" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A156" t="s">
+        <v>313</v>
+      </c>
+      <c r="B156">
+        <v>2023</v>
+      </c>
+      <c r="D156" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A157" t="s">
+        <v>315</v>
+      </c>
+      <c r="B157">
+        <v>2023</v>
+      </c>
+      <c r="D157" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A158" t="s">
+        <v>317</v>
+      </c>
+      <c r="B158">
+        <v>2019</v>
+      </c>
+      <c r="D158" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A159" t="s">
+        <v>319</v>
+      </c>
+      <c r="B159">
+        <v>2007</v>
+      </c>
+      <c r="D159" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A160" t="s">
+        <v>321</v>
+      </c>
+      <c r="B160">
+        <v>2022</v>
+      </c>
+      <c r="D160" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A161" t="s">
+        <v>323</v>
+      </c>
+      <c r="B161">
+        <v>2015</v>
+      </c>
+      <c r="D161" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A162" t="s">
+        <v>325</v>
+      </c>
+      <c r="B162">
+        <v>1993</v>
+      </c>
+      <c r="D162" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A163" t="s">
+        <v>327</v>
+      </c>
+      <c r="B163">
+        <v>2021</v>
+      </c>
+      <c r="D163" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A164" t="s">
+        <v>329</v>
+      </c>
+      <c r="B164">
+        <v>2007</v>
+      </c>
+      <c r="D164" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A165" t="s">
+        <v>331</v>
+      </c>
+      <c r="B165">
+        <v>1976</v>
+      </c>
+      <c r="D165" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A166" t="s">
+        <v>333</v>
+      </c>
+      <c r="B166">
+        <v>1995</v>
+      </c>
+      <c r="D166" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A167" t="s">
+        <v>335</v>
+      </c>
+      <c r="B167">
+        <v>2021</v>
+      </c>
+      <c r="D167" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A168" t="s">
+        <v>337</v>
+      </c>
+      <c r="B168">
+        <v>2016</v>
+      </c>
+      <c r="D168" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A169" t="s">
+        <v>339</v>
+      </c>
+      <c r="B169">
+        <v>2022</v>
+      </c>
+      <c r="D169" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A170" t="s">
+        <v>341</v>
+      </c>
+      <c r="B170">
+        <v>2025</v>
+      </c>
+      <c r="D170" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A171" t="s">
+        <v>343</v>
+      </c>
+      <c r="B171">
+        <v>2023</v>
+      </c>
+      <c r="D171" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A172" t="s">
+        <v>345</v>
+      </c>
+      <c r="B172">
+        <v>2022</v>
+      </c>
+      <c r="D172" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A173" t="s">
+        <v>347</v>
+      </c>
+      <c r="B173">
+        <v>2013</v>
+      </c>
+      <c r="D173" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="174" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A174" t="s">
+        <v>349</v>
+      </c>
+      <c r="B174">
+        <v>1999</v>
+      </c>
+      <c r="D174" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A175" t="s">
+        <v>351</v>
+      </c>
+      <c r="B175">
+        <v>2011</v>
+      </c>
+      <c r="D175" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A176" t="s">
+        <v>353</v>
+      </c>
+      <c r="B176">
+        <v>2023</v>
+      </c>
+      <c r="D176" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A177" t="s">
+        <v>355</v>
+      </c>
+      <c r="B177">
+        <v>1965</v>
+      </c>
+      <c r="D177" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A178" t="s">
+        <v>357</v>
+      </c>
+      <c r="B178">
+        <v>2007</v>
+      </c>
+      <c r="D178" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A179" t="s">
+        <v>359</v>
+      </c>
+      <c r="B179">
+        <v>1966</v>
+      </c>
+      <c r="D179" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="180" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A180" t="s">
+        <v>361</v>
+      </c>
+      <c r="B180">
+        <v>2011</v>
+      </c>
+      <c r="D180" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="181" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A181" t="s">
+        <v>363</v>
+      </c>
+      <c r="B181">
+        <v>2005</v>
+      </c>
+      <c r="D181" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="182" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A182" t="s">
+        <v>365</v>
+      </c>
+      <c r="B182">
+        <v>2014</v>
+      </c>
+      <c r="D182" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="183" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A183" t="s">
+        <v>367</v>
+      </c>
+      <c r="B183">
+        <v>2016</v>
+      </c>
+      <c r="D183" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="184" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A184" t="s">
+        <v>369</v>
+      </c>
+      <c r="B184">
+        <v>1922</v>
+      </c>
+      <c r="D184" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="185" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A185" t="s">
+        <v>371</v>
+      </c>
+      <c r="B185">
+        <v>2023</v>
+      </c>
+      <c r="D185" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="186" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A186" t="s">
+        <v>373</v>
+      </c>
+      <c r="B186">
+        <v>2012</v>
+      </c>
+      <c r="D186" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="187" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A187">
+        <v>96</v>
+      </c>
+      <c r="B187">
+        <v>2018</v>
+      </c>
+      <c r="D187" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="188" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A188" t="s">
+        <v>376</v>
+      </c>
+      <c r="B188">
+        <v>1968</v>
+      </c>
+      <c r="D188" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="189" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A189" t="s">
+        <v>378</v>
+      </c>
+      <c r="B189">
+        <v>2017</v>
+      </c>
+      <c r="D189" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="190" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A190" t="s">
+        <v>380</v>
+      </c>
+      <c r="B190">
+        <v>2023</v>
+      </c>
+      <c r="D190" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A191" t="s">
+        <v>382</v>
+      </c>
+      <c r="B191">
+        <v>1977</v>
+      </c>
+      <c r="D191" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="192" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A192" t="s">
+        <v>384</v>
+      </c>
+      <c r="B192">
+        <v>2016</v>
+      </c>
+      <c r="D192" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="193" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A193" t="s">
+        <v>386</v>
+      </c>
+      <c r="B193">
+        <v>1951</v>
+      </c>
+      <c r="D193" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A194" t="s">
+        <v>388</v>
+      </c>
+      <c r="B194">
+        <v>2024</v>
+      </c>
+      <c r="D194" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A195" t="s">
+        <v>390</v>
+      </c>
+      <c r="B195">
+        <v>2012</v>
+      </c>
+      <c r="D195" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A196" t="s">
+        <v>392</v>
+      </c>
+      <c r="B196">
+        <v>2004</v>
+      </c>
+      <c r="D196" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="197" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A197" t="s">
+        <v>394</v>
+      </c>
+      <c r="B197">
+        <v>2004</v>
+      </c>
+      <c r="D197" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A198" t="s">
+        <v>396</v>
+      </c>
+      <c r="B198">
+        <v>1971</v>
+      </c>
+      <c r="D198" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="199" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A199" t="s">
+        <v>398</v>
+      </c>
+      <c r="B199">
+        <v>2023</v>
+      </c>
+      <c r="D199" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A200" t="s">
+        <v>400</v>
+      </c>
+      <c r="B200">
+        <v>2019</v>
+      </c>
+      <c r="D200" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A201" t="s">
+        <v>402</v>
+      </c>
+      <c r="B201">
+        <v>2016</v>
+      </c>
+      <c r="D201" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="202" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A202" t="s">
+        <v>404</v>
+      </c>
+      <c r="B202">
+        <v>2019</v>
+      </c>
+      <c r="D202" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="203" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A203" t="s">
+        <v>406</v>
+      </c>
+      <c r="B203">
+        <v>1992</v>
+      </c>
+      <c r="D203" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="204" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A204" t="s">
+        <v>408</v>
+      </c>
+      <c r="B204">
+        <v>1973</v>
+      </c>
+      <c r="D204" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="205" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A205" t="s">
+        <v>410</v>
+      </c>
+      <c r="B205">
+        <v>2018</v>
+      </c>
+      <c r="D205" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="206" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A206" t="s">
+        <v>412</v>
+      </c>
+      <c r="B206">
+        <v>1991</v>
+      </c>
+      <c r="D206" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="207" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A207" t="s">
+        <v>414</v>
+      </c>
+      <c r="B207">
+        <v>1987</v>
+      </c>
+      <c r="D207" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="208" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A208" t="s">
+        <v>416</v>
+      </c>
+      <c r="B208">
+        <v>2004</v>
+      </c>
+      <c r="D208" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="209" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A209" t="s">
+        <v>418</v>
+      </c>
+      <c r="B209">
+        <v>2007</v>
+      </c>
+      <c r="D209" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="210" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A210" t="s">
+        <v>420</v>
+      </c>
+      <c r="B210">
+        <v>2006</v>
+      </c>
+      <c r="D210" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="211" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A211" t="s">
+        <v>422</v>
+      </c>
+      <c r="B211">
+        <v>2015</v>
+      </c>
+      <c r="D211" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="212" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A212" t="s">
+        <v>424</v>
+      </c>
+      <c r="B212">
+        <v>2016</v>
+      </c>
+      <c r="D212" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="213" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A213" t="s">
+        <v>426</v>
+      </c>
+      <c r="B213">
+        <v>1985</v>
+      </c>
+      <c r="D213" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="214" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A214" t="s">
+        <v>428</v>
+      </c>
+      <c r="B214">
+        <v>2022</v>
+      </c>
+      <c r="D214" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="215" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A215" t="s">
+        <v>430</v>
+      </c>
+      <c r="B215">
+        <v>2007</v>
+      </c>
+      <c r="D215" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="216" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A216" t="s">
+        <v>432</v>
+      </c>
+      <c r="B216">
+        <v>1981</v>
+      </c>
+      <c r="D216" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="217" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A217" t="s">
+        <v>434</v>
+      </c>
+      <c r="B217">
+        <v>2007</v>
+      </c>
+      <c r="D217" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="218" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A218" t="s">
+        <v>436</v>
+      </c>
+      <c r="B218">
+        <v>1980</v>
+      </c>
+      <c r="D218" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="219" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A219" t="s">
+        <v>438</v>
+      </c>
+      <c r="B219">
+        <v>1925</v>
+      </c>
+      <c r="D219" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="220" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A220" t="s">
+        <v>440</v>
+      </c>
+      <c r="B220">
+        <v>2010</v>
+      </c>
+      <c r="D220" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="221" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A221" t="s">
+        <v>442</v>
+      </c>
+      <c r="B221">
+        <v>1988</v>
+      </c>
+      <c r="D221" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="222" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A222" t="s">
+        <v>444</v>
+      </c>
+      <c r="B222">
+        <v>2004</v>
+      </c>
+      <c r="D222" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="223" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A223" t="s">
+        <v>446</v>
+      </c>
+      <c r="B223">
+        <v>1975</v>
+      </c>
+      <c r="D223" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="224" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A224" t="s">
+        <v>448</v>
+      </c>
+      <c r="B224">
+        <v>1990</v>
+      </c>
+      <c r="D224" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="225" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A225" t="s">
+        <v>450</v>
+      </c>
+      <c r="B225">
+        <v>2019</v>
+      </c>
+      <c r="D225" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="226" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A226" t="s">
+        <v>452</v>
+      </c>
+      <c r="B226">
+        <v>1995</v>
+      </c>
+      <c r="D226" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="227" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A227" t="s">
+        <v>454</v>
+      </c>
+      <c r="B227">
+        <v>2016</v>
+      </c>
+      <c r="D227" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="228" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A228" t="s">
+        <v>456</v>
+      </c>
+      <c r="B228">
+        <v>2011</v>
+      </c>
+      <c r="D228" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="229" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A229" t="s">
+        <v>458</v>
+      </c>
+      <c r="B229">
+        <v>1976</v>
+      </c>
+      <c r="D229" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="230" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A230" t="s">
+        <v>460</v>
+      </c>
+      <c r="B230">
+        <v>2000</v>
+      </c>
+      <c r="D230" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="231" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A231" t="s">
+        <v>462</v>
+      </c>
+      <c r="B231">
+        <v>2019</v>
+      </c>
+      <c r="D231" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="232" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A232" t="s">
+        <v>464</v>
+      </c>
+      <c r="B232">
+        <v>2012</v>
+      </c>
+      <c r="D232" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="233" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A233" t="s">
+        <v>466</v>
+      </c>
+      <c r="B233">
+        <v>2015</v>
+      </c>
+      <c r="D233" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="234" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A234" t="s">
+        <v>468</v>
+      </c>
+      <c r="B234">
+        <v>2001</v>
+      </c>
+      <c r="D234" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="235" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A235" t="s">
+        <v>470</v>
+      </c>
+      <c r="B235">
+        <v>2011</v>
+      </c>
+      <c r="D235" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="236" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A236" t="s">
+        <v>472</v>
+      </c>
+      <c r="B236">
+        <v>1969</v>
+      </c>
+      <c r="D236" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="237" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A237" t="s">
+        <v>474</v>
+      </c>
+      <c r="B237">
+        <v>2021</v>
+      </c>
+      <c r="D237" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="238" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A238" t="s">
+        <v>476</v>
+      </c>
+      <c r="B238">
+        <v>2024</v>
+      </c>
+      <c r="D238" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="239" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A239" t="s">
+        <v>478</v>
+      </c>
+      <c r="B239">
+        <v>2018</v>
+      </c>
+      <c r="D239" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="240" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A240" t="s">
+        <v>480</v>
+      </c>
+      <c r="B240">
+        <v>1956</v>
+      </c>
+      <c r="D240" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="241" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A241" t="s">
+        <v>482</v>
+      </c>
+      <c r="B241">
+        <v>2001</v>
+      </c>
+      <c r="D241" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="242" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A242" t="s">
+        <v>484</v>
+      </c>
+      <c r="B242">
+        <v>2023</v>
+      </c>
+      <c r="D242" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="243" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A243" t="s">
+        <v>486</v>
+      </c>
+      <c r="B243">
+        <v>2006</v>
+      </c>
+      <c r="D243" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="244" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A244" t="s">
+        <v>488</v>
+      </c>
+      <c r="B244">
+        <v>1954</v>
+      </c>
+      <c r="D244" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="245" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A245" t="s">
+        <v>490</v>
+      </c>
+      <c r="B245">
+        <v>2016</v>
+      </c>
+      <c r="D245" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="246" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A246" t="s">
+        <v>492</v>
+      </c>
+      <c r="B246">
+        <v>2021</v>
+      </c>
+      <c r="D246" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="247" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A247" t="s">
+        <v>494</v>
+      </c>
+      <c r="B247">
+        <v>2021</v>
+      </c>
+      <c r="D247" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="248" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A248" t="s">
+        <v>496</v>
+      </c>
+      <c r="B248">
+        <v>1997</v>
+      </c>
+      <c r="D248" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="249" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A249" t="s">
+        <v>498</v>
+      </c>
+      <c r="B249">
+        <v>2006</v>
+      </c>
+      <c r="D249" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="250" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A250" t="s">
+        <v>500</v>
+      </c>
+      <c r="B250">
+        <v>2012</v>
+      </c>
+      <c r="D250" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="251" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A251" t="s">
+        <v>502</v>
+      </c>
+      <c r="B251">
+        <v>2005</v>
+      </c>
+      <c r="D251" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="252" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A252" t="s">
+        <v>504</v>
+      </c>
+      <c r="B252">
+        <v>2015</v>
+      </c>
+      <c r="D252" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="253" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A253" t="s">
+        <v>506</v>
+      </c>
+      <c r="B253">
+        <v>2022</v>
+      </c>
+      <c r="D253" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="254" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A254">
+        <v>1900</v>
+      </c>
+      <c r="B254">
+        <v>1976</v>
+      </c>
+      <c r="D254" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="255" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A255" t="s">
+        <v>509</v>
+      </c>
+      <c r="B255">
+        <v>1960</v>
+      </c>
+      <c r="D255" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="256" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A256" t="s">
+        <v>511</v>
+      </c>
+      <c r="B256">
+        <v>2005</v>
+      </c>
+      <c r="D256" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="257" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A257" t="s">
+        <v>513</v>
+      </c>
+      <c r="B257">
+        <v>2022</v>
+      </c>
+      <c r="D257" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="258" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A258" t="s">
+        <v>515</v>
+      </c>
+      <c r="B258">
+        <v>1957</v>
+      </c>
+      <c r="D258" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="259" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A259" t="s">
+        <v>517</v>
+      </c>
+      <c r="B259">
+        <v>1995</v>
+      </c>
+      <c r="D259" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="260" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A260" t="s">
+        <v>519</v>
+      </c>
+      <c r="B260">
+        <v>1978</v>
+      </c>
+      <c r="D260" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="261" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A261" t="s">
+        <v>521</v>
+      </c>
+      <c r="B261">
+        <v>1988</v>
+      </c>
+      <c r="D261" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="262" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A262" t="s">
+        <v>523</v>
+      </c>
+      <c r="B262">
+        <v>1997</v>
+      </c>
+      <c r="D262" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="263" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A263" t="s">
+        <v>525</v>
+      </c>
+      <c r="B263">
+        <v>1957</v>
+      </c>
+      <c r="D263" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="264" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A264" t="s">
+        <v>527</v>
+      </c>
+      <c r="B264">
+        <v>1957</v>
+      </c>
+      <c r="D264" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="265" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A265" t="s">
+        <v>529</v>
+      </c>
+      <c r="B265">
+        <v>1928</v>
+      </c>
+      <c r="D265" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="266" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A266" t="s">
+        <v>531</v>
+      </c>
+      <c r="B266">
+        <v>1990</v>
+      </c>
+      <c r="D266" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="267" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A267" t="s">
+        <v>533</v>
+      </c>
+      <c r="B267">
+        <v>1966</v>
+      </c>
+      <c r="D267" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="268" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A268" t="s">
+        <v>535</v>
+      </c>
+      <c r="B268">
+        <v>1997</v>
+      </c>
+      <c r="D268" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="269" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A269" t="s">
+        <v>537</v>
+      </c>
+      <c r="B269">
+        <v>2000</v>
+      </c>
+      <c r="D269" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="270" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A270" t="s">
+        <v>539</v>
+      </c>
+      <c r="B270">
+        <v>1987</v>
+      </c>
+      <c r="D270" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="271" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A271" t="s">
+        <v>541</v>
+      </c>
+      <c r="B271">
+        <v>1924</v>
+      </c>
+      <c r="D271" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="272" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A272" t="s">
+        <v>543</v>
+      </c>
+      <c r="B272">
+        <v>2012</v>
+      </c>
+      <c r="D272" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="273" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A273" t="s">
+        <v>545</v>
+      </c>
+      <c r="B273">
+        <v>2025</v>
+      </c>
+      <c r="D273" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="274" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A274" t="s">
+        <v>547</v>
+      </c>
+      <c r="B274">
+        <v>1994</v>
+      </c>
+      <c r="D274" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="275" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A275" t="s">
+        <v>549</v>
+      </c>
+      <c r="B275">
+        <v>1942</v>
+      </c>
+      <c r="D275" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="276" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A276" t="s">
+        <v>551</v>
+      </c>
+      <c r="B276">
+        <v>1957</v>
+      </c>
+      <c r="D276" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="277" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A277" t="s">
+        <v>553</v>
+      </c>
+      <c r="B277">
+        <v>1931</v>
+      </c>
+      <c r="D277" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="278" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A278" t="s">
+        <v>555</v>
+      </c>
+      <c r="B278">
+        <v>1957</v>
+      </c>
+      <c r="D278" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="279" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A279" t="s">
+        <v>557</v>
+      </c>
+      <c r="B279">
+        <v>1945</v>
+      </c>
+      <c r="D279" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="280" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A280" t="s">
+        <v>559</v>
+      </c>
+      <c r="B280">
+        <v>1997</v>
+      </c>
+      <c r="D280" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="281" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A281" t="s">
+        <v>561</v>
+      </c>
+      <c r="B281">
+        <v>2004</v>
+      </c>
+      <c r="D281" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="282" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A282" t="s">
+        <v>563</v>
+      </c>
+      <c r="B282">
+        <v>1959</v>
+      </c>
+      <c r="D282" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="283" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A283" t="s">
+        <v>565</v>
+      </c>
+      <c r="B283">
+        <v>1964</v>
+      </c>
+      <c r="D283" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="284" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A284" t="s">
+        <v>567</v>
+      </c>
+      <c r="B284">
+        <v>2009</v>
+      </c>
+      <c r="D284" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="285" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A285" t="s">
+        <v>569</v>
+      </c>
+      <c r="B285">
+        <v>2020</v>
+      </c>
+      <c r="D285" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="286" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A286" t="s">
+        <v>571</v>
+      </c>
+      <c r="B286">
+        <v>1948</v>
+      </c>
+      <c r="D286" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="287" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A287" t="s">
+        <v>573</v>
+      </c>
+      <c r="B287">
+        <v>2006</v>
+      </c>
+      <c r="D287" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="288" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A288" t="s">
+        <v>575</v>
+      </c>
+      <c r="B288">
+        <v>1992</v>
+      </c>
+      <c r="D288" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="289" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A289" t="s">
+        <v>577</v>
+      </c>
+      <c r="B289">
+        <v>1999</v>
+      </c>
+      <c r="D289" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="290" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A290" t="s">
+        <v>579</v>
+      </c>
+      <c r="B290">
+        <v>1942</v>
+      </c>
+      <c r="D290" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="291" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A291" t="s">
+        <v>581</v>
+      </c>
+      <c r="B291">
+        <v>2024</v>
+      </c>
+      <c r="D291" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="292" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A292" t="s">
+        <v>583</v>
+      </c>
+      <c r="B292">
+        <v>2014</v>
+      </c>
+      <c r="D292" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="293" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A293" t="s">
+        <v>585</v>
+      </c>
+      <c r="B293">
+        <v>2003</v>
+      </c>
+      <c r="D293" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="294" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A294" t="s">
+        <v>587</v>
+      </c>
+      <c r="B294">
+        <v>2009</v>
+      </c>
+      <c r="D294" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="295" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A295" t="s">
+        <v>589</v>
+      </c>
+      <c r="B295">
+        <v>1953</v>
+      </c>
+      <c r="D295" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="296" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A296" t="s">
+        <v>591</v>
+      </c>
+      <c r="B296">
+        <v>1936</v>
+      </c>
+      <c r="D296" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="297" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A297" t="s">
+        <v>593</v>
+      </c>
+      <c r="B297">
+        <v>1955</v>
+      </c>
+      <c r="D297" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="298" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A298" t="s">
+        <v>595</v>
+      </c>
+      <c r="B298">
+        <v>1952</v>
+      </c>
+      <c r="D298" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="299" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A299" t="s">
+        <v>597</v>
+      </c>
+      <c r="B299">
+        <v>1963</v>
+      </c>
+      <c r="D299" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="300" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A300" t="s">
+        <v>599</v>
+      </c>
+      <c r="B300">
+        <v>2003</v>
+      </c>
+      <c r="D300" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="301" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A301" t="s">
+        <v>601</v>
+      </c>
+      <c r="B301">
+        <v>1996</v>
+      </c>
+      <c r="D301" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="302" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A302" t="s">
+        <v>603</v>
+      </c>
+      <c r="B302">
+        <v>2021</v>
+      </c>
+      <c r="D302" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="303" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A303" t="s">
+        <v>605</v>
+      </c>
+      <c r="B303">
+        <v>1957</v>
+      </c>
+      <c r="D303" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="304" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A304" t="s">
+        <v>607</v>
+      </c>
+      <c r="B304">
+        <v>2014</v>
+      </c>
+      <c r="D304" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="305" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A305" t="s">
+        <v>609</v>
+      </c>
+      <c r="B305">
+        <v>1981</v>
+      </c>
+      <c r="D305" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="306" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A306" t="s">
+        <v>611</v>
+      </c>
+      <c r="B306">
+        <v>1960</v>
+      </c>
+      <c r="D306" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="307" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A307" t="s">
+        <v>613</v>
+      </c>
+      <c r="B307">
+        <v>2017</v>
+      </c>
+      <c r="D307" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="308" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A308" t="s">
+        <v>615</v>
+      </c>
+      <c r="B308">
+        <v>2008</v>
+      </c>
+      <c r="D308" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="309" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A309" t="s">
+        <v>617</v>
+      </c>
+      <c r="B309">
+        <v>2001</v>
+      </c>
+      <c r="D309" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="310" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A310" t="s">
+        <v>619</v>
+      </c>
+      <c r="B310">
+        <v>1937</v>
+      </c>
+      <c r="D310" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="311" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A311" t="s">
+        <v>621</v>
+      </c>
+      <c r="B311">
+        <v>1996</v>
+      </c>
+      <c r="D311" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="312" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A312" t="s">
+        <v>623</v>
+      </c>
+      <c r="B312">
+        <v>1994</v>
+      </c>
+      <c r="D312" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="313" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A313" t="s">
+        <v>625</v>
+      </c>
+      <c r="B313">
+        <v>1964</v>
+      </c>
+      <c r="D313" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="314" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A314" t="s">
+        <v>627</v>
+      </c>
+      <c r="B314">
+        <v>1974</v>
+      </c>
+      <c r="D314" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="315" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A315" t="s">
+        <v>629</v>
+      </c>
+      <c r="B315">
+        <v>1950</v>
+      </c>
+      <c r="D315" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="316" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A316" t="s">
+        <v>631</v>
+      </c>
+      <c r="B316">
+        <v>1962</v>
+      </c>
+      <c r="D316" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="317" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A317" t="s">
+        <v>633</v>
+      </c>
+      <c r="B317">
+        <v>1997</v>
+      </c>
+      <c r="D317" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="318" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A318" t="s">
+        <v>635</v>
+      </c>
+      <c r="B318">
+        <v>1972</v>
+      </c>
+      <c r="D318" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="319" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A319" t="s">
+        <v>637</v>
+      </c>
+      <c r="B319">
+        <v>1957</v>
+      </c>
+      <c r="D319" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="320" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A320" t="s">
+        <v>639</v>
+      </c>
+      <c r="B320">
+        <v>2007</v>
+      </c>
+      <c r="D320" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="321" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A321" t="s">
+        <v>641</v>
+      </c>
+      <c r="B321">
+        <v>1921</v>
+      </c>
+      <c r="D321" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="322" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A322" t="s">
+        <v>643</v>
+      </c>
+      <c r="B322">
+        <v>1997</v>
+      </c>
+      <c r="D322" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="323" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A323" t="s">
+        <v>645</v>
+      </c>
+      <c r="B323">
+        <v>1959</v>
+      </c>
+      <c r="D323" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="324" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A324" t="s">
+        <v>647</v>
+      </c>
+      <c r="B324">
+        <v>1950</v>
+      </c>
+      <c r="D324" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="325" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A325" t="s">
+        <v>649</v>
+      </c>
+      <c r="B325">
+        <v>2017</v>
+      </c>
+      <c r="D325" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="326" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A326" t="s">
+        <v>651</v>
+      </c>
+      <c r="B326">
+        <v>1950</v>
+      </c>
+      <c r="D326" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="327" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A327" t="s">
+        <v>653</v>
+      </c>
+      <c r="B327">
+        <v>2004</v>
+      </c>
+      <c r="D327" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="328" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A328" t="s">
+        <v>655</v>
+      </c>
+      <c r="B328">
+        <v>1926</v>
+      </c>
+      <c r="D328" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="329" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A329" t="s">
+        <v>657</v>
+      </c>
+      <c r="B329">
+        <v>1962</v>
+      </c>
+      <c r="D329" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="330" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A330" t="s">
+        <v>659</v>
+      </c>
+      <c r="B330">
+        <v>1943</v>
+      </c>
+      <c r="D330" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="331" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A331" t="s">
+        <v>661</v>
+      </c>
+      <c r="B331">
+        <v>1988</v>
+      </c>
+      <c r="D331" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="332" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A332" t="s">
+        <v>663</v>
+      </c>
+      <c r="B332">
+        <v>2016</v>
+      </c>
+      <c r="D332" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="333" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A333" t="s">
+        <v>665</v>
+      </c>
+      <c r="B333">
+        <v>2010</v>
+      </c>
+      <c r="D333" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="334" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A334" t="s">
+        <v>667</v>
+      </c>
+      <c r="B334">
+        <v>2019</v>
+      </c>
+      <c r="D334" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="335" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A335" t="s">
+        <v>669</v>
+      </c>
+      <c r="B335">
+        <v>2009</v>
+      </c>
+      <c r="D335" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="336" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A336" t="s">
+        <v>671</v>
+      </c>
+      <c r="B336">
+        <v>1940</v>
+      </c>
+      <c r="D336" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="337" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A337" t="s">
+        <v>673</v>
+      </c>
+      <c r="B337">
+        <v>1962</v>
+      </c>
+      <c r="D337" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="338" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A338" t="s">
+        <v>675</v>
+      </c>
+      <c r="B338">
+        <v>1986</v>
+      </c>
+      <c r="D338" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="339" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A339" t="s">
+        <v>677</v>
+      </c>
+      <c r="B339">
+        <v>1927</v>
+      </c>
+      <c r="D339" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="340" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A340" t="s">
+        <v>679</v>
+      </c>
+      <c r="B340">
+        <v>1974</v>
+      </c>
+      <c r="D340" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="341" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A341" t="s">
+        <v>681</v>
+      </c>
+      <c r="B341">
+        <v>1962</v>
+      </c>
+      <c r="D341" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="342" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A342" t="s">
+        <v>683</v>
+      </c>
+      <c r="B342">
+        <v>2012</v>
+      </c>
+      <c r="D342" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="343" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A343" t="s">
+        <v>685</v>
+      </c>
+      <c r="B343">
+        <v>1960</v>
+      </c>
+      <c r="D343" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="344" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A344" t="s">
+        <v>687</v>
+      </c>
+      <c r="B344">
+        <v>1999</v>
+      </c>
+      <c r="D344" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="345" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A345" t="s">
+        <v>689</v>
+      </c>
+      <c r="B345">
+        <v>1973</v>
+      </c>
+      <c r="D345" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="346" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A346" t="s">
+        <v>691</v>
+      </c>
+      <c r="B346">
+        <v>1986</v>
+      </c>
+      <c r="D346" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="347" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A347" t="s">
+        <v>693</v>
+      </c>
+      <c r="B347">
+        <v>2013</v>
+      </c>
+      <c r="D347" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="348" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A348" t="s">
+        <v>695</v>
+      </c>
+      <c r="B348">
+        <v>1995</v>
+      </c>
+      <c r="D348" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="349" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A349" t="s">
+        <v>697</v>
+      </c>
+      <c r="B349">
+        <v>2024</v>
+      </c>
+      <c r="D349" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="350" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A350" t="s">
+        <v>699</v>
+      </c>
+      <c r="B350">
+        <v>1961</v>
+      </c>
+      <c r="D350" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="351" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A351" t="s">
+        <v>701</v>
+      </c>
+      <c r="B351">
+        <v>1959</v>
+      </c>
+      <c r="D351" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="352" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A352" t="s">
+        <v>703</v>
+      </c>
+      <c r="B352">
+        <v>1960</v>
+      </c>
+      <c r="D352" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="353" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A353" t="s">
+        <v>705</v>
+      </c>
+      <c r="B353">
+        <v>1983</v>
+      </c>
+      <c r="D353" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="354" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A354" t="s">
+        <v>707</v>
+      </c>
+      <c r="B354">
+        <v>1993</v>
+      </c>
+      <c r="D354" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="355" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A355" t="s">
+        <v>709</v>
+      </c>
+      <c r="B355">
+        <v>2018</v>
+      </c>
+      <c r="D355" t="s">
+        <v>710</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Official Whitelist.xlsx
+++ b/Official Whitelist.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bigba\aa Personal Projects\Letterboxd-List-Scraping\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E020EF68-3684-42A3-BD5D-4C59ABB3A091}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CB09E4E-20A8-4260-8B6D-DEBD217B0567}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="711" uniqueCount="711">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="751" uniqueCount="751">
   <si>
     <t>Title</t>
   </si>
@@ -2158,6 +2158,126 @@
   </si>
   <si>
     <t>https://letterboxd.com/film/the-wolf-house/</t>
+  </si>
+  <si>
+    <t>The Ox Bow Incident</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-ox-bow-incident/</t>
+  </si>
+  <si>
+    <t>Mustang</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/mustang-2015/</t>
+  </si>
+  <si>
+    <t>Fargo</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/fargo/</t>
+  </si>
+  <si>
+    <t>Punishment Park</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/punishment-park/</t>
+  </si>
+  <si>
+    <t>The Gold Rush</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-gold-rush/</t>
+  </si>
+  <si>
+    <t>Mulan</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/mulan/</t>
+  </si>
+  <si>
+    <t>Il Posto</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/il-posto/</t>
+  </si>
+  <si>
+    <t>Dead Mans Letters</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/dead-mans-letters/</t>
+  </si>
+  <si>
+    <t>Sanjuro</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/sanjuro/</t>
+  </si>
+  <si>
+    <t>Monty Python And The Holy Grail</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/monty-python-and-the-holy-grail/</t>
+  </si>
+  <si>
+    <t>Pink Floyd The Wall</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/pink-floyd-the-wall/</t>
+  </si>
+  <si>
+    <t>The Umbrellas Of Cherbourg</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-umbrellas-of-cherbourg/</t>
+  </si>
+  <si>
+    <t>Crayon Shin Chan The Adult Empire Strikes</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/crayon-shin-chan-the-adult-empire-strikes/</t>
+  </si>
+  <si>
+    <t>Reservoir Dogs</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/reservoir-dogs/</t>
+  </si>
+  <si>
+    <t>Rope</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/rope/</t>
+  </si>
+  <si>
+    <t>Souleymane's Story</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/souleymanes-story/</t>
+  </si>
+  <si>
+    <t>Ballad of a Soldier</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/ballad-of-a-soldier/</t>
+  </si>
+  <si>
+    <t>Happiness 1965</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/happiness-1965/</t>
+  </si>
+  <si>
+    <t>The Color of Pomegranates</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-color-of-pomegranates/</t>
+  </si>
+  <si>
+    <t>Rap World</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/rap-world/</t>
   </si>
 </sst>
 </file>
@@ -2498,7 +2618,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D355"/>
+  <dimension ref="A1:D375"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="46.36328125" bestFit="1" customWidth="1"/>
@@ -6415,6 +6535,226 @@
         <v>710</v>
       </c>
     </row>
+    <row r="356" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A356" t="s">
+        <v>711</v>
+      </c>
+      <c r="B356">
+        <v>1943</v>
+      </c>
+      <c r="D356" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="357" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A357" t="s">
+        <v>713</v>
+      </c>
+      <c r="B357">
+        <v>2015</v>
+      </c>
+      <c r="D357" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="358" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A358" t="s">
+        <v>715</v>
+      </c>
+      <c r="B358">
+        <v>1996</v>
+      </c>
+      <c r="D358" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="359" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A359" t="s">
+        <v>717</v>
+      </c>
+      <c r="B359">
+        <v>1971</v>
+      </c>
+      <c r="D359" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="360" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A360" t="s">
+        <v>719</v>
+      </c>
+      <c r="B360">
+        <v>1925</v>
+      </c>
+      <c r="D360" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="361" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A361" t="s">
+        <v>721</v>
+      </c>
+      <c r="B361">
+        <v>1998</v>
+      </c>
+      <c r="D361" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="362" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A362" t="s">
+        <v>723</v>
+      </c>
+      <c r="B362">
+        <v>1961</v>
+      </c>
+      <c r="D362" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="363" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A363" t="s">
+        <v>725</v>
+      </c>
+      <c r="B363">
+        <v>1986</v>
+      </c>
+      <c r="D363" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="364" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A364" t="s">
+        <v>727</v>
+      </c>
+      <c r="B364">
+        <v>1962</v>
+      </c>
+      <c r="D364" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="365" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A365" t="s">
+        <v>729</v>
+      </c>
+      <c r="B365">
+        <v>1975</v>
+      </c>
+      <c r="D365" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="366" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A366" t="s">
+        <v>731</v>
+      </c>
+      <c r="B366">
+        <v>1982</v>
+      </c>
+      <c r="D366" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="367" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A367" t="s">
+        <v>733</v>
+      </c>
+      <c r="B367">
+        <v>1964</v>
+      </c>
+      <c r="D367" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="368" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A368" t="s">
+        <v>735</v>
+      </c>
+      <c r="B368">
+        <v>2001</v>
+      </c>
+      <c r="D368" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="369" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A369" t="s">
+        <v>737</v>
+      </c>
+      <c r="B369">
+        <v>1992</v>
+      </c>
+      <c r="D369" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="370" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A370" t="s">
+        <v>739</v>
+      </c>
+      <c r="B370">
+        <v>1948</v>
+      </c>
+      <c r="D370" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="371" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A371" t="s">
+        <v>741</v>
+      </c>
+      <c r="B371">
+        <v>2024</v>
+      </c>
+      <c r="D371" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="372" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A372" t="s">
+        <v>743</v>
+      </c>
+      <c r="B372">
+        <v>1959</v>
+      </c>
+      <c r="D372" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="373" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A373" t="s">
+        <v>745</v>
+      </c>
+      <c r="B373">
+        <v>1965</v>
+      </c>
+      <c r="D373" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="374" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A374" t="s">
+        <v>747</v>
+      </c>
+      <c r="B374">
+        <v>1969</v>
+      </c>
+      <c r="D374" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="375" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A375" t="s">
+        <v>749</v>
+      </c>
+      <c r="B375">
+        <v>2024</v>
+      </c>
+      <c r="D375" t="s">
+        <v>750</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Official Whitelist.xlsx
+++ b/Official Whitelist.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bigba\aa Personal Projects\Letterboxd-List-Scraping\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CB09E4E-20A8-4260-8B6D-DEBD217B0567}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A9F3783-45F1-476F-9FFE-ACA917C05B74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="751" uniqueCount="751">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1055" uniqueCount="1054">
   <si>
     <t>Title</t>
   </si>
@@ -2278,13 +2278,922 @@
   </si>
   <si>
     <t>https://letterboxd.com/film/rap-world/</t>
+  </si>
+  <si>
+    <t>Center Stage</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/center-stage-1991/</t>
+  </si>
+  <si>
+    <t>Kandukondain Kandukondain</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/kandukondain-kandukondain/</t>
+  </si>
+  <si>
+    <t>An Angel At My Table</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/an-angel-at-my-table/</t>
+  </si>
+  <si>
+    <t>Gone With The Wind</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/gone-with-the-wind/</t>
+  </si>
+  <si>
+    <t>Topsy Turvy</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/topsy-turvy/</t>
+  </si>
+  <si>
+    <t>Barfi</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/barfi/</t>
+  </si>
+  <si>
+    <t>Empire Of The Sun</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/empire-of-the-sun/</t>
+  </si>
+  <si>
+    <t>West Side Story</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/west-side-story/</t>
+  </si>
+  <si>
+    <t>How To Train Your Dragon</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/how-to-train-your-dragon/</t>
+  </si>
+  <si>
+    <t>Phantom Of The Paradise</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/phantom-of-the-paradise/</t>
+  </si>
+  <si>
+    <t>Street Of Shame</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/street-of-shame/</t>
+  </si>
+  <si>
+    <t>Kaguya Sama Love Is War The First Kiss That Never Ends</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/kaguya-sama-love-is-war-the-first-kiss-that-never-ends/</t>
+  </si>
+  <si>
+    <t>Project Hail Mary</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/project-hail-mary/</t>
+  </si>
+  <si>
+    <t>The Cameraman</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-cameraman/</t>
+  </si>
+  <si>
+    <t>A Short Film About Killing</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/a-short-film-about-killing/</t>
+  </si>
+  <si>
+    <t>Sonatine</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/sonatine/</t>
+  </si>
+  <si>
+    <t>After Hours</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/after-hours/</t>
+  </si>
+  <si>
+    <t>Beau Travail</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/beau-travail/</t>
+  </si>
+  <si>
+    <t>Kanal 1957</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/kanal-1957/</t>
+  </si>
+  <si>
+    <t>Shrek</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/shrek/</t>
+  </si>
+  <si>
+    <t>The Innocents</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-innocents/</t>
+  </si>
+  <si>
+    <t>Ponyo</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/ponyo/</t>
+  </si>
+  <si>
+    <t>What We Do In The Shadows</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/what-we-do-in-the-shadows/</t>
+  </si>
+  <si>
+    <t>Trouble In Paradise</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/trouble-in-paradise/</t>
+  </si>
+  <si>
+    <t>Shrek 2</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/shrek-2/</t>
+  </si>
+  <si>
+    <t>Monicas Gang In An Adventure In Time</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/monicas-gang-in-an-adventure-in-time/</t>
+  </si>
+  <si>
+    <t>Safety Last</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/safety-last/</t>
+  </si>
+  <si>
+    <t>Harold And Maude</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/harold-and-maude/</t>
+  </si>
+  <si>
+    <t>Whats Up Doc 1972</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/whats-up-doc-1972/</t>
+  </si>
+  <si>
+    <t>A Short Film About Love</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/a-short-film-about-love/</t>
+  </si>
+  <si>
+    <t>Women On The Verge Of A Nervous Breakdown</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/women-on-the-verge-of-a-nervous-breakdown/</t>
+  </si>
+  <si>
+    <t>Toy Story</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/toy-story/</t>
+  </si>
+  <si>
+    <t>Out Of The Past</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/out-of-the-past/</t>
+  </si>
+  <si>
+    <t>My Darling Clementine</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/my-darling-clementine/</t>
+  </si>
+  <si>
+    <t>Lady Snowblood</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/lady-snowblood/</t>
+  </si>
+  <si>
+    <t>Aguirre The Wrath Of God</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/aguirre-the-wrath-of-god/</t>
+  </si>
+  <si>
+    <t>I Am a Fugitive from a Chain Gang</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/i-am-a-fugitive-from-a-chain-gang/</t>
+  </si>
+  <si>
+    <t>The Big Heat</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-big-heat/</t>
+  </si>
+  <si>
+    <t>3 Iron</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/3-iron/</t>
+  </si>
+  <si>
+    <t>Last Year At Marienbad</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/last-year-at-marienbad/</t>
+  </si>
+  <si>
+    <t>The Double Life of VÃ©ronique</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-double-life-of-veronique/</t>
+  </si>
+  <si>
+    <t>Up</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/up/</t>
+  </si>
+  <si>
+    <t>Tangerines</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/tangerines/</t>
+  </si>
+  <si>
+    <t>His Motorbike, Her Island</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/his-motorbike-her-island/</t>
+  </si>
+  <si>
+    <t>Petite Maman</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/petite-maman/</t>
+  </si>
+  <si>
+    <t>Elevator To The Gallows</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/elevator-to-the-gallows/</t>
+  </si>
+  <si>
+    <t>The Princess Bride</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-princess-bride/</t>
+  </si>
+  <si>
+    <t>Paprika 2006</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/paprika-2006/</t>
+  </si>
+  <si>
+    <t>Angels Egg</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/angels-egg/</t>
+  </si>
+  <si>
+    <t>Viridiana</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/viridiana/</t>
+  </si>
+  <si>
+    <t>Days Of Heaven</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/days-of-heaven/</t>
+  </si>
+  <si>
+    <t>Oslo, August 31st</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/oslo-august-31st/</t>
+  </si>
+  <si>
+    <t>Dou Kyu Sei Classmates</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/dou-kyu-sei-classmates/</t>
+  </si>
+  <si>
+    <t>Ghost In The Shell</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/ghost-in-the-shell/</t>
+  </si>
+  <si>
+    <t>The Crowd</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-crowd/</t>
+  </si>
+  <si>
+    <t>The Quiet Girl</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-quiet-girl/</t>
+  </si>
+  <si>
+    <t>The Breadwinner</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-breadwinner/</t>
+  </si>
+  <si>
+    <t>Whos Singin Over There</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/whos-singin-over-there/</t>
+  </si>
+  <si>
+    <t>Flow 2024</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/flow-2024/</t>
+  </si>
+  <si>
+    <t>Letter From An Unknown Woman</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/letter-from-an-unknown-woman/</t>
+  </si>
+  <si>
+    <t>Sidewalls</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/sidewalls/</t>
+  </si>
+  <si>
+    <t>Forbidden Games 1952</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/forbidden-games-1952/</t>
+  </si>
+  <si>
+    <t>Little Amelie Or The Character Of Rain</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/little-amelie-or-the-character-of-rain/</t>
+  </si>
+  <si>
+    <t>Orpheus</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/orpheus/</t>
+  </si>
+  <si>
+    <t>Black Girl</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/black-girl-1966/</t>
+  </si>
+  <si>
+    <t>Nothing But A Man</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/nothing-but-a-man/</t>
+  </si>
+  <si>
+    <t>Beauty And The Beast</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/beauty-and-the-beast/</t>
+  </si>
+  <si>
+    <t>Blindspotting</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/blindspotting/</t>
+  </si>
+  <si>
+    <t>Letter Never Sent</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/letter-never-sent/</t>
+  </si>
+  <si>
+    <t>Monsters Inc</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/monsters-inc/</t>
+  </si>
+  <si>
+    <t>Au Hasard Balthazar</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/au-hasard-balthazar/</t>
+  </si>
+  <si>
+    <t>True Stories</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/true-stories/</t>
+  </si>
+  <si>
+    <t>The War Game</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-war-game/</t>
+  </si>
+  <si>
+    <t>Hedwig And The Angry Inch</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/hedwig-and-the-angry-inch/</t>
+  </si>
+  <si>
+    <t>Ratcatcher</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/ratcatcher/</t>
+  </si>
+  <si>
+    <t>Three Men And A Leg</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/three-men-and-a-leg/</t>
+  </si>
+  <si>
+    <t>The Prince Of Egypt</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-prince-of-egypt/</t>
+  </si>
+  <si>
+    <t>Eternity</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/eternity-2017/</t>
+  </si>
+  <si>
+    <t>Shoeshine</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/shoeshine/</t>
+  </si>
+  <si>
+    <t>One Piece Baron Omatsuri And The Secret Island</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/one-piece-baron-omatsuri-and-the-secret-island/</t>
+  </si>
+  <si>
+    <t>The Music Room</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-music-room/</t>
+  </si>
+  <si>
+    <t>Kuroneko</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/kuroneko/</t>
+  </si>
+  <si>
+    <t>The Summit Of The Gods</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-summit-of-the-gods/</t>
+  </si>
+  <si>
+    <t>Given The Movie To The Sea</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/given-the-movie-to-the-sea/</t>
+  </si>
+  <si>
+    <t>All That Heaven Allows</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/all-that-heaven-allows/</t>
+  </si>
+  <si>
+    <t>When Harry Met Sally</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/when-harry-met-sally/</t>
+  </si>
+  <si>
+    <t>Songs From The Second Floor</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/songs-from-the-second-floor/</t>
+  </si>
+  <si>
+    <t>The Circus</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-circus/</t>
+  </si>
+  <si>
+    <t>Lilo Stitch</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/lilo-stitch/</t>
+  </si>
+  <si>
+    <t>Shadows of Forgotten Ancestors</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/shadows-of-forgotten-ancestors/</t>
+  </si>
+  <si>
+    <t>Boy</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/boy-2010/</t>
+  </si>
+  <si>
+    <t>Kizumonogatari Part 2: Nekketsu</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/kizumonogatari-part-2-nekketsu/</t>
+  </si>
+  <si>
+    <t>The Cabinet Of Dr Caligari 1920</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-cabinet-of-dr-caligari-1920/</t>
+  </si>
+  <si>
+    <t>The Muppet Christmas Carol</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-muppet-christmas-carol/</t>
+  </si>
+  <si>
+    <t>The Watermelon Woman</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-watermelon-woman/</t>
+  </si>
+  <si>
+    <t>Godzilla</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/godzilla/</t>
+  </si>
+  <si>
+    <t>The Farewell 2019</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-farewell-2019/</t>
+  </si>
+  <si>
+    <t>The Fabulous Baron Munchausen</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-fabulous-baron-munchausen/</t>
+  </si>
+  <si>
+    <t>One Cut Of The Dead</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/one-cut-of-the-dead/</t>
+  </si>
+  <si>
+    <t>Mouchette</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/mouchette/</t>
+  </si>
+  <si>
+    <t>10 Things I Hate About You</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/10-things-i-hate-about-you/</t>
+  </si>
+  <si>
+    <t>The Muppet Movie</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-muppet-movie/</t>
+  </si>
+  <si>
+    <t>The Wind</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-wind/</t>
+  </si>
+  <si>
+    <t>Kisapmata</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/kisapmata/</t>
+  </si>
+  <si>
+    <t>The Last Laugh</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-last-laugh/</t>
+  </si>
+  <si>
+    <t>Cold War 2018</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/cold-war-2018/</t>
+  </si>
+  <si>
+    <t>The Rocky Horror Picture Show</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-rocky-horror-picture-show/</t>
+  </si>
+  <si>
+    <t>Mononoke The Movie Chapter Ii The Ashes Of</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/mononoke-the-movie-chapter-ii-the-ashes-of/</t>
+  </si>
+  <si>
+    <t>Batman Mask Of The Phantasm</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/batman-mask-of-the-phantasm/</t>
+  </si>
+  <si>
+    <t>Four Adventures Of Reinette And Mirabelle</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/four-adventures-of-reinette-and-mirabelle/</t>
+  </si>
+  <si>
+    <t>Ivan the Terrible, Part II: The Boyars' Plot</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/ivan-the-terrible-part-ii-the-boyars-plot/</t>
+  </si>
+  <si>
+    <t>Ida</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/ida/</t>
+  </si>
+  <si>
+    <t>Insiang</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/insiang/</t>
+  </si>
+  <si>
+    <t>Lovers Rock 2020</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/lovers-rock-2020/</t>
+  </si>
+  <si>
+    <t>Laura</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/laura/</t>
+  </si>
+  <si>
+    <t>Young Hearts</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/young-hearts-2024/</t>
+  </si>
+  <si>
+    <t>The King And The Mockingbird</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-king-and-the-mockingbird/</t>
+  </si>
+  <si>
+    <t>Devi</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/devi/</t>
+  </si>
+  <si>
+    <t>Pariah</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/pariah/</t>
+  </si>
+  <si>
+    <t>The Swimmer</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-swimmer/</t>
+  </si>
+  <si>
+    <t>Day Of The Wacko</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/day-of-the-wacko/</t>
+  </si>
+  <si>
+    <t>I Daniel Blake</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/i-daniel-blake/</t>
+  </si>
+  <si>
+    <t>Tangled</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/tangled-2010/</t>
+  </si>
+  <si>
+    <t>The 8 Diagram Pole Fighter</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-8-diagram-pole-fighter/</t>
+  </si>
+  <si>
+    <t>Superstar The Karen Carpenter Story</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/superstar-the-karen-carpenter-story/</t>
+  </si>
+  <si>
+    <t>Night And The City</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/night-and-the-city/</t>
+  </si>
+  <si>
+    <t>U.S. Go Home</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/us-go-home/</t>
+  </si>
+  <si>
+    <t>Farha</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/farha/</t>
+  </si>
+  <si>
+    <t>My Little Pony Equestria Girls Rainbow Rocks</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/my-little-pony-equestria-girls-rainbow-rocks/</t>
+  </si>
+  <si>
+    <t>Buddies</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/buddies-1985/</t>
+  </si>
+  <si>
+    <t>The Boys</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-boys/</t>
+  </si>
+  <si>
+    <t>Maronas Fantastic Tale</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/maronas-fantastic-tale/</t>
+  </si>
+  <si>
+    <t>Land Of Mine</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/land-of-mine/</t>
+  </si>
+  <si>
+    <t>Black Dynamite</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/black-dynamite/</t>
+  </si>
+  <si>
+    <t>Frances Ha</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/frances-ha/</t>
+  </si>
+  <si>
+    <t>His Girl Friday</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/his-girl-friday/</t>
+  </si>
+  <si>
+    <t>The Chorus</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-chorus/</t>
+  </si>
+  <si>
+    <t>Pale Flower</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/pale-flower/</t>
+  </si>
+  <si>
+    <t>Saving Face</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/saving-face/</t>
+  </si>
+  <si>
+    <t>Sunshine</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/sunshine-2024/</t>
+  </si>
+  <si>
+    <t>Love in the Afternoon</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/love-in-the-afternoon-1972/</t>
+  </si>
+  <si>
+    <t>Porco Rosso</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/porco-rosso/</t>
+  </si>
+  <si>
+    <t>A Town Called Panic</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/a-town-called-panic/</t>
+  </si>
+  <si>
+    <t>Balkan Spy</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/balkan-spy/</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/babylon/</t>
+  </si>
+  <si>
+    <t>Finding Nemo</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/finding-nemo/</t>
+  </si>
+  <si>
+    <t>Hunger</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/hunger/</t>
+  </si>
+  <si>
+    <t>The Triplets Of Belleville</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-triplets-of-belleville/</t>
+  </si>
+  <si>
+    <t>Kirikou And The Sorceress</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/kirikou-and-the-sorceress/</t>
+  </si>
+  <si>
+    <t>Moonrise Kingdom</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/moonrise-kingdom/</t>
+  </si>
+  <si>
+    <t>Police Story</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/police-story/</t>
+  </si>
+  <si>
+    <t>Steamboat Bill Jr</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/steamboat-bill-jr/</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2296,6 +3205,14 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -2330,16 +3247,19 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -2618,7 +3538,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D375"/>
+  <dimension ref="A1:D527"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="46.36328125" bestFit="1" customWidth="1"/>
@@ -6755,7 +7675,1692 @@
         <v>750</v>
       </c>
     </row>
+    <row r="376" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A376" t="s">
+        <v>751</v>
+      </c>
+      <c r="B376">
+        <v>1991</v>
+      </c>
+      <c r="D376" s="2" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="377" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A377" t="s">
+        <v>753</v>
+      </c>
+      <c r="B377">
+        <v>2000</v>
+      </c>
+      <c r="D377" s="2" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="378" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A378" t="s">
+        <v>755</v>
+      </c>
+      <c r="B378">
+        <v>1990</v>
+      </c>
+      <c r="D378" s="2" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="379" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A379" t="s">
+        <v>757</v>
+      </c>
+      <c r="B379">
+        <v>1939</v>
+      </c>
+      <c r="D379" s="2" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="380" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A380" t="s">
+        <v>759</v>
+      </c>
+      <c r="B380">
+        <v>1999</v>
+      </c>
+      <c r="D380" s="2" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="381" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A381" t="s">
+        <v>761</v>
+      </c>
+      <c r="B381">
+        <v>2012</v>
+      </c>
+      <c r="D381" s="2" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="382" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A382" t="s">
+        <v>763</v>
+      </c>
+      <c r="B382">
+        <v>1987</v>
+      </c>
+      <c r="D382" s="2" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="383" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A383" t="s">
+        <v>765</v>
+      </c>
+      <c r="B383">
+        <v>1961</v>
+      </c>
+      <c r="D383" s="2" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="384" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A384" t="s">
+        <v>767</v>
+      </c>
+      <c r="B384">
+        <v>2010</v>
+      </c>
+      <c r="D384" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="385" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A385" t="s">
+        <v>769</v>
+      </c>
+      <c r="B385">
+        <v>1974</v>
+      </c>
+      <c r="D385" s="2" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="386" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A386" t="s">
+        <v>771</v>
+      </c>
+      <c r="B386">
+        <v>1956</v>
+      </c>
+      <c r="D386" s="2" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="387" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A387" t="s">
+        <v>773</v>
+      </c>
+      <c r="B387">
+        <v>2022</v>
+      </c>
+      <c r="D387" s="2" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="388" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A388" t="s">
+        <v>775</v>
+      </c>
+      <c r="B388">
+        <v>2026</v>
+      </c>
+      <c r="D388" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="389" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A389" t="s">
+        <v>777</v>
+      </c>
+      <c r="B389">
+        <v>1928</v>
+      </c>
+      <c r="D389" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="390" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A390" t="s">
+        <v>779</v>
+      </c>
+      <c r="B390">
+        <v>1988</v>
+      </c>
+      <c r="D390" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="391" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A391" t="s">
+        <v>781</v>
+      </c>
+      <c r="B391">
+        <v>1993</v>
+      </c>
+      <c r="D391" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="392" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A392" t="s">
+        <v>783</v>
+      </c>
+      <c r="B392">
+        <v>1985</v>
+      </c>
+      <c r="D392" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="393" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A393" t="s">
+        <v>785</v>
+      </c>
+      <c r="B393">
+        <v>1999</v>
+      </c>
+      <c r="D393" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="394" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A394" t="s">
+        <v>787</v>
+      </c>
+      <c r="B394">
+        <v>1957</v>
+      </c>
+      <c r="D394" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="395" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A395" t="s">
+        <v>789</v>
+      </c>
+      <c r="B395">
+        <v>2001</v>
+      </c>
+      <c r="D395" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="396" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A396" t="s">
+        <v>791</v>
+      </c>
+      <c r="B396">
+        <v>1961</v>
+      </c>
+      <c r="D396" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="397" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A397" t="s">
+        <v>793</v>
+      </c>
+      <c r="B397">
+        <v>2008</v>
+      </c>
+      <c r="D397" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="398" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A398" t="s">
+        <v>795</v>
+      </c>
+      <c r="B398">
+        <v>2014</v>
+      </c>
+      <c r="D398" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="399" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A399" t="s">
+        <v>797</v>
+      </c>
+      <c r="B399">
+        <v>1932</v>
+      </c>
+      <c r="D399" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="400" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A400" t="s">
+        <v>799</v>
+      </c>
+      <c r="B400">
+        <v>2004</v>
+      </c>
+      <c r="D400" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="401" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A401" t="s">
+        <v>801</v>
+      </c>
+      <c r="B401">
+        <v>2007</v>
+      </c>
+      <c r="D401" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="402" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A402" t="s">
+        <v>803</v>
+      </c>
+      <c r="B402">
+        <v>1923</v>
+      </c>
+      <c r="D402" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="403" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A403" t="s">
+        <v>805</v>
+      </c>
+      <c r="B403">
+        <v>1971</v>
+      </c>
+      <c r="D403" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="404" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A404" t="s">
+        <v>807</v>
+      </c>
+      <c r="B404">
+        <v>1972</v>
+      </c>
+      <c r="D404" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="405" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A405" t="s">
+        <v>809</v>
+      </c>
+      <c r="B405">
+        <v>1988</v>
+      </c>
+      <c r="D405" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="406" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A406" t="s">
+        <v>811</v>
+      </c>
+      <c r="B406">
+        <v>1988</v>
+      </c>
+      <c r="D406" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="407" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A407" t="s">
+        <v>813</v>
+      </c>
+      <c r="B407">
+        <v>1995</v>
+      </c>
+      <c r="D407" t="s">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="408" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A408" t="s">
+        <v>815</v>
+      </c>
+      <c r="B408">
+        <v>1947</v>
+      </c>
+      <c r="D408" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="409" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A409" t="s">
+        <v>817</v>
+      </c>
+      <c r="B409">
+        <v>1946</v>
+      </c>
+      <c r="D409" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="410" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A410" t="s">
+        <v>819</v>
+      </c>
+      <c r="B410">
+        <v>1973</v>
+      </c>
+      <c r="D410" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="411" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A411" t="s">
+        <v>821</v>
+      </c>
+      <c r="B411">
+        <v>1972</v>
+      </c>
+      <c r="D411" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="412" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A412" t="s">
+        <v>823</v>
+      </c>
+      <c r="B412">
+        <v>1932</v>
+      </c>
+      <c r="D412" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="413" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A413" t="s">
+        <v>825</v>
+      </c>
+      <c r="B413">
+        <v>1953</v>
+      </c>
+      <c r="D413" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="414" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A414" t="s">
+        <v>827</v>
+      </c>
+      <c r="B414">
+        <v>2004</v>
+      </c>
+      <c r="D414" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="415" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A415" t="s">
+        <v>829</v>
+      </c>
+      <c r="B415">
+        <v>1961</v>
+      </c>
+      <c r="D415" t="s">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="416" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A416" t="s">
+        <v>831</v>
+      </c>
+      <c r="B416">
+        <v>1991</v>
+      </c>
+      <c r="D416" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="417" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A417" t="s">
+        <v>833</v>
+      </c>
+      <c r="B417">
+        <v>2009</v>
+      </c>
+      <c r="D417" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="418" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A418" t="s">
+        <v>835</v>
+      </c>
+      <c r="B418">
+        <v>2013</v>
+      </c>
+      <c r="D418" t="s">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="419" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A419" t="s">
+        <v>837</v>
+      </c>
+      <c r="B419">
+        <v>1986</v>
+      </c>
+      <c r="D419" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="420" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A420" t="s">
+        <v>839</v>
+      </c>
+      <c r="B420">
+        <v>2021</v>
+      </c>
+      <c r="D420" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="421" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A421" t="s">
+        <v>841</v>
+      </c>
+      <c r="B421">
+        <v>1958</v>
+      </c>
+      <c r="D421" t="s">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="422" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A422" t="s">
+        <v>843</v>
+      </c>
+      <c r="B422">
+        <v>1987</v>
+      </c>
+      <c r="D422" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="423" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A423" t="s">
+        <v>845</v>
+      </c>
+      <c r="B423">
+        <v>2006</v>
+      </c>
+      <c r="D423" t="s">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="424" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A424" t="s">
+        <v>847</v>
+      </c>
+      <c r="B424">
+        <v>1985</v>
+      </c>
+      <c r="D424" t="s">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="425" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A425" t="s">
+        <v>849</v>
+      </c>
+      <c r="B425">
+        <v>1961</v>
+      </c>
+      <c r="D425" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="426" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A426" t="s">
+        <v>851</v>
+      </c>
+      <c r="B426">
+        <v>1978</v>
+      </c>
+      <c r="D426" t="s">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="427" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A427" t="s">
+        <v>853</v>
+      </c>
+      <c r="B427">
+        <v>2011</v>
+      </c>
+      <c r="D427" t="s">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="428" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A428" t="s">
+        <v>855</v>
+      </c>
+      <c r="B428">
+        <v>2016</v>
+      </c>
+      <c r="D428" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="429" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A429" t="s">
+        <v>857</v>
+      </c>
+      <c r="B429">
+        <v>1995</v>
+      </c>
+      <c r="D429" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="430" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A430" t="s">
+        <v>859</v>
+      </c>
+      <c r="B430">
+        <v>1928</v>
+      </c>
+      <c r="D430" t="s">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="431" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A431" t="s">
+        <v>861</v>
+      </c>
+      <c r="B431">
+        <v>2022</v>
+      </c>
+      <c r="D431" t="s">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="432" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A432" t="s">
+        <v>863</v>
+      </c>
+      <c r="B432">
+        <v>2017</v>
+      </c>
+      <c r="D432" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="433" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A433" t="s">
+        <v>865</v>
+      </c>
+      <c r="B433">
+        <v>1980</v>
+      </c>
+      <c r="D433" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="434" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A434" t="s">
+        <v>867</v>
+      </c>
+      <c r="B434">
+        <v>2024</v>
+      </c>
+      <c r="D434" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="435" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A435" t="s">
+        <v>869</v>
+      </c>
+      <c r="B435">
+        <v>1948</v>
+      </c>
+      <c r="D435" t="s">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="436" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A436" t="s">
+        <v>871</v>
+      </c>
+      <c r="B436">
+        <v>2011</v>
+      </c>
+      <c r="D436" t="s">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="437" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A437" t="s">
+        <v>873</v>
+      </c>
+      <c r="B437">
+        <v>1952</v>
+      </c>
+      <c r="D437" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="438" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A438" t="s">
+        <v>875</v>
+      </c>
+      <c r="B438">
+        <v>2025</v>
+      </c>
+      <c r="D438" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="439" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A439" t="s">
+        <v>877</v>
+      </c>
+      <c r="B439">
+        <v>1950</v>
+      </c>
+      <c r="D439" t="s">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="440" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A440" t="s">
+        <v>879</v>
+      </c>
+      <c r="B440">
+        <v>1966</v>
+      </c>
+      <c r="D440" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="441" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A441" t="s">
+        <v>881</v>
+      </c>
+      <c r="B441">
+        <v>1964</v>
+      </c>
+      <c r="D441" t="s">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="442" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A442" t="s">
+        <v>883</v>
+      </c>
+      <c r="B442">
+        <v>1946</v>
+      </c>
+      <c r="D442" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="443" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A443" t="s">
+        <v>885</v>
+      </c>
+      <c r="B443">
+        <v>2018</v>
+      </c>
+      <c r="D443" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="444" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A444" t="s">
+        <v>887</v>
+      </c>
+      <c r="B444">
+        <v>1960</v>
+      </c>
+      <c r="D444" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="445" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A445" t="s">
+        <v>889</v>
+      </c>
+      <c r="B445">
+        <v>2001</v>
+      </c>
+      <c r="D445" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="446" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A446" t="s">
+        <v>891</v>
+      </c>
+      <c r="B446">
+        <v>1966</v>
+      </c>
+      <c r="D446" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="447" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A447" t="s">
+        <v>893</v>
+      </c>
+      <c r="B447">
+        <v>1986</v>
+      </c>
+      <c r="D447" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="448" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A448" t="s">
+        <v>895</v>
+      </c>
+      <c r="B448">
+        <v>1966</v>
+      </c>
+      <c r="D448" t="s">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="449" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A449" t="s">
+        <v>897</v>
+      </c>
+      <c r="B449">
+        <v>2001</v>
+      </c>
+      <c r="D449" t="s">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="450" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A450" t="s">
+        <v>899</v>
+      </c>
+      <c r="B450">
+        <v>1999</v>
+      </c>
+      <c r="D450" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="451" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A451" t="s">
+        <v>901</v>
+      </c>
+      <c r="B451">
+        <v>1997</v>
+      </c>
+      <c r="D451" t="s">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="452" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A452" t="s">
+        <v>903</v>
+      </c>
+      <c r="B452">
+        <v>1998</v>
+      </c>
+      <c r="D452" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="453" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A453" t="s">
+        <v>905</v>
+      </c>
+      <c r="B453">
+        <v>2017</v>
+      </c>
+      <c r="D453" t="s">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="454" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A454" t="s">
+        <v>907</v>
+      </c>
+      <c r="B454">
+        <v>1946</v>
+      </c>
+      <c r="D454" t="s">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="455" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A455" t="s">
+        <v>909</v>
+      </c>
+      <c r="B455">
+        <v>2005</v>
+      </c>
+      <c r="D455" t="s">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="456" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A456" t="s">
+        <v>911</v>
+      </c>
+      <c r="B456">
+        <v>1958</v>
+      </c>
+      <c r="D456" t="s">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="457" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A457" t="s">
+        <v>913</v>
+      </c>
+      <c r="B457">
+        <v>1968</v>
+      </c>
+      <c r="D457" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="458" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A458" t="s">
+        <v>915</v>
+      </c>
+      <c r="B458">
+        <v>2021</v>
+      </c>
+      <c r="D458" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="459" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A459" t="s">
+        <v>917</v>
+      </c>
+      <c r="B459">
+        <v>2024</v>
+      </c>
+      <c r="D459" t="s">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="460" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A460" t="s">
+        <v>919</v>
+      </c>
+      <c r="B460">
+        <v>1955</v>
+      </c>
+      <c r="D460" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="461" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A461" t="s">
+        <v>921</v>
+      </c>
+      <c r="B461">
+        <v>1989</v>
+      </c>
+      <c r="D461" t="s">
+        <v>922</v>
+      </c>
+    </row>
+    <row r="462" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A462" t="s">
+        <v>923</v>
+      </c>
+      <c r="B462">
+        <v>2000</v>
+      </c>
+      <c r="D462" t="s">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="463" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A463" t="s">
+        <v>925</v>
+      </c>
+      <c r="B463">
+        <v>1928</v>
+      </c>
+      <c r="D463" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="464" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A464" t="s">
+        <v>927</v>
+      </c>
+      <c r="B464">
+        <v>2002</v>
+      </c>
+      <c r="D464" t="s">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="465" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A465" t="s">
+        <v>929</v>
+      </c>
+      <c r="B465">
+        <v>1965</v>
+      </c>
+      <c r="D465" t="s">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="466" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A466" t="s">
+        <v>931</v>
+      </c>
+      <c r="B466">
+        <v>2010</v>
+      </c>
+      <c r="D466" t="s">
+        <v>932</v>
+      </c>
+    </row>
+    <row r="467" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A467" t="s">
+        <v>933</v>
+      </c>
+      <c r="B467">
+        <v>2016</v>
+      </c>
+      <c r="D467" t="s">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="468" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A468" t="s">
+        <v>935</v>
+      </c>
+      <c r="B468">
+        <v>1920</v>
+      </c>
+      <c r="D468" t="s">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="469" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A469" t="s">
+        <v>937</v>
+      </c>
+      <c r="B469">
+        <v>1992</v>
+      </c>
+      <c r="D469" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="470" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A470" t="s">
+        <v>939</v>
+      </c>
+      <c r="B470">
+        <v>1996</v>
+      </c>
+      <c r="D470" t="s">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="471" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A471" t="s">
+        <v>941</v>
+      </c>
+      <c r="B471">
+        <v>1954</v>
+      </c>
+      <c r="D471" t="s">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="472" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A472" t="s">
+        <v>943</v>
+      </c>
+      <c r="B472">
+        <v>2019</v>
+      </c>
+      <c r="D472" t="s">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="473" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A473" t="s">
+        <v>945</v>
+      </c>
+      <c r="B473">
+        <v>1962</v>
+      </c>
+      <c r="D473" t="s">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="474" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A474" t="s">
+        <v>947</v>
+      </c>
+      <c r="B474">
+        <v>2017</v>
+      </c>
+      <c r="D474" t="s">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="475" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A475" t="s">
+        <v>949</v>
+      </c>
+      <c r="B475">
+        <v>1967</v>
+      </c>
+      <c r="D475" t="s">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="476" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A476" t="s">
+        <v>951</v>
+      </c>
+      <c r="B476">
+        <v>1999</v>
+      </c>
+      <c r="D476" t="s">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="477" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A477" t="s">
+        <v>953</v>
+      </c>
+      <c r="B477">
+        <v>1979</v>
+      </c>
+      <c r="D477" t="s">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="478" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A478" t="s">
+        <v>955</v>
+      </c>
+      <c r="B478">
+        <v>1928</v>
+      </c>
+      <c r="D478" t="s">
+        <v>956</v>
+      </c>
+    </row>
+    <row r="479" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A479" t="s">
+        <v>957</v>
+      </c>
+      <c r="B479">
+        <v>1981</v>
+      </c>
+      <c r="D479" t="s">
+        <v>958</v>
+      </c>
+    </row>
+    <row r="480" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A480" t="s">
+        <v>959</v>
+      </c>
+      <c r="B480">
+        <v>1924</v>
+      </c>
+      <c r="D480" t="s">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="481" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A481" t="s">
+        <v>961</v>
+      </c>
+      <c r="B481">
+        <v>2018</v>
+      </c>
+      <c r="D481" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="482" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A482" t="s">
+        <v>963</v>
+      </c>
+      <c r="B482">
+        <v>1975</v>
+      </c>
+      <c r="D482" t="s">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="483" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A483" t="s">
+        <v>965</v>
+      </c>
+      <c r="B483">
+        <v>2025</v>
+      </c>
+      <c r="D483" t="s">
+        <v>966</v>
+      </c>
+    </row>
+    <row r="484" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A484" t="s">
+        <v>967</v>
+      </c>
+      <c r="B484">
+        <v>1993</v>
+      </c>
+      <c r="D484" t="s">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="485" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A485" t="s">
+        <v>969</v>
+      </c>
+      <c r="B485">
+        <v>1987</v>
+      </c>
+      <c r="D485" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="486" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A486" t="s">
+        <v>971</v>
+      </c>
+      <c r="B486">
+        <v>1946</v>
+      </c>
+      <c r="D486" t="s">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="487" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A487" t="s">
+        <v>973</v>
+      </c>
+      <c r="B487">
+        <v>2013</v>
+      </c>
+      <c r="D487" t="s">
+        <v>974</v>
+      </c>
+    </row>
+    <row r="488" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A488" t="s">
+        <v>975</v>
+      </c>
+      <c r="B488">
+        <v>1976</v>
+      </c>
+      <c r="D488" t="s">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="489" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A489" t="s">
+        <v>977</v>
+      </c>
+      <c r="B489">
+        <v>2020</v>
+      </c>
+      <c r="D489" t="s">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="490" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A490" t="s">
+        <v>979</v>
+      </c>
+      <c r="B490">
+        <v>1944</v>
+      </c>
+      <c r="D490" t="s">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="491" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A491" t="s">
+        <v>981</v>
+      </c>
+      <c r="B491">
+        <v>2024</v>
+      </c>
+      <c r="D491" t="s">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="492" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A492" t="s">
+        <v>983</v>
+      </c>
+      <c r="B492">
+        <v>1980</v>
+      </c>
+      <c r="D492" t="s">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="493" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A493" t="s">
+        <v>985</v>
+      </c>
+      <c r="B493">
+        <v>1960</v>
+      </c>
+      <c r="D493" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="494" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A494" t="s">
+        <v>987</v>
+      </c>
+      <c r="B494">
+        <v>2011</v>
+      </c>
+      <c r="D494" t="s">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="495" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A495" t="s">
+        <v>989</v>
+      </c>
+      <c r="B495">
+        <v>1968</v>
+      </c>
+      <c r="D495" t="s">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="496" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A496" t="s">
+        <v>991</v>
+      </c>
+      <c r="B496">
+        <v>2002</v>
+      </c>
+      <c r="D496" t="s">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="497" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A497" t="s">
+        <v>993</v>
+      </c>
+      <c r="B497">
+        <v>2016</v>
+      </c>
+      <c r="D497" t="s">
+        <v>994</v>
+      </c>
+    </row>
+    <row r="498" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A498" t="s">
+        <v>995</v>
+      </c>
+      <c r="B498">
+        <v>2010</v>
+      </c>
+      <c r="D498" t="s">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="499" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A499" t="s">
+        <v>997</v>
+      </c>
+      <c r="B499">
+        <v>1984</v>
+      </c>
+      <c r="D499" t="s">
+        <v>998</v>
+      </c>
+    </row>
+    <row r="500" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A500" t="s">
+        <v>999</v>
+      </c>
+      <c r="B500">
+        <v>1987</v>
+      </c>
+      <c r="D500" t="s">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="501" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A501" t="s">
+        <v>1001</v>
+      </c>
+      <c r="B501">
+        <v>1950</v>
+      </c>
+      <c r="D501" t="s">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="502" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A502" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B502">
+        <v>1994</v>
+      </c>
+      <c r="D502" t="s">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="503" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A503" t="s">
+        <v>1005</v>
+      </c>
+      <c r="B503">
+        <v>2021</v>
+      </c>
+      <c r="D503" t="s">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="504" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A504" t="s">
+        <v>1007</v>
+      </c>
+      <c r="B504">
+        <v>2014</v>
+      </c>
+      <c r="D504" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="505" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A505" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B505">
+        <v>1985</v>
+      </c>
+      <c r="D505" t="s">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="506" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A506" t="s">
+        <v>1011</v>
+      </c>
+      <c r="B506">
+        <v>1998</v>
+      </c>
+      <c r="D506" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="507" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A507" t="s">
+        <v>1013</v>
+      </c>
+      <c r="B507">
+        <v>2019</v>
+      </c>
+      <c r="D507" t="s">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="508" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A508" t="s">
+        <v>1015</v>
+      </c>
+      <c r="B508">
+        <v>2015</v>
+      </c>
+      <c r="D508" t="s">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="509" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A509" t="s">
+        <v>1017</v>
+      </c>
+      <c r="B509">
+        <v>2009</v>
+      </c>
+      <c r="D509" t="s">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="510" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A510" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B510">
+        <v>2012</v>
+      </c>
+      <c r="D510" t="s">
+        <v>1020</v>
+      </c>
+    </row>
+    <row r="511" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A511" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B511">
+        <v>1940</v>
+      </c>
+      <c r="D511" t="s">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="512" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A512" t="s">
+        <v>1023</v>
+      </c>
+      <c r="B512">
+        <v>2004</v>
+      </c>
+      <c r="D512" t="s">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="513" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A513" t="s">
+        <v>1025</v>
+      </c>
+      <c r="B513">
+        <v>1964</v>
+      </c>
+      <c r="D513" t="s">
+        <v>1026</v>
+      </c>
+    </row>
+    <row r="514" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A514" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B514">
+        <v>2004</v>
+      </c>
+      <c r="D514" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="515" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A515" t="s">
+        <v>1029</v>
+      </c>
+      <c r="B515">
+        <v>2024</v>
+      </c>
+      <c r="D515" t="s">
+        <v>1030</v>
+      </c>
+    </row>
+    <row r="516" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A516" t="s">
+        <v>1031</v>
+      </c>
+      <c r="B516">
+        <v>1972</v>
+      </c>
+      <c r="D516" t="s">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="517" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A517" t="s">
+        <v>1033</v>
+      </c>
+      <c r="B517">
+        <v>1992</v>
+      </c>
+      <c r="D517" t="s">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="518" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A518" t="s">
+        <v>1035</v>
+      </c>
+      <c r="B518">
+        <v>2009</v>
+      </c>
+      <c r="D518" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="519" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A519" t="s">
+        <v>1037</v>
+      </c>
+      <c r="B519">
+        <v>1984</v>
+      </c>
+      <c r="D519" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="520" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A520" t="s">
+        <v>513</v>
+      </c>
+      <c r="B520">
+        <v>1980</v>
+      </c>
+      <c r="D520" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="521" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A521" t="s">
+        <v>1040</v>
+      </c>
+      <c r="B521">
+        <v>2003</v>
+      </c>
+      <c r="D521" t="s">
+        <v>1041</v>
+      </c>
+    </row>
+    <row r="522" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A522" t="s">
+        <v>1042</v>
+      </c>
+      <c r="B522">
+        <v>2008</v>
+      </c>
+      <c r="D522" t="s">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="523" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A523" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B523">
+        <v>2003</v>
+      </c>
+      <c r="D523" t="s">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="524" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A524" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B524">
+        <v>1998</v>
+      </c>
+      <c r="D524" t="s">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="525" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A525" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B525">
+        <v>2012</v>
+      </c>
+      <c r="D525" t="s">
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="526" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A526" t="s">
+        <v>1050</v>
+      </c>
+      <c r="B526">
+        <v>1985</v>
+      </c>
+      <c r="D526" t="s">
+        <v>1051</v>
+      </c>
+    </row>
+    <row r="527" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A527" t="s">
+        <v>1052</v>
+      </c>
+      <c r="B527">
+        <v>1928</v>
+      </c>
+      <c r="D527" t="s">
+        <v>1053</v>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D376" r:id="rId1" xr:uid="{E845355F-2512-4FEA-8B22-7261DB0AEF68}"/>
+    <hyperlink ref="D377" r:id="rId2" xr:uid="{0BABEE8A-8F45-47E1-A57B-B9CD3AD6300A}"/>
+    <hyperlink ref="D378" r:id="rId3" xr:uid="{8C35DED6-55FB-4D0F-BC67-11555078D011}"/>
+    <hyperlink ref="D379" r:id="rId4" xr:uid="{6236F1CA-23A5-4253-A673-1D1AC489343F}"/>
+    <hyperlink ref="D380" r:id="rId5" xr:uid="{C86998E7-D40B-4095-B2C1-413E1E5982F6}"/>
+    <hyperlink ref="D381" r:id="rId6" xr:uid="{F938ED9A-6735-4A64-8558-B5829A874738}"/>
+    <hyperlink ref="D382" r:id="rId7" xr:uid="{4D495342-2395-4F7B-89F5-9893D9EC3A96}"/>
+    <hyperlink ref="D383" r:id="rId8" xr:uid="{0AF84B25-9FD2-451C-8DA3-4E0F17F12AC9}"/>
+    <hyperlink ref="D385" r:id="rId9" xr:uid="{776C9CEA-7871-4374-A43D-DFF17F3051B4}"/>
+    <hyperlink ref="D386" r:id="rId10" xr:uid="{454DB360-E518-429F-A862-554126EEE6A1}"/>
+    <hyperlink ref="D387" r:id="rId11" xr:uid="{368B7CDE-8355-4739-83B5-7B0ABB90B5B2}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Official Whitelist.xlsx
+++ b/Official Whitelist.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bigba\aa Personal Projects\Letterboxd-List-Scraping\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A9F3783-45F1-476F-9FFE-ACA917C05B74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26ECD877-48C1-48D8-B674-4BD61141BA05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1055" uniqueCount="1054">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1101" uniqueCount="1100">
   <si>
     <t>Title</t>
   </si>
@@ -3187,6 +3187,144 @@
   </si>
   <si>
     <t>https://letterboxd.com/film/steamboat-bill-jr/</t>
+  </si>
+  <si>
+    <t>The Cremator</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-cremator/</t>
+  </si>
+  <si>
+    <t>The Plague Dogs</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-plague-dogs/</t>
+  </si>
+  <si>
+    <t>Germany Year Zero</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/germany-year-zero/</t>
+  </si>
+  <si>
+    <t>Hour Of The Wolf</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/hour-of-the-wolf/</t>
+  </si>
+  <si>
+    <t>Out 1</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/out-1/</t>
+  </si>
+  <si>
+    <t>The Voice Of Hind Rajab</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-voice-of-hind-rajab/</t>
+  </si>
+  <si>
+    <t>When I Grow Up Ill Be A Kangaroo</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/when-i-grow-up-ill-be-a-kangaroo/</t>
+  </si>
+  <si>
+    <t>My Father's Shadow</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/my-fathers-shadow-2025/</t>
+  </si>
+  <si>
+    <t>CÃ©line</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/film:96932/</t>
+  </si>
+  <si>
+    <t>Red Dawn 1990</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/red-dawn-1990/</t>
+  </si>
+  <si>
+    <t>The Set Up</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-set-up/</t>
+  </si>
+  <si>
+    <t>The Venture Bros Radiant Is The Blood Of The Baboon Heart</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-venture-bros-radiant-is-the-blood-of-the-baboon-heart/</t>
+  </si>
+  <si>
+    <t>The Guns</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-guns/</t>
+  </si>
+  <si>
+    <t>The Pied Piper</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-pied-piper-1986/</t>
+  </si>
+  <si>
+    <t>Annie Hall</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/annie-hall/</t>
+  </si>
+  <si>
+    <t>The New Land</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-new-land/</t>
+  </si>
+  <si>
+    <t>In Vanda's Room</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/in-vandas-room/</t>
+  </si>
+  <si>
+    <t>Mahanadhi</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/mahanadhi/</t>
+  </si>
+  <si>
+    <t>Michael Madana Kama Rajan</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/michael-madana-kama-rajan/</t>
+  </si>
+  <si>
+    <t>Padayappa</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/padayappa/</t>
+  </si>
+  <si>
+    <t>Deiva Thirumagal</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/deiva-thirumagal/</t>
+  </si>
+  <si>
+    <t>Vasool Raja Mbbs</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/vasool-raja-mbbs/</t>
+  </si>
+  <si>
+    <t>Pelle the Conqueror</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/pelle-the-conqueror/</t>
   </si>
 </sst>
 </file>
@@ -3538,7 +3676,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D527"/>
+  <dimension ref="A1:D550"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="46.36328125" bestFit="1" customWidth="1"/>
@@ -9345,6 +9483,259 @@
       </c>
       <c r="D527" t="s">
         <v>1053</v>
+      </c>
+    </row>
+    <row r="528" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A528" t="s">
+        <v>1054</v>
+      </c>
+      <c r="B528">
+        <v>1969</v>
+      </c>
+      <c r="D528" s="2" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="529" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A529" t="s">
+        <v>1056</v>
+      </c>
+      <c r="B529">
+        <v>1982</v>
+      </c>
+      <c r="D529" t="s">
+        <v>1057</v>
+      </c>
+    </row>
+    <row r="530" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A530" t="s">
+        <v>1058</v>
+      </c>
+      <c r="B530">
+        <v>1948</v>
+      </c>
+      <c r="D530" t="s">
+        <v>1059</v>
+      </c>
+    </row>
+    <row r="531" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A531" t="s">
+        <v>1060</v>
+      </c>
+      <c r="B531">
+        <v>1968</v>
+      </c>
+      <c r="D531" t="s">
+        <v>1061</v>
+      </c>
+    </row>
+    <row r="532" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A532" t="s">
+        <v>1062</v>
+      </c>
+      <c r="B532">
+        <v>1971</v>
+      </c>
+      <c r="D532" t="s">
+        <v>1063</v>
+      </c>
+    </row>
+    <row r="533" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A533" t="s">
+        <v>1064</v>
+      </c>
+      <c r="B533">
+        <v>2025</v>
+      </c>
+      <c r="D533" t="s">
+        <v>1065</v>
+      </c>
+    </row>
+    <row r="534" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A534" t="s">
+        <v>1066</v>
+      </c>
+      <c r="B534">
+        <v>2004</v>
+      </c>
+      <c r="D534" t="s">
+        <v>1067</v>
+      </c>
+    </row>
+    <row r="535" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A535" t="s">
+        <v>1068</v>
+      </c>
+      <c r="B535">
+        <v>2025</v>
+      </c>
+      <c r="D535" t="s">
+        <v>1069</v>
+      </c>
+    </row>
+    <row r="536" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A536" t="s">
+        <v>1070</v>
+      </c>
+      <c r="B536">
+        <v>1992</v>
+      </c>
+      <c r="D536" t="s">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="537" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A537" t="s">
+        <v>1072</v>
+      </c>
+      <c r="B537">
+        <v>1990</v>
+      </c>
+      <c r="D537" t="s">
+        <v>1073</v>
+      </c>
+    </row>
+    <row r="538" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A538" t="s">
+        <v>1074</v>
+      </c>
+      <c r="B538">
+        <v>1949</v>
+      </c>
+      <c r="D538" t="s">
+        <v>1075</v>
+      </c>
+    </row>
+    <row r="539" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A539" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B539">
+        <v>2023</v>
+      </c>
+      <c r="D539" t="s">
+        <v>1077</v>
+      </c>
+    </row>
+    <row r="540" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A540" t="s">
+        <v>1078</v>
+      </c>
+      <c r="B540">
+        <v>1964</v>
+      </c>
+      <c r="D540" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="541" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A541" t="s">
+        <v>1080</v>
+      </c>
+      <c r="B541">
+        <v>1986</v>
+      </c>
+      <c r="D541" t="s">
+        <v>1081</v>
+      </c>
+    </row>
+    <row r="542" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A542" t="s">
+        <v>1082</v>
+      </c>
+      <c r="B542">
+        <v>1977</v>
+      </c>
+      <c r="D542" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="543" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A543" t="s">
+        <v>1084</v>
+      </c>
+      <c r="B543">
+        <v>1972</v>
+      </c>
+      <c r="D543" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="544" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A544" t="s">
+        <v>1086</v>
+      </c>
+      <c r="B544">
+        <v>2000</v>
+      </c>
+      <c r="D544" t="s">
+        <v>1087</v>
+      </c>
+    </row>
+    <row r="545" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A545" t="s">
+        <v>1088</v>
+      </c>
+      <c r="B545">
+        <v>1994</v>
+      </c>
+      <c r="D545" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="546" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A546" t="s">
+        <v>1090</v>
+      </c>
+      <c r="B546">
+        <v>1990</v>
+      </c>
+      <c r="D546" t="s">
+        <v>1091</v>
+      </c>
+    </row>
+    <row r="547" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A547" t="s">
+        <v>1092</v>
+      </c>
+      <c r="B547">
+        <v>1999</v>
+      </c>
+      <c r="D547" t="s">
+        <v>1093</v>
+      </c>
+    </row>
+    <row r="548" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A548" t="s">
+        <v>1094</v>
+      </c>
+      <c r="B548">
+        <v>2011</v>
+      </c>
+      <c r="D548" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="549" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A549" t="s">
+        <v>1096</v>
+      </c>
+      <c r="B549">
+        <v>2004</v>
+      </c>
+      <c r="D549" t="s">
+        <v>1097</v>
+      </c>
+    </row>
+    <row r="550" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A550" t="s">
+        <v>1098</v>
+      </c>
+      <c r="B550">
+        <v>1987</v>
+      </c>
+      <c r="D550" t="s">
+        <v>1099</v>
       </c>
     </row>
   </sheetData>
@@ -9360,6 +9751,7 @@
     <hyperlink ref="D385" r:id="rId9" xr:uid="{776C9CEA-7871-4374-A43D-DFF17F3051B4}"/>
     <hyperlink ref="D386" r:id="rId10" xr:uid="{454DB360-E518-429F-A862-554126EEE6A1}"/>
     <hyperlink ref="D387" r:id="rId11" xr:uid="{368B7CDE-8355-4739-83B5-7B0ABB90B5B2}"/>
+    <hyperlink ref="D528" r:id="rId12" xr:uid="{A4301CC4-9A54-49C3-8360-6DD0E8DCE230}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Official Whitelist.xlsx
+++ b/Official Whitelist.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bigba\aa Personal Projects\Letterboxd-List-Scraping\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26ECD877-48C1-48D8-B674-4BD61141BA05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29E26AEC-88BC-4C3F-BA75-6A91EA408255}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1101" uniqueCount="1100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1109" uniqueCount="1108">
   <si>
     <t>Title</t>
   </si>
@@ -3060,12 +3060,6 @@
     <t>https://letterboxd.com/film/buddies-1985/</t>
   </si>
   <si>
-    <t>The Boys</t>
-  </si>
-  <si>
-    <t>https://letterboxd.com/film/the-boys/</t>
-  </si>
-  <si>
     <t>Maronas Fantastic Tale</t>
   </si>
   <si>
@@ -3325,6 +3319,36 @@
   </si>
   <si>
     <t>https://letterboxd.com/film/pelle-the-conqueror/</t>
+  </si>
+  <si>
+    <t>Haikyu The Dumpster Battle</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/haikyu-the-dumpster-battle/</t>
+  </si>
+  <si>
+    <t>The Runner</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-runner/</t>
+  </si>
+  <si>
+    <t>Barbie Princess Charm School</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/barbie-princess-charm-school/</t>
+  </si>
+  <si>
+    <t>Scenes From A Marriage</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/scenes-from-a-marriage/</t>
+  </si>
+  <si>
+    <t>C O Kancharapalem</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/c-o-kancharapalem/</t>
   </si>
 </sst>
 </file>
@@ -3676,7 +3700,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D550"/>
+  <dimension ref="A1:D554"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="46.36328125" bestFit="1" customWidth="1"/>
@@ -9248,7 +9272,7 @@
         <v>1011</v>
       </c>
       <c r="B506">
-        <v>1998</v>
+        <v>2019</v>
       </c>
       <c r="D506" t="s">
         <v>1012</v>
@@ -9259,7 +9283,7 @@
         <v>1013</v>
       </c>
       <c r="B507">
-        <v>2019</v>
+        <v>2015</v>
       </c>
       <c r="D507" t="s">
         <v>1014</v>
@@ -9270,7 +9294,7 @@
         <v>1015</v>
       </c>
       <c r="B508">
-        <v>2015</v>
+        <v>2009</v>
       </c>
       <c r="D508" t="s">
         <v>1016</v>
@@ -9281,7 +9305,7 @@
         <v>1017</v>
       </c>
       <c r="B509">
-        <v>2009</v>
+        <v>2012</v>
       </c>
       <c r="D509" t="s">
         <v>1018</v>
@@ -9292,7 +9316,7 @@
         <v>1019</v>
       </c>
       <c r="B510">
-        <v>2012</v>
+        <v>1940</v>
       </c>
       <c r="D510" t="s">
         <v>1020</v>
@@ -9303,7 +9327,7 @@
         <v>1021</v>
       </c>
       <c r="B511">
-        <v>1940</v>
+        <v>2004</v>
       </c>
       <c r="D511" t="s">
         <v>1022</v>
@@ -9314,7 +9338,7 @@
         <v>1023</v>
       </c>
       <c r="B512">
-        <v>2004</v>
+        <v>1964</v>
       </c>
       <c r="D512" t="s">
         <v>1024</v>
@@ -9325,7 +9349,7 @@
         <v>1025</v>
       </c>
       <c r="B513">
-        <v>1964</v>
+        <v>2004</v>
       </c>
       <c r="D513" t="s">
         <v>1026</v>
@@ -9336,7 +9360,7 @@
         <v>1027</v>
       </c>
       <c r="B514">
-        <v>2004</v>
+        <v>2024</v>
       </c>
       <c r="D514" t="s">
         <v>1028</v>
@@ -9347,7 +9371,7 @@
         <v>1029</v>
       </c>
       <c r="B515">
-        <v>2024</v>
+        <v>1972</v>
       </c>
       <c r="D515" t="s">
         <v>1030</v>
@@ -9358,7 +9382,7 @@
         <v>1031</v>
       </c>
       <c r="B516">
-        <v>1972</v>
+        <v>1992</v>
       </c>
       <c r="D516" t="s">
         <v>1032</v>
@@ -9369,7 +9393,7 @@
         <v>1033</v>
       </c>
       <c r="B517">
-        <v>1992</v>
+        <v>2009</v>
       </c>
       <c r="D517" t="s">
         <v>1034</v>
@@ -9380,7 +9404,7 @@
         <v>1035</v>
       </c>
       <c r="B518">
-        <v>2009</v>
+        <v>1984</v>
       </c>
       <c r="D518" t="s">
         <v>1036</v>
@@ -9388,21 +9412,21 @@
     </row>
     <row r="519" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A519" t="s">
+        <v>513</v>
+      </c>
+      <c r="B519">
+        <v>1980</v>
+      </c>
+      <c r="D519" t="s">
         <v>1037</v>
-      </c>
-      <c r="B519">
-        <v>1984</v>
-      </c>
-      <c r="D519" t="s">
-        <v>1038</v>
       </c>
     </row>
     <row r="520" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A520" t="s">
-        <v>513</v>
+        <v>1038</v>
       </c>
       <c r="B520">
-        <v>1980</v>
+        <v>2003</v>
       </c>
       <c r="D520" t="s">
         <v>1039</v>
@@ -9413,7 +9437,7 @@
         <v>1040</v>
       </c>
       <c r="B521">
-        <v>2003</v>
+        <v>2008</v>
       </c>
       <c r="D521" t="s">
         <v>1041</v>
@@ -9424,7 +9448,7 @@
         <v>1042</v>
       </c>
       <c r="B522">
-        <v>2008</v>
+        <v>2003</v>
       </c>
       <c r="D522" t="s">
         <v>1043</v>
@@ -9435,7 +9459,7 @@
         <v>1044</v>
       </c>
       <c r="B523">
-        <v>2003</v>
+        <v>1998</v>
       </c>
       <c r="D523" t="s">
         <v>1045</v>
@@ -9446,7 +9470,7 @@
         <v>1046</v>
       </c>
       <c r="B524">
-        <v>1998</v>
+        <v>2012</v>
       </c>
       <c r="D524" t="s">
         <v>1047</v>
@@ -9457,7 +9481,7 @@
         <v>1048</v>
       </c>
       <c r="B525">
-        <v>2012</v>
+        <v>1985</v>
       </c>
       <c r="D525" t="s">
         <v>1049</v>
@@ -9468,7 +9492,7 @@
         <v>1050</v>
       </c>
       <c r="B526">
-        <v>1985</v>
+        <v>1928</v>
       </c>
       <c r="D526" t="s">
         <v>1051</v>
@@ -9479,9 +9503,9 @@
         <v>1052</v>
       </c>
       <c r="B527">
-        <v>1928</v>
-      </c>
-      <c r="D527" t="s">
+        <v>1969</v>
+      </c>
+      <c r="D527" s="2" t="s">
         <v>1053</v>
       </c>
     </row>
@@ -9490,9 +9514,9 @@
         <v>1054</v>
       </c>
       <c r="B528">
-        <v>1969</v>
-      </c>
-      <c r="D528" s="2" t="s">
+        <v>1982</v>
+      </c>
+      <c r="D528" t="s">
         <v>1055</v>
       </c>
     </row>
@@ -9501,7 +9525,7 @@
         <v>1056</v>
       </c>
       <c r="B529">
-        <v>1982</v>
+        <v>1948</v>
       </c>
       <c r="D529" t="s">
         <v>1057</v>
@@ -9512,7 +9536,7 @@
         <v>1058</v>
       </c>
       <c r="B530">
-        <v>1948</v>
+        <v>1968</v>
       </c>
       <c r="D530" t="s">
         <v>1059</v>
@@ -9523,7 +9547,7 @@
         <v>1060</v>
       </c>
       <c r="B531">
-        <v>1968</v>
+        <v>1971</v>
       </c>
       <c r="D531" t="s">
         <v>1061</v>
@@ -9534,7 +9558,7 @@
         <v>1062</v>
       </c>
       <c r="B532">
-        <v>1971</v>
+        <v>2025</v>
       </c>
       <c r="D532" t="s">
         <v>1063</v>
@@ -9545,7 +9569,7 @@
         <v>1064</v>
       </c>
       <c r="B533">
-        <v>2025</v>
+        <v>2004</v>
       </c>
       <c r="D533" t="s">
         <v>1065</v>
@@ -9556,7 +9580,7 @@
         <v>1066</v>
       </c>
       <c r="B534">
-        <v>2004</v>
+        <v>2025</v>
       </c>
       <c r="D534" t="s">
         <v>1067</v>
@@ -9567,7 +9591,7 @@
         <v>1068</v>
       </c>
       <c r="B535">
-        <v>2025</v>
+        <v>1992</v>
       </c>
       <c r="D535" t="s">
         <v>1069</v>
@@ -9578,7 +9602,7 @@
         <v>1070</v>
       </c>
       <c r="B536">
-        <v>1992</v>
+        <v>1990</v>
       </c>
       <c r="D536" t="s">
         <v>1071</v>
@@ -9589,7 +9613,7 @@
         <v>1072</v>
       </c>
       <c r="B537">
-        <v>1990</v>
+        <v>1949</v>
       </c>
       <c r="D537" t="s">
         <v>1073</v>
@@ -9600,7 +9624,7 @@
         <v>1074</v>
       </c>
       <c r="B538">
-        <v>1949</v>
+        <v>2023</v>
       </c>
       <c r="D538" t="s">
         <v>1075</v>
@@ -9611,7 +9635,7 @@
         <v>1076</v>
       </c>
       <c r="B539">
-        <v>2023</v>
+        <v>1964</v>
       </c>
       <c r="D539" t="s">
         <v>1077</v>
@@ -9622,7 +9646,7 @@
         <v>1078</v>
       </c>
       <c r="B540">
-        <v>1964</v>
+        <v>1986</v>
       </c>
       <c r="D540" t="s">
         <v>1079</v>
@@ -9633,7 +9657,7 @@
         <v>1080</v>
       </c>
       <c r="B541">
-        <v>1986</v>
+        <v>1977</v>
       </c>
       <c r="D541" t="s">
         <v>1081</v>
@@ -9644,7 +9668,7 @@
         <v>1082</v>
       </c>
       <c r="B542">
-        <v>1977</v>
+        <v>1972</v>
       </c>
       <c r="D542" t="s">
         <v>1083</v>
@@ -9655,7 +9679,7 @@
         <v>1084</v>
       </c>
       <c r="B543">
-        <v>1972</v>
+        <v>2000</v>
       </c>
       <c r="D543" t="s">
         <v>1085</v>
@@ -9666,7 +9690,7 @@
         <v>1086</v>
       </c>
       <c r="B544">
-        <v>2000</v>
+        <v>1994</v>
       </c>
       <c r="D544" t="s">
         <v>1087</v>
@@ -9677,7 +9701,7 @@
         <v>1088</v>
       </c>
       <c r="B545">
-        <v>1994</v>
+        <v>1990</v>
       </c>
       <c r="D545" t="s">
         <v>1089</v>
@@ -9688,7 +9712,7 @@
         <v>1090</v>
       </c>
       <c r="B546">
-        <v>1990</v>
+        <v>1999</v>
       </c>
       <c r="D546" t="s">
         <v>1091</v>
@@ -9699,7 +9723,7 @@
         <v>1092</v>
       </c>
       <c r="B547">
-        <v>1999</v>
+        <v>2011</v>
       </c>
       <c r="D547" t="s">
         <v>1093</v>
@@ -9710,7 +9734,7 @@
         <v>1094</v>
       </c>
       <c r="B548">
-        <v>2011</v>
+        <v>2004</v>
       </c>
       <c r="D548" t="s">
         <v>1095</v>
@@ -9721,7 +9745,7 @@
         <v>1096</v>
       </c>
       <c r="B549">
-        <v>2004</v>
+        <v>1987</v>
       </c>
       <c r="D549" t="s">
         <v>1097</v>
@@ -9732,10 +9756,54 @@
         <v>1098</v>
       </c>
       <c r="B550">
-        <v>1987</v>
+        <v>2024</v>
       </c>
       <c r="D550" t="s">
         <v>1099</v>
+      </c>
+    </row>
+    <row r="551" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A551" t="s">
+        <v>1100</v>
+      </c>
+      <c r="B551">
+        <v>1984</v>
+      </c>
+      <c r="D551" s="2" t="s">
+        <v>1101</v>
+      </c>
+    </row>
+    <row r="552" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A552" t="s">
+        <v>1102</v>
+      </c>
+      <c r="B552">
+        <v>2011</v>
+      </c>
+      <c r="D552" s="2" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="553" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A553" t="s">
+        <v>1104</v>
+      </c>
+      <c r="B553">
+        <v>1974</v>
+      </c>
+      <c r="D553" t="s">
+        <v>1105</v>
+      </c>
+    </row>
+    <row r="554" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A554" t="s">
+        <v>1106</v>
+      </c>
+      <c r="B554">
+        <v>2018</v>
+      </c>
+      <c r="D554" s="2" t="s">
+        <v>1107</v>
       </c>
     </row>
   </sheetData>
@@ -9751,7 +9819,10 @@
     <hyperlink ref="D385" r:id="rId9" xr:uid="{776C9CEA-7871-4374-A43D-DFF17F3051B4}"/>
     <hyperlink ref="D386" r:id="rId10" xr:uid="{454DB360-E518-429F-A862-554126EEE6A1}"/>
     <hyperlink ref="D387" r:id="rId11" xr:uid="{368B7CDE-8355-4739-83B5-7B0ABB90B5B2}"/>
-    <hyperlink ref="D528" r:id="rId12" xr:uid="{A4301CC4-9A54-49C3-8360-6DD0E8DCE230}"/>
+    <hyperlink ref="D527" r:id="rId12" xr:uid="{A4301CC4-9A54-49C3-8360-6DD0E8DCE230}"/>
+    <hyperlink ref="D551" r:id="rId13" xr:uid="{16145F1C-6214-4749-8D8A-FDD477E08B28}"/>
+    <hyperlink ref="D552" r:id="rId14" xr:uid="{024C5F8B-8F81-420D-868D-5D8E76ABB1AE}"/>
+    <hyperlink ref="D554" r:id="rId15" xr:uid="{E70978B9-40E5-446D-987D-E57F6DB2DA9E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Official Whitelist.xlsx
+++ b/Official Whitelist.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bigba\aa Personal Projects\Letterboxd-List-Scraping\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29E26AEC-88BC-4C3F-BA75-6A91EA408255}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{286A05FB-9B42-4F3E-A79D-97E51079085E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1109" uniqueCount="1108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1120" uniqueCount="1119">
   <si>
     <t>Title</t>
   </si>
@@ -3349,6 +3349,39 @@
   </si>
   <si>
     <t>https://letterboxd.com/film/c-o-kancharapalem/</t>
+  </si>
+  <si>
+    <t>Stormskerry Maja</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/stormskerry-maja/</t>
+  </si>
+  <si>
+    <t>Time Still Turns The Pages</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/time-still-turns-the-pages/</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Walking the Streets of Moscow</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/walking-the-streets-of-moscow/</t>
+  </si>
+  <si>
+    <t>War And Peace Part Ii Natasha Rostova</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/war-and-peace-part-ii-natasha-rostova/</t>
+  </si>
+  <si>
+    <t>Castration Movie Anthology i. Traps</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/castration-movie-anthology-i-traps/</t>
   </si>
 </sst>
 </file>
@@ -3700,7 +3733,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D554"/>
+  <dimension ref="A1:E559"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="46.36328125" bestFit="1" customWidth="1"/>
@@ -9696,7 +9729,7 @@
         <v>1087</v>
       </c>
     </row>
-    <row r="545" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="545" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A545" t="s">
         <v>1088</v>
       </c>
@@ -9707,7 +9740,7 @@
         <v>1089</v>
       </c>
     </row>
-    <row r="546" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="546" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A546" t="s">
         <v>1090</v>
       </c>
@@ -9718,7 +9751,7 @@
         <v>1091</v>
       </c>
     </row>
-    <row r="547" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="547" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A547" t="s">
         <v>1092</v>
       </c>
@@ -9729,7 +9762,7 @@
         <v>1093</v>
       </c>
     </row>
-    <row r="548" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="548" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A548" t="s">
         <v>1094</v>
       </c>
@@ -9740,7 +9773,7 @@
         <v>1095</v>
       </c>
     </row>
-    <row r="549" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="549" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A549" t="s">
         <v>1096</v>
       </c>
@@ -9751,7 +9784,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="550" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="550" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A550" t="s">
         <v>1098</v>
       </c>
@@ -9762,7 +9795,7 @@
         <v>1099</v>
       </c>
     </row>
-    <row r="551" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="551" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A551" t="s">
         <v>1100</v>
       </c>
@@ -9773,7 +9806,7 @@
         <v>1101</v>
       </c>
     </row>
-    <row r="552" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="552" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A552" t="s">
         <v>1102</v>
       </c>
@@ -9784,7 +9817,7 @@
         <v>1103</v>
       </c>
     </row>
-    <row r="553" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="553" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A553" t="s">
         <v>1104</v>
       </c>
@@ -9795,7 +9828,7 @@
         <v>1105</v>
       </c>
     </row>
-    <row r="554" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="554" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A554" t="s">
         <v>1106</v>
       </c>
@@ -9804,6 +9837,79 @@
       </c>
       <c r="D554" s="2" t="s">
         <v>1107</v>
+      </c>
+    </row>
+    <row r="555" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A555" t="s">
+        <v>1108</v>
+      </c>
+      <c r="B555">
+        <v>2024</v>
+      </c>
+      <c r="C555">
+        <v>1028769</v>
+      </c>
+      <c r="D555" s="2" t="s">
+        <v>1109</v>
+      </c>
+    </row>
+    <row r="556" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A556" t="s">
+        <v>1110</v>
+      </c>
+      <c r="B556">
+        <v>2023</v>
+      </c>
+      <c r="C556">
+        <v>957863</v>
+      </c>
+      <c r="D556" s="2" t="s">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="557" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A557" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B557">
+        <v>1964</v>
+      </c>
+      <c r="C557">
+        <v>27862</v>
+      </c>
+      <c r="D557" s="2" t="s">
+        <v>1114</v>
+      </c>
+    </row>
+    <row r="558" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A558" t="s">
+        <v>1115</v>
+      </c>
+      <c r="B558">
+        <v>1965</v>
+      </c>
+      <c r="C558">
+        <v>149465</v>
+      </c>
+      <c r="D558" s="2" t="s">
+        <v>1116</v>
+      </c>
+    </row>
+    <row r="559" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A559" t="s">
+        <v>1117</v>
+      </c>
+      <c r="B559">
+        <v>2024</v>
+      </c>
+      <c r="C559">
+        <v>1243479</v>
+      </c>
+      <c r="D559" s="2" t="s">
+        <v>1118</v>
+      </c>
+      <c r="E559" t="s">
+        <v>1112</v>
       </c>
     </row>
   </sheetData>
@@ -9823,6 +9929,11 @@
     <hyperlink ref="D551" r:id="rId13" xr:uid="{16145F1C-6214-4749-8D8A-FDD477E08B28}"/>
     <hyperlink ref="D552" r:id="rId14" xr:uid="{024C5F8B-8F81-420D-868D-5D8E76ABB1AE}"/>
     <hyperlink ref="D554" r:id="rId15" xr:uid="{E70978B9-40E5-446D-987D-E57F6DB2DA9E}"/>
+    <hyperlink ref="D555" r:id="rId16" xr:uid="{A294FD8A-3D0D-4D2E-87BD-F10BABD32315}"/>
+    <hyperlink ref="D556" r:id="rId17" xr:uid="{F28C7628-2B4D-4FCE-8952-BFDD7C7F06CE}"/>
+    <hyperlink ref="D557" r:id="rId18" xr:uid="{193BDB09-EFD2-4937-8E49-91638F1A9791}"/>
+    <hyperlink ref="D558" r:id="rId19" xr:uid="{5C1D518D-E5D1-4FFF-A746-E8BAD67AEA01}"/>
+    <hyperlink ref="D559" r:id="rId20" xr:uid="{5D8CCB0C-6663-42F7-A44C-954C049BD83E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Official Whitelist.xlsx
+++ b/Official Whitelist.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bigba\aa Personal Projects\Letterboxd-List-Scraping\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{286A05FB-9B42-4F3E-A79D-97E51079085E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAAA3A60-63E7-4750-916F-3C262B1AD911}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="380" yWindow="380" windowWidth="14400" windowHeight="8170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1120" uniqueCount="1119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1130" uniqueCount="1127">
   <si>
     <t>Title</t>
   </si>
@@ -3382,6 +3382,30 @@
   </si>
   <si>
     <t>https://letterboxd.com/film/castration-movie-anthology-i-traps/</t>
+  </si>
+  <si>
+    <t>NausicaÃ¤ of the Valley of the Wind</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/nausicaa-of-the-valley-of-the-wind/</t>
+  </si>
+  <si>
+    <t>Extraordinary Stories</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/extraordinary-stories/</t>
+  </si>
+  <si>
+    <t>The Promised Land</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-promised-land-1975/</t>
+  </si>
+  <si>
+    <t>Thevar Magan</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/thevar-magan/</t>
   </si>
 </sst>
 </file>
@@ -3733,7 +3757,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E559"/>
+  <dimension ref="A1:E563"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="46.36328125" bestFit="1" customWidth="1"/>
@@ -9910,6 +9934,68 @@
       </c>
       <c r="E559" t="s">
         <v>1112</v>
+      </c>
+    </row>
+    <row r="560" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A560" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B560">
+        <v>1984</v>
+      </c>
+      <c r="C560">
+        <v>81</v>
+      </c>
+      <c r="D560" s="2" t="s">
+        <v>1120</v>
+      </c>
+      <c r="E560" t="s">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="561" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A561" t="s">
+        <v>1121</v>
+      </c>
+      <c r="B561">
+        <v>2008</v>
+      </c>
+      <c r="C561">
+        <v>111188</v>
+      </c>
+      <c r="D561" s="2" t="s">
+        <v>1122</v>
+      </c>
+      <c r="E561" t="s">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="562" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A562" t="s">
+        <v>1123</v>
+      </c>
+      <c r="B562">
+        <v>1975</v>
+      </c>
+      <c r="C562">
+        <v>511</v>
+      </c>
+      <c r="D562" s="2" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="563" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A563" t="s">
+        <v>1125</v>
+      </c>
+      <c r="B563">
+        <v>1992</v>
+      </c>
+      <c r="C563">
+        <v>66362</v>
+      </c>
+      <c r="D563" s="2" t="s">
+        <v>1126</v>
       </c>
     </row>
   </sheetData>
@@ -9934,6 +10020,10 @@
     <hyperlink ref="D557" r:id="rId18" xr:uid="{193BDB09-EFD2-4937-8E49-91638F1A9791}"/>
     <hyperlink ref="D558" r:id="rId19" xr:uid="{5C1D518D-E5D1-4FFF-A746-E8BAD67AEA01}"/>
     <hyperlink ref="D559" r:id="rId20" xr:uid="{5D8CCB0C-6663-42F7-A44C-954C049BD83E}"/>
+    <hyperlink ref="D560" r:id="rId21" xr:uid="{4375E633-718C-4FF4-B551-501BADD47EFD}"/>
+    <hyperlink ref="D561" r:id="rId22" xr:uid="{946D4369-9E99-4934-BD8D-833824E29DAC}"/>
+    <hyperlink ref="D562" r:id="rId23" xr:uid="{B0DAA382-D612-4C52-92CC-60F966246E5A}"/>
+    <hyperlink ref="D563" r:id="rId24" xr:uid="{F1F98DA8-9B33-4768-A093-3D35DBF11836}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Official Whitelist.xlsx
+++ b/Official Whitelist.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bigba\aa Personal Projects\Letterboxd-List-Scraping\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAAA3A60-63E7-4750-916F-3C262B1AD911}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12A0C7A8-C99F-4BAC-8F50-4194F13886C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="380" yWindow="380" windowWidth="14400" windowHeight="8170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2080" yWindow="2080" windowWidth="14400" windowHeight="8170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1130" uniqueCount="1127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1138" uniqueCount="1135">
   <si>
     <t>Title</t>
   </si>
@@ -3406,6 +3406,30 @@
   </si>
   <si>
     <t>https://letterboxd.com/film/thevar-magan/</t>
+  </si>
+  <si>
+    <t>Nostos The Return</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/nostos-the-return/</t>
+  </si>
+  <si>
+    <t>Kung Fu Hustle</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/kung-fu-hustle/</t>
+  </si>
+  <si>
+    <t>Nadodikkattu</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/nadodikkattu/</t>
+  </si>
+  <si>
+    <t>Eros + Massacre</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/eros-massacre/</t>
   </si>
 </sst>
 </file>
@@ -3757,7 +3781,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E563"/>
+  <dimension ref="A1:E567"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="46.36328125" bestFit="1" customWidth="1"/>
@@ -9996,6 +10020,62 @@
       </c>
       <c r="D563" s="2" t="s">
         <v>1126</v>
+      </c>
+    </row>
+    <row r="564" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A564" t="s">
+        <v>1127</v>
+      </c>
+      <c r="B564">
+        <v>1989</v>
+      </c>
+      <c r="C564">
+        <v>237957</v>
+      </c>
+      <c r="D564" t="s">
+        <v>1128</v>
+      </c>
+    </row>
+    <row r="565" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A565" t="s">
+        <v>1129</v>
+      </c>
+      <c r="B565">
+        <v>2004</v>
+      </c>
+      <c r="C565">
+        <v>9470</v>
+      </c>
+      <c r="D565" s="2" t="s">
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="566" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A566" t="s">
+        <v>1131</v>
+      </c>
+      <c r="B566">
+        <v>1987</v>
+      </c>
+      <c r="C566">
+        <v>275366</v>
+      </c>
+      <c r="D566" t="s">
+        <v>1132</v>
+      </c>
+    </row>
+    <row r="567" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A567" t="s">
+        <v>1133</v>
+      </c>
+      <c r="B567">
+        <v>1969</v>
+      </c>
+      <c r="C567">
+        <v>78117</v>
+      </c>
+      <c r="D567" t="s">
+        <v>1134</v>
       </c>
     </row>
   </sheetData>
@@ -10024,6 +10104,7 @@
     <hyperlink ref="D561" r:id="rId22" xr:uid="{946D4369-9E99-4934-BD8D-833824E29DAC}"/>
     <hyperlink ref="D562" r:id="rId23" xr:uid="{B0DAA382-D612-4C52-92CC-60F966246E5A}"/>
     <hyperlink ref="D563" r:id="rId24" xr:uid="{F1F98DA8-9B33-4768-A093-3D35DBF11836}"/>
+    <hyperlink ref="D565" r:id="rId25" xr:uid="{183D0A7D-6CE1-42F6-B6E1-4F9B48010CF2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Official Whitelist.xlsx
+++ b/Official Whitelist.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bigba\aa Personal Projects\Letterboxd-List-Scraping\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12A0C7A8-C99F-4BAC-8F50-4194F13886C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{665A4384-62DC-4175-A287-E30D3F6DE382}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2080" yWindow="2080" windowWidth="14400" windowHeight="8170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1138" uniqueCount="1135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1137" uniqueCount="1136">
   <si>
     <t>Title</t>
   </si>
@@ -3363,9 +3363,6 @@
     <t>https://letterboxd.com/film/time-still-turns-the-pages/</t>
   </si>
   <si>
-    <t>Yes</t>
-  </si>
-  <si>
     <t>Walking the Streets of Moscow</t>
   </si>
   <si>
@@ -3430,6 +3427,12 @@
   </si>
   <si>
     <t>https://letterboxd.com/film/eros-massacre/</t>
+  </si>
+  <si>
+    <t>Sairat</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/sairat/</t>
   </si>
 </sst>
 </file>
@@ -3781,7 +3784,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E567"/>
+  <dimension ref="A1:D568"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="46.36328125" bestFit="1" customWidth="1"/>
@@ -9777,7 +9780,7 @@
         <v>1087</v>
       </c>
     </row>
-    <row r="545" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="545" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A545" t="s">
         <v>1088</v>
       </c>
@@ -9788,7 +9791,7 @@
         <v>1089</v>
       </c>
     </row>
-    <row r="546" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="546" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A546" t="s">
         <v>1090</v>
       </c>
@@ -9799,7 +9802,7 @@
         <v>1091</v>
       </c>
     </row>
-    <row r="547" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="547" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A547" t="s">
         <v>1092</v>
       </c>
@@ -9810,7 +9813,7 @@
         <v>1093</v>
       </c>
     </row>
-    <row r="548" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="548" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A548" t="s">
         <v>1094</v>
       </c>
@@ -9821,7 +9824,7 @@
         <v>1095</v>
       </c>
     </row>
-    <row r="549" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="549" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A549" t="s">
         <v>1096</v>
       </c>
@@ -9832,7 +9835,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="550" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="550" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A550" t="s">
         <v>1098</v>
       </c>
@@ -9843,7 +9846,7 @@
         <v>1099</v>
       </c>
     </row>
-    <row r="551" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="551" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A551" t="s">
         <v>1100</v>
       </c>
@@ -9854,7 +9857,7 @@
         <v>1101</v>
       </c>
     </row>
-    <row r="552" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="552" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A552" t="s">
         <v>1102</v>
       </c>
@@ -9865,7 +9868,7 @@
         <v>1103</v>
       </c>
     </row>
-    <row r="553" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="553" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A553" t="s">
         <v>1104</v>
       </c>
@@ -9876,7 +9879,7 @@
         <v>1105</v>
       </c>
     </row>
-    <row r="554" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="554" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A554" t="s">
         <v>1106</v>
       </c>
@@ -9887,7 +9890,7 @@
         <v>1107</v>
       </c>
     </row>
-    <row r="555" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="555" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A555" t="s">
         <v>1108</v>
       </c>
@@ -9901,7 +9904,7 @@
         <v>1109</v>
       </c>
     </row>
-    <row r="556" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="556" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A556" t="s">
         <v>1110</v>
       </c>
@@ -9915,9 +9918,9 @@
         <v>1111</v>
       </c>
     </row>
-    <row r="557" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="557" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A557" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="B557">
         <v>1964</v>
@@ -9926,12 +9929,12 @@
         <v>27862</v>
       </c>
       <c r="D557" s="2" t="s">
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="558" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A558" t="s">
         <v>1114</v>
-      </c>
-    </row>
-    <row r="558" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A558" t="s">
-        <v>1115</v>
       </c>
       <c r="B558">
         <v>1965</v>
@@ -9940,12 +9943,12 @@
         <v>149465</v>
       </c>
       <c r="D558" s="2" t="s">
+        <v>1115</v>
+      </c>
+    </row>
+    <row r="559" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A559" t="s">
         <v>1116</v>
-      </c>
-    </row>
-    <row r="559" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A559" t="s">
-        <v>1117</v>
       </c>
       <c r="B559">
         <v>2024</v>
@@ -9954,15 +9957,12 @@
         <v>1243479</v>
       </c>
       <c r="D559" s="2" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="560" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A560" t="s">
         <v>1118</v>
-      </c>
-      <c r="E559" t="s">
-        <v>1112</v>
-      </c>
-    </row>
-    <row r="560" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A560" t="s">
-        <v>1119</v>
       </c>
       <c r="B560">
         <v>1984</v>
@@ -9971,15 +9971,12 @@
         <v>81</v>
       </c>
       <c r="D560" s="2" t="s">
+        <v>1119</v>
+      </c>
+    </row>
+    <row r="561" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A561" t="s">
         <v>1120</v>
-      </c>
-      <c r="E560" t="s">
-        <v>1112</v>
-      </c>
-    </row>
-    <row r="561" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A561" t="s">
-        <v>1121</v>
       </c>
       <c r="B561">
         <v>2008</v>
@@ -9988,15 +9985,12 @@
         <v>111188</v>
       </c>
       <c r="D561" s="2" t="s">
+        <v>1121</v>
+      </c>
+    </row>
+    <row r="562" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A562" t="s">
         <v>1122</v>
-      </c>
-      <c r="E561" t="s">
-        <v>1112</v>
-      </c>
-    </row>
-    <row r="562" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A562" t="s">
-        <v>1123</v>
       </c>
       <c r="B562">
         <v>1975</v>
@@ -10005,12 +9999,12 @@
         <v>511</v>
       </c>
       <c r="D562" s="2" t="s">
+        <v>1123</v>
+      </c>
+    </row>
+    <row r="563" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A563" t="s">
         <v>1124</v>
-      </c>
-    </row>
-    <row r="563" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A563" t="s">
-        <v>1125</v>
       </c>
       <c r="B563">
         <v>1992</v>
@@ -10019,12 +10013,12 @@
         <v>66362</v>
       </c>
       <c r="D563" s="2" t="s">
+        <v>1125</v>
+      </c>
+    </row>
+    <row r="564" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A564" t="s">
         <v>1126</v>
-      </c>
-    </row>
-    <row r="564" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A564" t="s">
-        <v>1127</v>
       </c>
       <c r="B564">
         <v>1989</v>
@@ -10033,12 +10027,12 @@
         <v>237957</v>
       </c>
       <c r="D564" t="s">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="565" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A565" t="s">
         <v>1128</v>
-      </c>
-    </row>
-    <row r="565" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A565" t="s">
-        <v>1129</v>
       </c>
       <c r="B565">
         <v>2004</v>
@@ -10047,12 +10041,12 @@
         <v>9470</v>
       </c>
       <c r="D565" s="2" t="s">
+        <v>1129</v>
+      </c>
+    </row>
+    <row r="566" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A566" t="s">
         <v>1130</v>
-      </c>
-    </row>
-    <row r="566" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A566" t="s">
-        <v>1131</v>
       </c>
       <c r="B566">
         <v>1987</v>
@@ -10061,12 +10055,12 @@
         <v>275366</v>
       </c>
       <c r="D566" t="s">
+        <v>1131</v>
+      </c>
+    </row>
+    <row r="567" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A567" t="s">
         <v>1132</v>
-      </c>
-    </row>
-    <row r="567" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A567" t="s">
-        <v>1133</v>
       </c>
       <c r="B567">
         <v>1969</v>
@@ -10075,7 +10069,21 @@
         <v>78117</v>
       </c>
       <c r="D567" t="s">
+        <v>1133</v>
+      </c>
+    </row>
+    <row r="568" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A568" t="s">
         <v>1134</v>
+      </c>
+      <c r="B568">
+        <v>2016</v>
+      </c>
+      <c r="C568">
+        <v>383367</v>
+      </c>
+      <c r="D568" s="2" t="s">
+        <v>1135</v>
       </c>
     </row>
   </sheetData>
@@ -10105,6 +10113,7 @@
     <hyperlink ref="D562" r:id="rId23" xr:uid="{B0DAA382-D612-4C52-92CC-60F966246E5A}"/>
     <hyperlink ref="D563" r:id="rId24" xr:uid="{F1F98DA8-9B33-4768-A093-3D35DBF11836}"/>
     <hyperlink ref="D565" r:id="rId25" xr:uid="{183D0A7D-6CE1-42F6-B6E1-4F9B48010CF2}"/>
+    <hyperlink ref="D568" r:id="rId26" xr:uid="{82067776-FBC4-42EE-8A1C-DC7F82929CE6}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Official Whitelist.xlsx
+++ b/Official Whitelist.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bigba\aa Personal Projects\Letterboxd-List-Scraping\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{665A4384-62DC-4175-A287-E30D3F6DE382}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7B7495D-54B7-473D-B55A-F7472DA494B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1137" uniqueCount="1136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1139" uniqueCount="1138">
   <si>
     <t>Title</t>
   </si>
@@ -3433,6 +3433,12 @@
   </si>
   <si>
     <t>https://letterboxd.com/film/sairat/</t>
+  </si>
+  <si>
+    <t>Main Vaapas Aaunga</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/main-vaapas-aaunga/</t>
   </si>
 </sst>
 </file>
@@ -3784,7 +3790,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D568"/>
+  <dimension ref="A1:D569"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="46.36328125" bestFit="1" customWidth="1"/>
@@ -10084,6 +10090,20 @@
       </c>
       <c r="D568" s="2" t="s">
         <v>1135</v>
+      </c>
+    </row>
+    <row r="569" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A569" t="s">
+        <v>1136</v>
+      </c>
+      <c r="B569">
+        <v>2026</v>
+      </c>
+      <c r="C569">
+        <v>1431068</v>
+      </c>
+      <c r="D569" s="2" t="s">
+        <v>1137</v>
       </c>
     </row>
   </sheetData>
@@ -10114,6 +10134,7 @@
     <hyperlink ref="D563" r:id="rId24" xr:uid="{F1F98DA8-9B33-4768-A093-3D35DBF11836}"/>
     <hyperlink ref="D565" r:id="rId25" xr:uid="{183D0A7D-6CE1-42F6-B6E1-4F9B48010CF2}"/>
     <hyperlink ref="D568" r:id="rId26" xr:uid="{82067776-FBC4-42EE-8A1C-DC7F82929CE6}"/>
+    <hyperlink ref="D569" r:id="rId27" xr:uid="{749A53FD-F4AA-4550-B4EE-F7566180BD0B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Official Whitelist.xlsx
+++ b/Official Whitelist.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bigba\aa Personal Projects\Letterboxd-List-Scraping\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7B7495D-54B7-473D-B55A-F7472DA494B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D017A96-D180-4FFD-93D9-72700751CD79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1139" uniqueCount="1138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1141" uniqueCount="1140">
   <si>
     <t>Title</t>
   </si>
@@ -3439,6 +3439,12 @@
   </si>
   <si>
     <t>https://letterboxd.com/film/main-vaapas-aaunga/</t>
+  </si>
+  <si>
+    <t>Uptown Girls</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/uptown-girls/</t>
   </si>
 </sst>
 </file>
@@ -3790,7 +3796,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D569"/>
+  <dimension ref="A1:D570"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="46.36328125" bestFit="1" customWidth="1"/>
@@ -10104,6 +10110,20 @@
       </c>
       <c r="D569" s="2" t="s">
         <v>1137</v>
+      </c>
+    </row>
+    <row r="570" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A570" t="s">
+        <v>1138</v>
+      </c>
+      <c r="B570">
+        <v>2003</v>
+      </c>
+      <c r="C570">
+        <v>14926</v>
+      </c>
+      <c r="D570" t="s">
+        <v>1139</v>
       </c>
     </row>
   </sheetData>

--- a/Official Whitelist.xlsx
+++ b/Official Whitelist.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bigba\aa Personal Projects\Letterboxd-List-Scraping\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D017A96-D180-4FFD-93D9-72700751CD79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66F15952-60E6-4F99-B680-DA3ACFFD371F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1141" uniqueCount="1140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1149" uniqueCount="1148">
   <si>
     <t>Title</t>
   </si>
@@ -318,12 +318,6 @@
     <t>https://letterboxd.com/film/heat-1995/</t>
   </si>
   <si>
-    <t>Edvard Munch</t>
-  </si>
-  <si>
-    <t>https://letterboxd.com/film/edvard-munch/</t>
-  </si>
-  <si>
     <t>Children Of Paradise</t>
   </si>
   <si>
@@ -1656,12 +1650,6 @@
     <t>https://letterboxd.com/film/sherlock-jr/</t>
   </si>
   <si>
-    <t>Its Such A Beautiful Day</t>
-  </si>
-  <si>
-    <t>https://letterboxd.com/film/its-such-a-beautiful-day/</t>
-  </si>
-  <si>
     <t>Chainsaw Man The Movie Reze Arc</t>
   </si>
   <si>
@@ -3333,18 +3321,6 @@
     <t>https://letterboxd.com/film/the-runner/</t>
   </si>
   <si>
-    <t>Barbie Princess Charm School</t>
-  </si>
-  <si>
-    <t>https://letterboxd.com/film/barbie-princess-charm-school/</t>
-  </si>
-  <si>
-    <t>Scenes From A Marriage</t>
-  </si>
-  <si>
-    <t>https://letterboxd.com/film/scenes-from-a-marriage/</t>
-  </si>
-  <si>
     <t>C O Kancharapalem</t>
   </si>
   <si>
@@ -3445,6 +3421,54 @@
   </si>
   <si>
     <t>https://letterboxd.com/film/uptown-girls/</t>
+  </si>
+  <si>
+    <t>Blood In, Blood Out</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/blood-in-blood-out/</t>
+  </si>
+  <si>
+    <t>Satluj</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/satluj-2026/</t>
+  </si>
+  <si>
+    <t>Crayon Shin-chan: The Storm Called: The Adult Empire Strikes Back</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/crayon-shin-chan-the-storm-called-the-adult/</t>
+  </si>
+  <si>
+    <t>The Chaos Class</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-chaos-class/</t>
+  </si>
+  <si>
+    <t>Loving Vincent</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/loving-vincent/</t>
+  </si>
+  <si>
+    <t>The Color Of Paradise</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-color-of-paradise/</t>
+  </si>
+  <si>
+    <t>The Odyssey</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-odyssey-2026/</t>
+  </si>
+  <si>
+    <t>Bajrangi Bhaijaan</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/bajrangi-bhaijaan/</t>
   </si>
 </sst>
 </file>
@@ -3796,7 +3820,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D570"/>
+  <dimension ref="A1:D574"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="46.36328125" bestFit="1" customWidth="1"/>
@@ -4030,6131 +4054,6204 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B21">
-        <v>1982</v>
+        <v>1965</v>
       </c>
       <c r="D21" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B22">
-        <v>1965</v>
+        <v>1975</v>
       </c>
       <c r="D22" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B23">
-        <v>1975</v>
+        <v>2002</v>
       </c>
       <c r="D23" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B24">
-        <v>2002</v>
+        <v>1979</v>
       </c>
       <c r="D24" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B25">
-        <v>1979</v>
+        <v>1974</v>
       </c>
       <c r="D25" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B26">
-        <v>1974</v>
+        <v>1962</v>
       </c>
       <c r="D26" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B27">
-        <v>1962</v>
+        <v>1993</v>
       </c>
       <c r="D27" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B28">
-        <v>1993</v>
+        <v>2008</v>
       </c>
       <c r="D28" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B29">
-        <v>2008</v>
+        <v>1968</v>
       </c>
       <c r="D29" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B30">
-        <v>1968</v>
+        <v>1994</v>
       </c>
       <c r="D30" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B31">
-        <v>1994</v>
+        <v>2001</v>
       </c>
       <c r="D31" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B32">
-        <v>2001</v>
+        <v>2018</v>
       </c>
       <c r="D32" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B33">
-        <v>2018</v>
+        <v>2024</v>
       </c>
       <c r="D33" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B34">
-        <v>2024</v>
+        <v>2009</v>
       </c>
       <c r="D34" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B35">
-        <v>2009</v>
+        <v>1953</v>
       </c>
       <c r="D35" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B36">
-        <v>1953</v>
+        <v>1961</v>
       </c>
       <c r="D36" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B37">
-        <v>1961</v>
+        <v>1984</v>
       </c>
       <c r="D37" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B38">
-        <v>1984</v>
+        <v>2006</v>
       </c>
       <c r="D38" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B39">
-        <v>2006</v>
+        <v>1981</v>
       </c>
       <c r="D39" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B40">
-        <v>1981</v>
+        <v>2012</v>
       </c>
       <c r="D40" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B41">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="D41" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B42">
-        <v>2013</v>
+        <v>1960</v>
       </c>
       <c r="D42" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B43">
-        <v>1960</v>
+        <v>2003</v>
       </c>
       <c r="D43" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B44">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="D44" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B45">
-        <v>2004</v>
+        <v>1995</v>
       </c>
       <c r="D45" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B46">
         <v>1995</v>
       </c>
       <c r="D46" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B47">
-        <v>1995</v>
+        <v>1945</v>
       </c>
       <c r="D47" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B48">
-        <v>1974</v>
+        <v>2021</v>
       </c>
       <c r="D48" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B49">
-        <v>1945</v>
+        <v>1992</v>
       </c>
       <c r="D49" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B50">
-        <v>2021</v>
+        <v>2000</v>
       </c>
       <c r="D50" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B51">
-        <v>1992</v>
+        <v>1999</v>
       </c>
       <c r="D51" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B52">
-        <v>2000</v>
+        <v>1960</v>
       </c>
       <c r="D52" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B53">
-        <v>1999</v>
+        <v>1975</v>
       </c>
       <c r="D53" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B54">
-        <v>1960</v>
+        <v>1998</v>
       </c>
       <c r="D54" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B55">
-        <v>1975</v>
+        <v>1946</v>
       </c>
       <c r="D55" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B56">
-        <v>1998</v>
+        <v>1959</v>
       </c>
       <c r="D56" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B57">
-        <v>1946</v>
+        <v>2015</v>
       </c>
       <c r="D57" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B58">
-        <v>1959</v>
+        <v>1957</v>
       </c>
       <c r="D58" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B59">
-        <v>2015</v>
+        <v>2010</v>
       </c>
       <c r="D59" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B60">
-        <v>1957</v>
+        <v>1964</v>
       </c>
       <c r="D60" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B61">
-        <v>2010</v>
+        <v>1987</v>
       </c>
       <c r="D61" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B62">
-        <v>1964</v>
+        <v>1994</v>
       </c>
       <c r="D62" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B63">
-        <v>1987</v>
+        <v>2018</v>
       </c>
       <c r="D63" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B64">
-        <v>1994</v>
+        <v>1927</v>
       </c>
       <c r="D64" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B65">
-        <v>2018</v>
+        <v>1965</v>
       </c>
       <c r="D65" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B66">
-        <v>1927</v>
+        <v>1943</v>
       </c>
       <c r="D66" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B67">
-        <v>1965</v>
+        <v>2011</v>
       </c>
       <c r="D67" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B68">
-        <v>1943</v>
+        <v>1980</v>
       </c>
       <c r="D68" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B69">
-        <v>2011</v>
+        <v>1972</v>
       </c>
       <c r="D69" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B70">
-        <v>1980</v>
+        <v>1999</v>
       </c>
       <c r="D70" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B71">
-        <v>1972</v>
+        <v>1984</v>
       </c>
       <c r="D71" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B72">
-        <v>1999</v>
+        <v>1991</v>
       </c>
       <c r="D72" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B73">
-        <v>1984</v>
+        <v>1978</v>
       </c>
       <c r="D73" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B74">
-        <v>1991</v>
+        <v>1971</v>
       </c>
       <c r="D74" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B75">
-        <v>1978</v>
+        <v>2014</v>
       </c>
       <c r="D75" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B76">
-        <v>1971</v>
+        <v>2004</v>
       </c>
       <c r="D76" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B77">
-        <v>2014</v>
+        <v>1995</v>
       </c>
       <c r="D77" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B78">
-        <v>2004</v>
+        <v>2024</v>
       </c>
       <c r="D78" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B79">
-        <v>1995</v>
+        <v>1997</v>
       </c>
       <c r="D79" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B80">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="D80" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B81">
-        <v>1997</v>
+        <v>2022</v>
       </c>
       <c r="D81" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B82">
-        <v>2021</v>
+        <v>2003</v>
       </c>
       <c r="D82" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B83">
-        <v>2022</v>
+        <v>1967</v>
       </c>
       <c r="D83" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B84">
-        <v>2003</v>
+        <v>1995</v>
       </c>
       <c r="D84" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B85">
-        <v>1967</v>
+        <v>2012</v>
       </c>
       <c r="D85" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B86">
-        <v>1995</v>
+        <v>2003</v>
       </c>
       <c r="D86" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B87">
-        <v>2012</v>
+        <v>2009</v>
       </c>
       <c r="D87" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B88">
-        <v>2003</v>
+        <v>2025</v>
       </c>
       <c r="D88" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B89">
-        <v>2009</v>
+        <v>1974</v>
       </c>
       <c r="D89" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B90">
-        <v>2025</v>
+        <v>2018</v>
       </c>
       <c r="D90" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B91">
-        <v>1974</v>
+        <v>2000</v>
       </c>
       <c r="D91" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B92">
-        <v>2018</v>
+        <v>1973</v>
       </c>
       <c r="D92" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B93">
-        <v>2000</v>
+        <v>2011</v>
       </c>
       <c r="D93" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B94">
-        <v>1973</v>
+        <v>2000</v>
       </c>
       <c r="D94" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B95">
-        <v>2011</v>
+        <v>1975</v>
       </c>
       <c r="D95" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B96">
-        <v>2000</v>
+        <v>1991</v>
       </c>
       <c r="D96" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B97">
-        <v>1975</v>
+        <v>2023</v>
       </c>
       <c r="D97" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B98">
-        <v>1991</v>
+        <v>1963</v>
       </c>
       <c r="D98" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B99">
-        <v>2023</v>
+        <v>2019</v>
       </c>
       <c r="D99" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B100">
-        <v>1963</v>
+        <v>1975</v>
       </c>
       <c r="D100" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B101">
-        <v>2019</v>
+        <v>1989</v>
       </c>
       <c r="D101" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B102">
-        <v>1975</v>
+        <v>1963</v>
       </c>
       <c r="D102" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B103">
-        <v>1989</v>
+        <v>1996</v>
       </c>
       <c r="D103" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B104">
-        <v>1963</v>
+        <v>2025</v>
       </c>
       <c r="D104" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B105">
-        <v>1996</v>
+        <v>1983</v>
       </c>
       <c r="D105" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B106">
-        <v>2025</v>
+        <v>2009</v>
       </c>
       <c r="D106" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B107">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="D107" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B108">
-        <v>2009</v>
+        <v>1993</v>
       </c>
       <c r="D108" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B109">
-        <v>1982</v>
+        <v>1984</v>
       </c>
       <c r="D109" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B110">
-        <v>1993</v>
+        <v>1971</v>
       </c>
       <c r="D110" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B111">
-        <v>1984</v>
+        <v>2023</v>
       </c>
       <c r="D111" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B112">
-        <v>1971</v>
+        <v>2004</v>
       </c>
       <c r="D112" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B113">
-        <v>2023</v>
+        <v>1970</v>
       </c>
       <c r="D113" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B114">
-        <v>2004</v>
+        <v>1960</v>
       </c>
       <c r="D114" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B115">
-        <v>1970</v>
+        <v>2000</v>
       </c>
       <c r="D115" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B116">
-        <v>1960</v>
+        <v>2017</v>
       </c>
       <c r="D116" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B117">
-        <v>2000</v>
+        <v>2024</v>
       </c>
       <c r="D117" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B118">
-        <v>2017</v>
+        <v>1978</v>
       </c>
       <c r="D118" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B119">
-        <v>2024</v>
+        <v>2006</v>
       </c>
       <c r="D119" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B120">
-        <v>1978</v>
+        <v>1999</v>
       </c>
       <c r="D120" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B121">
-        <v>2006</v>
+        <v>1998</v>
       </c>
       <c r="D121" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B122">
-        <v>1999</v>
+        <v>1959</v>
       </c>
       <c r="D122" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B123">
-        <v>1998</v>
+        <v>2016</v>
       </c>
       <c r="D123" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B124">
-        <v>1959</v>
+        <v>2013</v>
       </c>
       <c r="D124" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B125">
-        <v>2016</v>
+        <v>2005</v>
       </c>
       <c r="D125" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B126">
-        <v>2013</v>
+        <v>2000</v>
       </c>
       <c r="D126" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B127">
-        <v>2005</v>
+        <v>1965</v>
       </c>
       <c r="D127" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B128">
-        <v>2000</v>
+        <v>2018</v>
       </c>
       <c r="D128" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B129">
-        <v>1965</v>
+        <v>1991</v>
       </c>
       <c r="D129" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B130">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="D130" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B131">
-        <v>1991</v>
+        <v>2025</v>
       </c>
       <c r="D131" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B132">
-        <v>2019</v>
+        <v>2014</v>
       </c>
       <c r="D132" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B133">
-        <v>2025</v>
+        <v>2014</v>
       </c>
       <c r="D133" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B134">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="D134" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B135">
-        <v>2014</v>
+        <v>2019</v>
       </c>
       <c r="D135" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B136">
-        <v>2013</v>
+        <v>1998</v>
       </c>
       <c r="D136" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B137">
-        <v>2019</v>
+        <v>2015</v>
       </c>
       <c r="D137" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B138">
-        <v>1998</v>
+        <v>2012</v>
       </c>
       <c r="D138" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B139">
-        <v>2015</v>
+        <v>2012</v>
       </c>
       <c r="D139" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B140">
-        <v>2012</v>
+        <v>2014</v>
       </c>
       <c r="D140" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B141">
-        <v>2012</v>
+        <v>2008</v>
       </c>
       <c r="D141" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B142">
-        <v>2014</v>
+        <v>1993</v>
       </c>
       <c r="D142" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B143">
-        <v>2008</v>
+        <v>1988</v>
       </c>
       <c r="D143" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B144">
-        <v>1993</v>
+        <v>2025</v>
       </c>
       <c r="D144" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B145">
-        <v>1988</v>
+        <v>1973</v>
       </c>
       <c r="D145" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B146">
-        <v>2025</v>
+        <v>1948</v>
       </c>
       <c r="D146" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B147">
-        <v>1973</v>
+        <v>1958</v>
       </c>
       <c r="D147" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B148">
-        <v>1948</v>
+        <v>2007</v>
       </c>
       <c r="D148" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B149">
-        <v>1958</v>
+        <v>2007</v>
       </c>
       <c r="D149" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B150">
-        <v>2007</v>
+        <v>1983</v>
       </c>
       <c r="D150" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B151">
-        <v>2007</v>
+        <v>2019</v>
       </c>
       <c r="D151" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B152">
-        <v>1983</v>
+        <v>1998</v>
       </c>
       <c r="D152" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B153">
-        <v>2019</v>
+        <v>1983</v>
       </c>
       <c r="D153" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B154">
-        <v>1998</v>
+        <v>2023</v>
       </c>
       <c r="D154" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B155">
-        <v>1983</v>
+        <v>2023</v>
       </c>
       <c r="D155" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B156">
-        <v>2023</v>
+        <v>2019</v>
       </c>
       <c r="D156" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B157">
-        <v>2023</v>
+        <v>2007</v>
       </c>
       <c r="D157" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B158">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="D158" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B159">
-        <v>2007</v>
+        <v>2015</v>
       </c>
       <c r="D159" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B160">
-        <v>2022</v>
+        <v>1993</v>
       </c>
       <c r="D160" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B161">
-        <v>2015</v>
+        <v>2021</v>
       </c>
       <c r="D161" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B162">
-        <v>1993</v>
+        <v>2007</v>
       </c>
       <c r="D162" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B163">
-        <v>2021</v>
+        <v>1976</v>
       </c>
       <c r="D163" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B164">
-        <v>2007</v>
+        <v>1995</v>
       </c>
       <c r="D164" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B165">
-        <v>1976</v>
+        <v>2021</v>
       </c>
       <c r="D165" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B166">
-        <v>1995</v>
+        <v>2016</v>
       </c>
       <c r="D166" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B167">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D167" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B168">
-        <v>2016</v>
+        <v>2025</v>
       </c>
       <c r="D168" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B169">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="D169" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B170">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="D170" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B171">
-        <v>2023</v>
+        <v>2013</v>
       </c>
       <c r="D171" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B172">
-        <v>2022</v>
+        <v>1999</v>
       </c>
       <c r="D172" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B173">
-        <v>2013</v>
+        <v>2011</v>
       </c>
       <c r="D173" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B174">
-        <v>1999</v>
+        <v>2023</v>
       </c>
       <c r="D174" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B175">
-        <v>2011</v>
+        <v>1965</v>
       </c>
       <c r="D175" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B176">
-        <v>2023</v>
+        <v>2007</v>
       </c>
       <c r="D176" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B177">
-        <v>1965</v>
+        <v>1966</v>
       </c>
       <c r="D177" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B178">
-        <v>2007</v>
+        <v>2011</v>
       </c>
       <c r="D178" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B179">
-        <v>1966</v>
+        <v>2005</v>
       </c>
       <c r="D179" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B180">
-        <v>2011</v>
+        <v>2014</v>
       </c>
       <c r="D180" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B181">
-        <v>2005</v>
+        <v>2016</v>
       </c>
       <c r="D181" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B182">
-        <v>2014</v>
+        <v>1922</v>
       </c>
       <c r="D182" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B183">
-        <v>2016</v>
+        <v>2023</v>
       </c>
       <c r="D183" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B184">
-        <v>1922</v>
+        <v>2012</v>
       </c>
       <c r="D184" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A185" t="s">
-        <v>371</v>
+      <c r="A185">
+        <v>96</v>
       </c>
       <c r="B185">
-        <v>2023</v>
+        <v>2018</v>
       </c>
       <c r="D185" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B186">
-        <v>2012</v>
+        <v>1968</v>
       </c>
       <c r="D186" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A187">
-        <v>96</v>
+      <c r="A187" t="s">
+        <v>376</v>
       </c>
       <c r="B187">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="D187" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B188">
-        <v>1968</v>
+        <v>2023</v>
       </c>
       <c r="D188" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B189">
-        <v>2017</v>
+        <v>1977</v>
       </c>
       <c r="D189" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B190">
-        <v>2023</v>
+        <v>2016</v>
       </c>
       <c r="D190" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B191">
-        <v>1977</v>
+        <v>1951</v>
       </c>
       <c r="D191" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B192">
-        <v>2016</v>
+        <v>2024</v>
       </c>
       <c r="D192" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B193">
-        <v>1951</v>
+        <v>2012</v>
       </c>
       <c r="D193" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="194" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B194">
-        <v>2024</v>
+        <v>2004</v>
       </c>
       <c r="D194" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="195" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B195">
-        <v>2012</v>
+        <v>2004</v>
       </c>
       <c r="D195" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="196" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B196">
-        <v>2004</v>
+        <v>1971</v>
       </c>
       <c r="D196" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B197">
-        <v>2004</v>
+        <v>2023</v>
       </c>
       <c r="D197" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="198" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B198">
-        <v>1971</v>
+        <v>2019</v>
       </c>
       <c r="D198" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B199">
-        <v>2023</v>
+        <v>2016</v>
       </c>
       <c r="D199" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="200" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B200">
         <v>2019</v>
       </c>
       <c r="D200" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="201" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B201">
-        <v>2016</v>
+        <v>1992</v>
       </c>
       <c r="D201" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B202">
-        <v>2019</v>
+        <v>1973</v>
       </c>
       <c r="D202" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="203" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B203">
-        <v>1992</v>
+        <v>2018</v>
       </c>
       <c r="D203" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="204" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B204">
-        <v>1973</v>
+        <v>1991</v>
       </c>
       <c r="D204" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="205" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B205">
-        <v>2018</v>
+        <v>1987</v>
       </c>
       <c r="D205" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="206" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B206">
-        <v>1991</v>
+        <v>2004</v>
       </c>
       <c r="D206" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B207">
-        <v>1987</v>
+        <v>2007</v>
       </c>
       <c r="D207" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="B208">
-        <v>2004</v>
+        <v>2006</v>
       </c>
       <c r="D208" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B209">
-        <v>2007</v>
+        <v>2015</v>
       </c>
       <c r="D209" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="210" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B210">
-        <v>2006</v>
+        <v>2016</v>
       </c>
       <c r="D210" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="211" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B211">
-        <v>2015</v>
+        <v>1985</v>
       </c>
       <c r="D211" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="212" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B212">
-        <v>2016</v>
+        <v>2022</v>
       </c>
       <c r="D212" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="213" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B213">
-        <v>1985</v>
+        <v>2007</v>
       </c>
       <c r="D213" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="214" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B214">
-        <v>2022</v>
+        <v>1981</v>
       </c>
       <c r="D214" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="215" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B215">
         <v>2007</v>
       </c>
       <c r="D215" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="216" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B216">
-        <v>1981</v>
+        <v>1980</v>
       </c>
       <c r="D216" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B217">
-        <v>2007</v>
+        <v>1925</v>
       </c>
       <c r="D217" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="218" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B218">
-        <v>1980</v>
+        <v>2010</v>
       </c>
       <c r="D218" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="219" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B219">
-        <v>1925</v>
+        <v>1988</v>
       </c>
       <c r="D219" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="220" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="B220">
-        <v>2010</v>
+        <v>2004</v>
       </c>
       <c r="D220" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="221" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B221">
-        <v>1988</v>
+        <v>1975</v>
       </c>
       <c r="D221" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="222" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B222">
-        <v>2004</v>
+        <v>1990</v>
       </c>
       <c r="D222" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="223" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B223">
-        <v>1975</v>
+        <v>2019</v>
       </c>
       <c r="D223" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="224" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B224">
-        <v>1990</v>
+        <v>1995</v>
       </c>
       <c r="D224" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="225" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B225">
-        <v>2019</v>
+        <v>2016</v>
       </c>
       <c r="D225" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="226" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B226">
-        <v>1995</v>
+        <v>2011</v>
       </c>
       <c r="D226" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="227" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="B227">
-        <v>2016</v>
+        <v>1976</v>
       </c>
       <c r="D227" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="228" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B228">
-        <v>2011</v>
+        <v>2000</v>
       </c>
       <c r="D228" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="229" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="B229">
-        <v>1976</v>
+        <v>2019</v>
       </c>
       <c r="D229" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="230" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B230">
-        <v>2000</v>
+        <v>2012</v>
       </c>
       <c r="D230" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="231" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B231">
-        <v>2019</v>
+        <v>2015</v>
       </c>
       <c r="D231" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="232" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="B232">
-        <v>2012</v>
+        <v>2001</v>
       </c>
       <c r="D232" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="233" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="B233">
-        <v>2015</v>
+        <v>2011</v>
       </c>
       <c r="D233" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="234" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B234">
-        <v>2001</v>
+        <v>1969</v>
       </c>
       <c r="D234" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="235" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="B235">
-        <v>2011</v>
+        <v>2021</v>
       </c>
       <c r="D235" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="236" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="B236">
-        <v>1969</v>
+        <v>2024</v>
       </c>
       <c r="D236" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="237" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A237" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="B237">
-        <v>2021</v>
+        <v>2018</v>
       </c>
       <c r="D237" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="238" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B238">
-        <v>2024</v>
+        <v>1956</v>
       </c>
       <c r="D238" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="239" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B239">
-        <v>2018</v>
+        <v>2001</v>
       </c>
       <c r="D239" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="240" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B240">
-        <v>1956</v>
+        <v>2023</v>
       </c>
       <c r="D240" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="241" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B241">
-        <v>2001</v>
+        <v>2006</v>
       </c>
       <c r="D241" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="242" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="B242">
-        <v>2023</v>
+        <v>1954</v>
       </c>
       <c r="D242" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="243" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="B243">
-        <v>2006</v>
+        <v>2016</v>
       </c>
       <c r="D243" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="B244">
-        <v>1954</v>
+        <v>2021</v>
       </c>
       <c r="D244" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="245" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="B245">
-        <v>2016</v>
+        <v>2021</v>
       </c>
       <c r="D245" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="246" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="B246">
-        <v>2021</v>
+        <v>1997</v>
       </c>
       <c r="D246" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="247" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="B247">
-        <v>2021</v>
+        <v>2006</v>
       </c>
       <c r="D247" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="248" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="B248">
-        <v>1997</v>
+        <v>2012</v>
       </c>
       <c r="D248" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="249" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="B249">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="D249" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="250" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="B250">
-        <v>2012</v>
+        <v>2015</v>
       </c>
       <c r="D250" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="251" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="B251">
-        <v>2005</v>
+        <v>2022</v>
       </c>
       <c r="D251" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="252" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A252" t="s">
-        <v>504</v>
+      <c r="A252">
+        <v>1900</v>
       </c>
       <c r="B252">
-        <v>2015</v>
+        <v>1976</v>
       </c>
       <c r="D252" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="253" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B253">
-        <v>2022</v>
+        <v>1960</v>
       </c>
       <c r="D253" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="254" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A254">
-        <v>1900</v>
+      <c r="A254" t="s">
+        <v>509</v>
       </c>
       <c r="B254">
-        <v>1976</v>
+        <v>2005</v>
       </c>
       <c r="D254" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="255" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="B255">
-        <v>1960</v>
+        <v>2022</v>
       </c>
       <c r="D255" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="256" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="B256">
-        <v>2005</v>
+        <v>1957</v>
       </c>
       <c r="D256" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="257" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="B257">
-        <v>2022</v>
+        <v>1995</v>
       </c>
       <c r="D257" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="258" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="B258">
-        <v>1957</v>
+        <v>1978</v>
       </c>
       <c r="D258" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="259" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="B259">
-        <v>1995</v>
+        <v>1988</v>
       </c>
       <c r="D259" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="260" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="B260">
-        <v>1978</v>
+        <v>1997</v>
       </c>
       <c r="D260" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="261" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="B261">
-        <v>1988</v>
+        <v>1957</v>
       </c>
       <c r="D261" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="262" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="B262">
-        <v>1997</v>
+        <v>1957</v>
       </c>
       <c r="D262" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="263" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="B263">
-        <v>1957</v>
+        <v>1928</v>
       </c>
       <c r="D263" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
     </row>
     <row r="264" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="B264">
-        <v>1957</v>
+        <v>1990</v>
       </c>
       <c r="D264" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
     </row>
     <row r="265" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="B265">
-        <v>1928</v>
+        <v>1966</v>
       </c>
       <c r="D265" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
     <row r="266" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="B266">
-        <v>1990</v>
+        <v>1997</v>
       </c>
       <c r="D266" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
     <row r="267" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="B267">
-        <v>1966</v>
+        <v>2000</v>
       </c>
       <c r="D267" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
     </row>
     <row r="268" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="B268">
-        <v>1997</v>
+        <v>1987</v>
       </c>
       <c r="D268" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
     </row>
     <row r="269" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="B269">
-        <v>2000</v>
+        <v>1924</v>
       </c>
       <c r="D269" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="270" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="B270">
-        <v>1987</v>
+        <v>2025</v>
       </c>
       <c r="D270" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
     <row r="271" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="B271">
-        <v>1924</v>
+        <v>1994</v>
       </c>
       <c r="D271" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="272" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="B272">
-        <v>2012</v>
+        <v>1942</v>
       </c>
       <c r="D272" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="273" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="B273">
-        <v>2025</v>
+        <v>1957</v>
       </c>
       <c r="D273" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="274" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="B274">
-        <v>1994</v>
+        <v>1931</v>
       </c>
       <c r="D274" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="275" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="B275">
-        <v>1942</v>
+        <v>1957</v>
       </c>
       <c r="D275" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
     </row>
     <row r="276" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="B276">
-        <v>1957</v>
+        <v>1945</v>
       </c>
       <c r="D276" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="277" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="B277">
-        <v>1931</v>
+        <v>1997</v>
       </c>
       <c r="D277" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
     </row>
     <row r="278" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="B278">
-        <v>1957</v>
+        <v>2004</v>
       </c>
       <c r="D278" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
     <row r="279" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="B279">
-        <v>1945</v>
+        <v>1959</v>
       </c>
       <c r="D279" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="280" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A280" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="B280">
-        <v>1997</v>
+        <v>1964</v>
       </c>
       <c r="D280" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
     </row>
     <row r="281" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="B281">
-        <v>2004</v>
+        <v>2009</v>
       </c>
       <c r="D281" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
     </row>
     <row r="282" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="B282">
-        <v>1959</v>
+        <v>2020</v>
       </c>
       <c r="D282" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
     </row>
     <row r="283" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="B283">
-        <v>1964</v>
+        <v>1948</v>
       </c>
       <c r="D283" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
     </row>
     <row r="284" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="B284">
-        <v>2009</v>
+        <v>2006</v>
       </c>
       <c r="D284" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
     </row>
     <row r="285" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="B285">
-        <v>2020</v>
+        <v>1992</v>
       </c>
       <c r="D285" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
     </row>
     <row r="286" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="B286">
-        <v>1948</v>
+        <v>1999</v>
       </c>
       <c r="D286" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
     </row>
     <row r="287" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="B287">
-        <v>2006</v>
+        <v>1942</v>
       </c>
       <c r="D287" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
     <row r="288" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="B288">
-        <v>1992</v>
+        <v>2024</v>
       </c>
       <c r="D288" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="B289">
-        <v>1999</v>
+        <v>2014</v>
       </c>
       <c r="D289" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
     </row>
     <row r="290" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="B290">
-        <v>1942</v>
+        <v>2003</v>
       </c>
       <c r="D290" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
     </row>
     <row r="291" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="B291">
-        <v>2024</v>
+        <v>2009</v>
       </c>
       <c r="D291" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
     </row>
     <row r="292" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="B292">
-        <v>2014</v>
+        <v>1953</v>
       </c>
       <c r="D292" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
     </row>
     <row r="293" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="B293">
-        <v>2003</v>
+        <v>1936</v>
       </c>
       <c r="D293" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
     </row>
     <row r="294" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="B294">
-        <v>2009</v>
+        <v>1955</v>
       </c>
       <c r="D294" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
     </row>
     <row r="295" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="B295">
-        <v>1953</v>
+        <v>1952</v>
       </c>
       <c r="D295" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
     </row>
     <row r="296" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="B296">
-        <v>1936</v>
+        <v>1963</v>
       </c>
       <c r="D296" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
     </row>
     <row r="297" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="B297">
-        <v>1955</v>
+        <v>2003</v>
       </c>
       <c r="D297" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
     </row>
     <row r="298" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="B298">
-        <v>1952</v>
+        <v>1996</v>
       </c>
       <c r="D298" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
     </row>
     <row r="299" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="B299">
-        <v>1963</v>
+        <v>2021</v>
       </c>
       <c r="D299" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
     </row>
     <row r="300" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="B300">
-        <v>2003</v>
+        <v>1957</v>
       </c>
       <c r="D300" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
     </row>
     <row r="301" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="B301">
-        <v>1996</v>
+        <v>2014</v>
       </c>
       <c r="D301" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
     <row r="302" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="B302">
-        <v>2021</v>
+        <v>1981</v>
       </c>
       <c r="D302" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
     </row>
     <row r="303" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="B303">
-        <v>1957</v>
+        <v>1960</v>
       </c>
       <c r="D303" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
     </row>
     <row r="304" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="B304">
-        <v>2014</v>
+        <v>2017</v>
       </c>
       <c r="D304" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
     </row>
     <row r="305" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="B305">
-        <v>1981</v>
+        <v>2008</v>
       </c>
       <c r="D305" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
     </row>
     <row r="306" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="B306">
-        <v>1960</v>
+        <v>2001</v>
       </c>
       <c r="D306" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
     </row>
     <row r="307" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="B307">
-        <v>2017</v>
+        <v>1937</v>
       </c>
       <c r="D307" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
     </row>
     <row r="308" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A308" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="B308">
-        <v>2008</v>
+        <v>1996</v>
       </c>
       <c r="D308" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
     </row>
     <row r="309" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A309" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="B309">
-        <v>2001</v>
+        <v>1994</v>
       </c>
       <c r="D309" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
     </row>
     <row r="310" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="B310">
-        <v>1937</v>
+        <v>1964</v>
       </c>
       <c r="D310" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
     </row>
     <row r="311" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="B311">
-        <v>1996</v>
+        <v>1974</v>
       </c>
       <c r="D311" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
     </row>
     <row r="312" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="B312">
-        <v>1994</v>
+        <v>1950</v>
       </c>
       <c r="D312" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
     </row>
     <row r="313" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="B313">
-        <v>1964</v>
+        <v>1962</v>
       </c>
       <c r="D313" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
     </row>
     <row r="314" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="B314">
-        <v>1974</v>
+        <v>1997</v>
       </c>
       <c r="D314" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
     </row>
     <row r="315" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="B315">
-        <v>1950</v>
+        <v>1972</v>
       </c>
       <c r="D315" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
     </row>
     <row r="316" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="B316">
-        <v>1962</v>
+        <v>1957</v>
       </c>
       <c r="D316" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
     </row>
     <row r="317" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="B317">
-        <v>1997</v>
+        <v>2007</v>
       </c>
       <c r="D317" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
     </row>
     <row r="318" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="B318">
-        <v>1972</v>
+        <v>1921</v>
       </c>
       <c r="D318" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
     </row>
     <row r="319" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="B319">
-        <v>1957</v>
+        <v>1997</v>
       </c>
       <c r="D319" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
     </row>
     <row r="320" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="B320">
-        <v>2007</v>
+        <v>1959</v>
       </c>
       <c r="D320" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
     </row>
     <row r="321" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="B321">
-        <v>1921</v>
+        <v>1950</v>
       </c>
       <c r="D321" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
     </row>
     <row r="322" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="B322">
-        <v>1997</v>
+        <v>2017</v>
       </c>
       <c r="D322" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
     </row>
     <row r="323" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="B323">
-        <v>1959</v>
+        <v>1950</v>
       </c>
       <c r="D323" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
     </row>
     <row r="324" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="B324">
-        <v>1950</v>
+        <v>2004</v>
       </c>
       <c r="D324" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
     </row>
     <row r="325" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="B325">
-        <v>2017</v>
+        <v>1926</v>
       </c>
       <c r="D325" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
     </row>
     <row r="326" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="B326">
-        <v>1950</v>
+        <v>1962</v>
       </c>
       <c r="D326" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
     </row>
     <row r="327" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="B327">
-        <v>2004</v>
+        <v>1943</v>
       </c>
       <c r="D327" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
     </row>
     <row r="328" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="B328">
-        <v>1926</v>
+        <v>1988</v>
       </c>
       <c r="D328" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
     </row>
     <row r="329" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A329" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="B329">
-        <v>1962</v>
+        <v>2016</v>
       </c>
       <c r="D329" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
     </row>
     <row r="330" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A330" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="B330">
-        <v>1943</v>
+        <v>2010</v>
       </c>
       <c r="D330" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
     </row>
     <row r="331" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A331" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="B331">
-        <v>1988</v>
+        <v>2019</v>
       </c>
       <c r="D331" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
     </row>
     <row r="332" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A332" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="B332">
-        <v>2016</v>
+        <v>2009</v>
       </c>
       <c r="D332" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
     </row>
     <row r="333" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A333" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="B333">
-        <v>2010</v>
+        <v>1940</v>
       </c>
       <c r="D333" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
     </row>
     <row r="334" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A334" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="B334">
-        <v>2019</v>
+        <v>1962</v>
       </c>
       <c r="D334" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
     </row>
     <row r="335" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A335" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="B335">
-        <v>2009</v>
+        <v>1986</v>
       </c>
       <c r="D335" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
     </row>
     <row r="336" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A336" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="B336">
-        <v>1940</v>
+        <v>1927</v>
       </c>
       <c r="D336" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
     </row>
     <row r="337" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A337" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="B337">
-        <v>1962</v>
+        <v>1974</v>
       </c>
       <c r="D337" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
     </row>
     <row r="338" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A338" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="B338">
-        <v>1986</v>
+        <v>1962</v>
       </c>
       <c r="D338" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
     </row>
     <row r="339" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A339" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="B339">
-        <v>1927</v>
+        <v>2012</v>
       </c>
       <c r="D339" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
     </row>
     <row r="340" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A340" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="B340">
-        <v>1974</v>
+        <v>1960</v>
       </c>
       <c r="D340" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
     </row>
     <row r="341" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A341" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="B341">
-        <v>1962</v>
+        <v>1999</v>
       </c>
       <c r="D341" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
     </row>
     <row r="342" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A342" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="B342">
-        <v>2012</v>
+        <v>1973</v>
       </c>
       <c r="D342" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
     </row>
     <row r="343" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A343" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="B343">
-        <v>1960</v>
+        <v>1986</v>
       </c>
       <c r="D343" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
     </row>
     <row r="344" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A344" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="B344">
-        <v>1999</v>
+        <v>2013</v>
       </c>
       <c r="D344" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
     </row>
     <row r="345" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A345" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="B345">
-        <v>1973</v>
+        <v>1995</v>
       </c>
       <c r="D345" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
     </row>
     <row r="346" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A346" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="B346">
-        <v>1986</v>
+        <v>2024</v>
       </c>
       <c r="D346" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
     </row>
     <row r="347" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A347" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="B347">
-        <v>2013</v>
+        <v>1961</v>
       </c>
       <c r="D347" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
     </row>
     <row r="348" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A348" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="B348">
-        <v>1995</v>
+        <v>1959</v>
       </c>
       <c r="D348" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
     </row>
     <row r="349" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A349" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="B349">
-        <v>2024</v>
+        <v>1960</v>
       </c>
       <c r="D349" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
     </row>
     <row r="350" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A350" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="B350">
-        <v>1961</v>
+        <v>1983</v>
       </c>
       <c r="D350" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
     </row>
     <row r="351" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A351" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="B351">
-        <v>1959</v>
+        <v>1993</v>
       </c>
       <c r="D351" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
     </row>
     <row r="352" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A352" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="B352">
-        <v>1960</v>
+        <v>2018</v>
       </c>
       <c r="D352" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
     </row>
     <row r="353" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A353" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="B353">
-        <v>1983</v>
+        <v>1943</v>
       </c>
       <c r="D353" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
     </row>
     <row r="354" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A354" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="B354">
-        <v>1993</v>
+        <v>2015</v>
       </c>
       <c r="D354" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
     </row>
     <row r="355" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A355" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="B355">
-        <v>2018</v>
+        <v>1996</v>
       </c>
       <c r="D355" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
     </row>
     <row r="356" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A356" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="B356">
-        <v>1943</v>
+        <v>1971</v>
       </c>
       <c r="D356" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
     </row>
     <row r="357" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A357" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="B357">
-        <v>2015</v>
+        <v>1925</v>
       </c>
       <c r="D357" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
     </row>
     <row r="358" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A358" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="B358">
-        <v>1996</v>
+        <v>1998</v>
       </c>
       <c r="D358" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
     </row>
     <row r="359" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A359" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="B359">
-        <v>1971</v>
+        <v>1961</v>
       </c>
       <c r="D359" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
     </row>
     <row r="360" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A360" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="B360">
-        <v>1925</v>
+        <v>1986</v>
       </c>
       <c r="D360" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
     </row>
     <row r="361" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A361" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="B361">
-        <v>1998</v>
+        <v>1962</v>
       </c>
       <c r="D361" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
     </row>
     <row r="362" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A362" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="B362">
-        <v>1961</v>
+        <v>1975</v>
       </c>
       <c r="D362" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
     </row>
     <row r="363" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A363" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="B363">
-        <v>1986</v>
+        <v>1982</v>
       </c>
       <c r="D363" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
     </row>
     <row r="364" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A364" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="B364">
-        <v>1962</v>
+        <v>1964</v>
       </c>
       <c r="D364" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
     </row>
     <row r="365" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A365" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="B365">
-        <v>1975</v>
+        <v>2001</v>
       </c>
       <c r="D365" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
     </row>
     <row r="366" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A366" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="B366">
-        <v>1982</v>
+        <v>1992</v>
       </c>
       <c r="D366" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
     </row>
     <row r="367" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A367" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="B367">
-        <v>1964</v>
+        <v>1948</v>
       </c>
       <c r="D367" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
     </row>
     <row r="368" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A368" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="B368">
-        <v>2001</v>
+        <v>2024</v>
       </c>
       <c r="D368" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
     </row>
     <row r="369" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A369" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="B369">
-        <v>1992</v>
+        <v>1959</v>
       </c>
       <c r="D369" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
     </row>
     <row r="370" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A370" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="B370">
-        <v>1948</v>
+        <v>1965</v>
       </c>
       <c r="D370" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
     </row>
     <row r="371" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A371" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="B371">
-        <v>2024</v>
+        <v>1969</v>
       </c>
       <c r="D371" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
     </row>
     <row r="372" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A372" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="B372">
-        <v>1959</v>
+        <v>2024</v>
       </c>
       <c r="D372" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
     </row>
     <row r="373" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A373" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="B373">
-        <v>1965</v>
-      </c>
-      <c r="D373" t="s">
-        <v>746</v>
+        <v>1991</v>
+      </c>
+      <c r="D373" s="2" t="s">
+        <v>748</v>
       </c>
     </row>
     <row r="374" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A374" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="B374">
-        <v>1969</v>
-      </c>
-      <c r="D374" t="s">
-        <v>748</v>
+        <v>2000</v>
+      </c>
+      <c r="D374" s="2" t="s">
+        <v>750</v>
       </c>
     </row>
     <row r="375" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A375" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="B375">
-        <v>2024</v>
-      </c>
-      <c r="D375" t="s">
-        <v>750</v>
+        <v>1990</v>
+      </c>
+      <c r="D375" s="2" t="s">
+        <v>752</v>
       </c>
     </row>
     <row r="376" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A376" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="B376">
-        <v>1991</v>
+        <v>1939</v>
       </c>
       <c r="D376" s="2" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
     </row>
     <row r="377" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A377" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="B377">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="D377" s="2" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
     </row>
     <row r="378" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A378" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="B378">
-        <v>1990</v>
+        <v>2012</v>
       </c>
       <c r="D378" s="2" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
     </row>
     <row r="379" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A379" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="B379">
-        <v>1939</v>
+        <v>1987</v>
       </c>
       <c r="D379" s="2" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
     </row>
     <row r="380" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A380" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="B380">
-        <v>1999</v>
+        <v>1961</v>
       </c>
       <c r="D380" s="2" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
     </row>
     <row r="381" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A381" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="B381">
-        <v>2012</v>
-      </c>
-      <c r="D381" s="2" t="s">
-        <v>762</v>
+        <v>2010</v>
+      </c>
+      <c r="D381" t="s">
+        <v>764</v>
       </c>
     </row>
     <row r="382" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A382" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="B382">
-        <v>1987</v>
+        <v>1974</v>
       </c>
       <c r="D382" s="2" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
     </row>
     <row r="383" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A383" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="B383">
-        <v>1961</v>
+        <v>1956</v>
       </c>
       <c r="D383" s="2" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
     </row>
     <row r="384" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A384" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="B384">
-        <v>2010</v>
-      </c>
-      <c r="D384" t="s">
-        <v>768</v>
+        <v>2022</v>
+      </c>
+      <c r="D384" s="2" t="s">
+        <v>770</v>
       </c>
     </row>
     <row r="385" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A385" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="B385">
-        <v>1974</v>
-      </c>
-      <c r="D385" s="2" t="s">
-        <v>770</v>
+        <v>2026</v>
+      </c>
+      <c r="D385" t="s">
+        <v>772</v>
       </c>
     </row>
     <row r="386" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A386" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="B386">
-        <v>1956</v>
-      </c>
-      <c r="D386" s="2" t="s">
-        <v>772</v>
+        <v>1928</v>
+      </c>
+      <c r="D386" t="s">
+        <v>774</v>
       </c>
     </row>
     <row r="387" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A387" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="B387">
-        <v>2022</v>
-      </c>
-      <c r="D387" s="2" t="s">
-        <v>774</v>
+        <v>1988</v>
+      </c>
+      <c r="D387" t="s">
+        <v>776</v>
       </c>
     </row>
     <row r="388" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A388" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="B388">
-        <v>2026</v>
+        <v>1993</v>
       </c>
       <c r="D388" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
     </row>
     <row r="389" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A389" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="B389">
-        <v>1928</v>
+        <v>1985</v>
       </c>
       <c r="D389" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
     </row>
     <row r="390" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A390" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="B390">
-        <v>1988</v>
+        <v>1999</v>
       </c>
       <c r="D390" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
     </row>
     <row r="391" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A391" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="B391">
-        <v>1993</v>
+        <v>1957</v>
       </c>
       <c r="D391" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
     </row>
     <row r="392" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A392" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="B392">
-        <v>1985</v>
+        <v>2001</v>
       </c>
       <c r="D392" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
     </row>
     <row r="393" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A393" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="B393">
-        <v>1999</v>
+        <v>1961</v>
       </c>
       <c r="D393" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
     </row>
     <row r="394" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A394" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="B394">
-        <v>1957</v>
+        <v>2008</v>
       </c>
       <c r="D394" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
     </row>
     <row r="395" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A395" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="B395">
-        <v>2001</v>
+        <v>2014</v>
       </c>
       <c r="D395" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
     </row>
     <row r="396" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A396" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="B396">
-        <v>1961</v>
+        <v>1932</v>
       </c>
       <c r="D396" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
     </row>
     <row r="397" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A397" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="B397">
-        <v>2008</v>
+        <v>2004</v>
       </c>
       <c r="D397" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
     </row>
     <row r="398" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A398" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="B398">
-        <v>2014</v>
+        <v>2007</v>
       </c>
       <c r="D398" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
     </row>
     <row r="399" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A399" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="B399">
-        <v>1932</v>
+        <v>1923</v>
       </c>
       <c r="D399" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
     </row>
     <row r="400" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A400" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="B400">
-        <v>2004</v>
+        <v>1971</v>
       </c>
       <c r="D400" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
     </row>
     <row r="401" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A401" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="B401">
-        <v>2007</v>
+        <v>1972</v>
       </c>
       <c r="D401" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
     </row>
     <row r="402" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A402" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="B402">
-        <v>1923</v>
+        <v>1988</v>
       </c>
       <c r="D402" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
     </row>
     <row r="403" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A403" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="B403">
-        <v>1971</v>
+        <v>1988</v>
       </c>
       <c r="D403" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
     </row>
     <row r="404" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A404" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="B404">
-        <v>1972</v>
+        <v>1995</v>
       </c>
       <c r="D404" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
     </row>
     <row r="405" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A405" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="B405">
-        <v>1988</v>
+        <v>1947</v>
       </c>
       <c r="D405" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
     </row>
     <row r="406" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A406" t="s">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="B406">
-        <v>1988</v>
+        <v>1946</v>
       </c>
       <c r="D406" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
     </row>
     <row r="407" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A407" t="s">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="B407">
-        <v>1995</v>
+        <v>1973</v>
       </c>
       <c r="D407" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
     </row>
     <row r="408" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A408" t="s">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="B408">
-        <v>1947</v>
+        <v>1972</v>
       </c>
       <c r="D408" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
     </row>
     <row r="409" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A409" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="B409">
-        <v>1946</v>
+        <v>1932</v>
       </c>
       <c r="D409" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
     </row>
     <row r="410" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A410" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="B410">
-        <v>1973</v>
+        <v>1953</v>
       </c>
       <c r="D410" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
     </row>
     <row r="411" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A411" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="B411">
-        <v>1972</v>
+        <v>2004</v>
       </c>
       <c r="D411" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
     </row>
     <row r="412" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A412" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="B412">
-        <v>1932</v>
+        <v>1961</v>
       </c>
       <c r="D412" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
     </row>
     <row r="413" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A413" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="B413">
-        <v>1953</v>
+        <v>1991</v>
       </c>
       <c r="D413" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
     </row>
     <row r="414" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A414" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="B414">
-        <v>2004</v>
+        <v>2009</v>
       </c>
       <c r="D414" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
     </row>
     <row r="415" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A415" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="B415">
-        <v>1961</v>
+        <v>2013</v>
       </c>
       <c r="D415" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
     </row>
     <row r="416" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A416" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="B416">
-        <v>1991</v>
+        <v>1986</v>
       </c>
       <c r="D416" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
     </row>
     <row r="417" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A417" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="B417">
-        <v>2009</v>
+        <v>2021</v>
       </c>
       <c r="D417" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
     </row>
     <row r="418" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A418" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="B418">
-        <v>2013</v>
+        <v>1958</v>
       </c>
       <c r="D418" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
     </row>
     <row r="419" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A419" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="B419">
-        <v>1986</v>
+        <v>1987</v>
       </c>
       <c r="D419" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
     </row>
     <row r="420" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A420" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="B420">
-        <v>2021</v>
+        <v>2006</v>
       </c>
       <c r="D420" t="s">
-        <v>840</v>
+        <v>842</v>
       </c>
     </row>
     <row r="421" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A421" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="B421">
-        <v>1958</v>
+        <v>1985</v>
       </c>
       <c r="D421" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
     </row>
     <row r="422" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A422" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="B422">
-        <v>1987</v>
+        <v>1961</v>
       </c>
       <c r="D422" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
     </row>
     <row r="423" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A423" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="B423">
-        <v>2006</v>
+        <v>1978</v>
       </c>
       <c r="D423" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
     </row>
     <row r="424" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A424" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="B424">
-        <v>1985</v>
+        <v>2011</v>
       </c>
       <c r="D424" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
     </row>
     <row r="425" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A425" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="B425">
-        <v>1961</v>
+        <v>2016</v>
       </c>
       <c r="D425" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
     </row>
     <row r="426" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A426" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="B426">
-        <v>1978</v>
+        <v>1995</v>
       </c>
       <c r="D426" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
     </row>
     <row r="427" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A427" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="B427">
-        <v>2011</v>
+        <v>1928</v>
       </c>
       <c r="D427" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
     </row>
     <row r="428" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A428" t="s">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="B428">
-        <v>2016</v>
+        <v>2022</v>
       </c>
       <c r="D428" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
     </row>
     <row r="429" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A429" t="s">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="B429">
-        <v>1995</v>
+        <v>2017</v>
       </c>
       <c r="D429" t="s">
-        <v>858</v>
+        <v>860</v>
       </c>
     </row>
     <row r="430" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A430" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="B430">
-        <v>1928</v>
+        <v>1980</v>
       </c>
       <c r="D430" t="s">
-        <v>860</v>
+        <v>862</v>
       </c>
     </row>
     <row r="431" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A431" t="s">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="B431">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="D431" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
     </row>
     <row r="432" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A432" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="B432">
-        <v>2017</v>
+        <v>1948</v>
       </c>
       <c r="D432" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
     </row>
     <row r="433" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A433" t="s">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="B433">
-        <v>1980</v>
+        <v>2011</v>
       </c>
       <c r="D433" t="s">
-        <v>866</v>
+        <v>868</v>
       </c>
     </row>
     <row r="434" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A434" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="B434">
-        <v>2024</v>
+        <v>1952</v>
       </c>
       <c r="D434" t="s">
-        <v>868</v>
+        <v>870</v>
       </c>
     </row>
     <row r="435" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A435" t="s">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="B435">
-        <v>1948</v>
+        <v>2025</v>
       </c>
       <c r="D435" t="s">
-        <v>870</v>
+        <v>872</v>
       </c>
     </row>
     <row r="436" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A436" t="s">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="B436">
-        <v>2011</v>
+        <v>1950</v>
       </c>
       <c r="D436" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
     </row>
     <row r="437" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A437" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="B437">
-        <v>1952</v>
+        <v>1966</v>
       </c>
       <c r="D437" t="s">
-        <v>874</v>
+        <v>876</v>
       </c>
     </row>
     <row r="438" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A438" t="s">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="B438">
-        <v>2025</v>
+        <v>1964</v>
       </c>
       <c r="D438" t="s">
-        <v>876</v>
+        <v>878</v>
       </c>
     </row>
     <row r="439" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A439" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="B439">
-        <v>1950</v>
+        <v>1946</v>
       </c>
       <c r="D439" t="s">
-        <v>878</v>
+        <v>880</v>
       </c>
     </row>
     <row r="440" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A440" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="B440">
-        <v>1966</v>
+        <v>2018</v>
       </c>
       <c r="D440" t="s">
-        <v>880</v>
+        <v>882</v>
       </c>
     </row>
     <row r="441" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A441" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="B441">
-        <v>1964</v>
+        <v>1960</v>
       </c>
       <c r="D441" t="s">
-        <v>882</v>
+        <v>884</v>
       </c>
     </row>
     <row r="442" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A442" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="B442">
-        <v>1946</v>
+        <v>2001</v>
       </c>
       <c r="D442" t="s">
-        <v>884</v>
+        <v>886</v>
       </c>
     </row>
     <row r="443" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A443" t="s">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="B443">
-        <v>2018</v>
+        <v>1966</v>
       </c>
       <c r="D443" t="s">
-        <v>886</v>
+        <v>888</v>
       </c>
     </row>
     <row r="444" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A444" t="s">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="B444">
-        <v>1960</v>
+        <v>1986</v>
       </c>
       <c r="D444" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
     </row>
     <row r="445" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A445" t="s">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="B445">
-        <v>2001</v>
+        <v>1966</v>
       </c>
       <c r="D445" t="s">
-        <v>890</v>
+        <v>892</v>
       </c>
     </row>
     <row r="446" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A446" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="B446">
-        <v>1966</v>
+        <v>2001</v>
       </c>
       <c r="D446" t="s">
-        <v>892</v>
+        <v>894</v>
       </c>
     </row>
     <row r="447" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A447" t="s">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="B447">
-        <v>1986</v>
+        <v>1999</v>
       </c>
       <c r="D447" t="s">
-        <v>894</v>
+        <v>896</v>
       </c>
     </row>
     <row r="448" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A448" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="B448">
-        <v>1966</v>
+        <v>1997</v>
       </c>
       <c r="D448" t="s">
-        <v>896</v>
+        <v>898</v>
       </c>
     </row>
     <row r="449" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A449" t="s">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="B449">
-        <v>2001</v>
+        <v>1998</v>
       </c>
       <c r="D449" t="s">
-        <v>898</v>
+        <v>900</v>
       </c>
     </row>
     <row r="450" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A450" t="s">
-        <v>899</v>
+        <v>901</v>
       </c>
       <c r="B450">
-        <v>1999</v>
+        <v>2017</v>
       </c>
       <c r="D450" t="s">
-        <v>900</v>
+        <v>902</v>
       </c>
     </row>
     <row r="451" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A451" t="s">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="B451">
-        <v>1997</v>
+        <v>1946</v>
       </c>
       <c r="D451" t="s">
-        <v>902</v>
+        <v>904</v>
       </c>
     </row>
     <row r="452" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A452" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="B452">
-        <v>1998</v>
+        <v>2005</v>
       </c>
       <c r="D452" t="s">
-        <v>904</v>
+        <v>906</v>
       </c>
     </row>
     <row r="453" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A453" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="B453">
-        <v>2017</v>
+        <v>1958</v>
       </c>
       <c r="D453" t="s">
-        <v>906</v>
+        <v>908</v>
       </c>
     </row>
     <row r="454" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A454" t="s">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="B454">
-        <v>1946</v>
+        <v>1968</v>
       </c>
       <c r="D454" t="s">
-        <v>908</v>
+        <v>910</v>
       </c>
     </row>
     <row r="455" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A455" t="s">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="B455">
-        <v>2005</v>
+        <v>2021</v>
       </c>
       <c r="D455" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
     </row>
     <row r="456" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A456" t="s">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="B456">
-        <v>1958</v>
+        <v>2024</v>
       </c>
       <c r="D456" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
     </row>
     <row r="457" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A457" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="B457">
-        <v>1968</v>
+        <v>1955</v>
       </c>
       <c r="D457" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
     </row>
     <row r="458" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A458" t="s">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="B458">
-        <v>2021</v>
+        <v>1989</v>
       </c>
       <c r="D458" t="s">
-        <v>916</v>
+        <v>918</v>
       </c>
     </row>
     <row r="459" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A459" t="s">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="B459">
-        <v>2024</v>
+        <v>2000</v>
       </c>
       <c r="D459" t="s">
-        <v>918</v>
+        <v>920</v>
       </c>
     </row>
     <row r="460" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A460" t="s">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="B460">
-        <v>1955</v>
+        <v>1928</v>
       </c>
       <c r="D460" t="s">
-        <v>920</v>
+        <v>922</v>
       </c>
     </row>
     <row r="461" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A461" t="s">
-        <v>921</v>
+        <v>923</v>
       </c>
       <c r="B461">
-        <v>1989</v>
+        <v>2002</v>
       </c>
       <c r="D461" t="s">
-        <v>922</v>
+        <v>924</v>
       </c>
     </row>
     <row r="462" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A462" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
       <c r="B462">
-        <v>2000</v>
+        <v>1965</v>
       </c>
       <c r="D462" t="s">
-        <v>924</v>
+        <v>926</v>
       </c>
     </row>
     <row r="463" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A463" t="s">
-        <v>925</v>
+        <v>927</v>
       </c>
       <c r="B463">
-        <v>1928</v>
+        <v>2010</v>
       </c>
       <c r="D463" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
     </row>
     <row r="464" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A464" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="B464">
-        <v>2002</v>
+        <v>2016</v>
       </c>
       <c r="D464" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
     </row>
     <row r="465" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A465" t="s">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="B465">
-        <v>1965</v>
+        <v>1920</v>
       </c>
       <c r="D465" t="s">
-        <v>930</v>
+        <v>932</v>
       </c>
     </row>
     <row r="466" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A466" t="s">
-        <v>931</v>
+        <v>933</v>
       </c>
       <c r="B466">
-        <v>2010</v>
+        <v>1992</v>
       </c>
       <c r="D466" t="s">
-        <v>932</v>
+        <v>934</v>
       </c>
     </row>
     <row r="467" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A467" t="s">
-        <v>933</v>
+        <v>935</v>
       </c>
       <c r="B467">
-        <v>2016</v>
+        <v>1996</v>
       </c>
       <c r="D467" t="s">
-        <v>934</v>
+        <v>936</v>
       </c>
     </row>
     <row r="468" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A468" t="s">
-        <v>935</v>
+        <v>937</v>
       </c>
       <c r="B468">
-        <v>1920</v>
+        <v>1954</v>
       </c>
       <c r="D468" t="s">
-        <v>936</v>
+        <v>938</v>
       </c>
     </row>
     <row r="469" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A469" t="s">
-        <v>937</v>
+        <v>939</v>
       </c>
       <c r="B469">
-        <v>1992</v>
+        <v>2019</v>
       </c>
       <c r="D469" t="s">
-        <v>938</v>
+        <v>940</v>
       </c>
     </row>
     <row r="470" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A470" t="s">
-        <v>939</v>
+        <v>941</v>
       </c>
       <c r="B470">
-        <v>1996</v>
+        <v>1962</v>
       </c>
       <c r="D470" t="s">
-        <v>940</v>
+        <v>942</v>
       </c>
     </row>
     <row r="471" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A471" t="s">
-        <v>941</v>
+        <v>943</v>
       </c>
       <c r="B471">
-        <v>1954</v>
+        <v>2017</v>
       </c>
       <c r="D471" t="s">
-        <v>942</v>
+        <v>944</v>
       </c>
     </row>
     <row r="472" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A472" t="s">
-        <v>943</v>
+        <v>945</v>
       </c>
       <c r="B472">
-        <v>2019</v>
+        <v>1967</v>
       </c>
       <c r="D472" t="s">
-        <v>944</v>
+        <v>946</v>
       </c>
     </row>
     <row r="473" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A473" t="s">
-        <v>945</v>
+        <v>947</v>
       </c>
       <c r="B473">
-        <v>1962</v>
+        <v>1999</v>
       </c>
       <c r="D473" t="s">
-        <v>946</v>
+        <v>948</v>
       </c>
     </row>
     <row r="474" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A474" t="s">
-        <v>947</v>
+        <v>949</v>
       </c>
       <c r="B474">
-        <v>2017</v>
+        <v>1979</v>
       </c>
       <c r="D474" t="s">
-        <v>948</v>
+        <v>950</v>
       </c>
     </row>
     <row r="475" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A475" t="s">
-        <v>949</v>
+        <v>951</v>
       </c>
       <c r="B475">
-        <v>1967</v>
+        <v>1928</v>
       </c>
       <c r="D475" t="s">
-        <v>950</v>
+        <v>952</v>
       </c>
     </row>
     <row r="476" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A476" t="s">
-        <v>951</v>
+        <v>953</v>
       </c>
       <c r="B476">
-        <v>1999</v>
+        <v>1981</v>
       </c>
       <c r="D476" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
     </row>
     <row r="477" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A477" t="s">
-        <v>953</v>
+        <v>955</v>
       </c>
       <c r="B477">
-        <v>1979</v>
+        <v>1924</v>
       </c>
       <c r="D477" t="s">
-        <v>954</v>
+        <v>956</v>
       </c>
     </row>
     <row r="478" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A478" t="s">
-        <v>955</v>
+        <v>957</v>
       </c>
       <c r="B478">
-        <v>1928</v>
+        <v>2018</v>
       </c>
       <c r="D478" t="s">
-        <v>956</v>
+        <v>958</v>
       </c>
     </row>
     <row r="479" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A479" t="s">
-        <v>957</v>
+        <v>959</v>
       </c>
       <c r="B479">
-        <v>1981</v>
+        <v>1975</v>
       </c>
       <c r="D479" t="s">
-        <v>958</v>
+        <v>960</v>
       </c>
     </row>
     <row r="480" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A480" t="s">
-        <v>959</v>
+        <v>961</v>
       </c>
       <c r="B480">
-        <v>1924</v>
+        <v>2025</v>
       </c>
       <c r="D480" t="s">
-        <v>960</v>
+        <v>962</v>
       </c>
     </row>
     <row r="481" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A481" t="s">
-        <v>961</v>
+        <v>963</v>
       </c>
       <c r="B481">
-        <v>2018</v>
+        <v>1993</v>
       </c>
       <c r="D481" t="s">
-        <v>962</v>
+        <v>964</v>
       </c>
     </row>
     <row r="482" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A482" t="s">
-        <v>963</v>
+        <v>965</v>
       </c>
       <c r="B482">
-        <v>1975</v>
+        <v>1987</v>
       </c>
       <c r="D482" t="s">
-        <v>964</v>
+        <v>966</v>
       </c>
     </row>
     <row r="483" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A483" t="s">
-        <v>965</v>
+        <v>967</v>
       </c>
       <c r="B483">
-        <v>2025</v>
+        <v>1946</v>
       </c>
       <c r="D483" t="s">
-        <v>966</v>
+        <v>968</v>
       </c>
     </row>
     <row r="484" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A484" t="s">
-        <v>967</v>
+        <v>969</v>
       </c>
       <c r="B484">
-        <v>1993</v>
+        <v>2013</v>
       </c>
       <c r="D484" t="s">
-        <v>968</v>
+        <v>970</v>
       </c>
     </row>
     <row r="485" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A485" t="s">
-        <v>969</v>
+        <v>971</v>
       </c>
       <c r="B485">
-        <v>1987</v>
+        <v>1976</v>
       </c>
       <c r="D485" t="s">
-        <v>970</v>
+        <v>972</v>
       </c>
     </row>
     <row r="486" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A486" t="s">
-        <v>971</v>
+        <v>973</v>
       </c>
       <c r="B486">
-        <v>1946</v>
+        <v>2020</v>
       </c>
       <c r="D486" t="s">
-        <v>972</v>
+        <v>974</v>
       </c>
     </row>
     <row r="487" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A487" t="s">
-        <v>973</v>
+        <v>975</v>
       </c>
       <c r="B487">
-        <v>2013</v>
+        <v>1944</v>
       </c>
       <c r="D487" t="s">
-        <v>974</v>
+        <v>976</v>
       </c>
     </row>
     <row r="488" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A488" t="s">
-        <v>975</v>
+        <v>977</v>
       </c>
       <c r="B488">
-        <v>1976</v>
+        <v>2024</v>
       </c>
       <c r="D488" t="s">
-        <v>976</v>
+        <v>978</v>
       </c>
     </row>
     <row r="489" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A489" t="s">
-        <v>977</v>
+        <v>979</v>
       </c>
       <c r="B489">
-        <v>2020</v>
+        <v>1980</v>
       </c>
       <c r="D489" t="s">
-        <v>978</v>
+        <v>980</v>
       </c>
     </row>
     <row r="490" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A490" t="s">
-        <v>979</v>
+        <v>981</v>
       </c>
       <c r="B490">
-        <v>1944</v>
+        <v>1960</v>
       </c>
       <c r="D490" t="s">
-        <v>980</v>
+        <v>982</v>
       </c>
     </row>
     <row r="491" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A491" t="s">
-        <v>981</v>
+        <v>983</v>
       </c>
       <c r="B491">
-        <v>2024</v>
+        <v>2011</v>
       </c>
       <c r="D491" t="s">
-        <v>982</v>
+        <v>984</v>
       </c>
     </row>
     <row r="492" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A492" t="s">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="B492">
-        <v>1980</v>
+        <v>1968</v>
       </c>
       <c r="D492" t="s">
-        <v>984</v>
+        <v>986</v>
       </c>
     </row>
     <row r="493" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A493" t="s">
-        <v>985</v>
+        <v>987</v>
       </c>
       <c r="B493">
-        <v>1960</v>
+        <v>2002</v>
       </c>
       <c r="D493" t="s">
-        <v>986</v>
+        <v>988</v>
       </c>
     </row>
     <row r="494" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A494" t="s">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="B494">
-        <v>2011</v>
+        <v>2016</v>
       </c>
       <c r="D494" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
     </row>
     <row r="495" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A495" t="s">
-        <v>989</v>
+        <v>991</v>
       </c>
       <c r="B495">
-        <v>1968</v>
+        <v>2010</v>
       </c>
       <c r="D495" t="s">
-        <v>990</v>
+        <v>992</v>
       </c>
     </row>
     <row r="496" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A496" t="s">
-        <v>991</v>
+        <v>993</v>
       </c>
       <c r="B496">
-        <v>2002</v>
+        <v>1984</v>
       </c>
       <c r="D496" t="s">
-        <v>992</v>
+        <v>994</v>
       </c>
     </row>
     <row r="497" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A497" t="s">
-        <v>993</v>
+        <v>995</v>
       </c>
       <c r="B497">
-        <v>2016</v>
+        <v>1987</v>
       </c>
       <c r="D497" t="s">
-        <v>994</v>
+        <v>996</v>
       </c>
     </row>
     <row r="498" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A498" t="s">
-        <v>995</v>
+        <v>997</v>
       </c>
       <c r="B498">
-        <v>2010</v>
+        <v>1950</v>
       </c>
       <c r="D498" t="s">
-        <v>996</v>
+        <v>998</v>
       </c>
     </row>
     <row r="499" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A499" t="s">
-        <v>997</v>
+        <v>999</v>
       </c>
       <c r="B499">
-        <v>1984</v>
+        <v>1994</v>
       </c>
       <c r="D499" t="s">
-        <v>998</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="500" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A500" t="s">
-        <v>999</v>
+        <v>1001</v>
       </c>
       <c r="B500">
-        <v>1987</v>
+        <v>2021</v>
       </c>
       <c r="D500" t="s">
-        <v>1000</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="501" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A501" t="s">
-        <v>1001</v>
+        <v>1003</v>
       </c>
       <c r="B501">
-        <v>1950</v>
+        <v>2014</v>
       </c>
       <c r="D501" t="s">
-        <v>1002</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="502" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A502" t="s">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="B502">
-        <v>1994</v>
+        <v>1985</v>
       </c>
       <c r="D502" t="s">
-        <v>1004</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="503" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A503" t="s">
-        <v>1005</v>
+        <v>1007</v>
       </c>
       <c r="B503">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="D503" t="s">
-        <v>1006</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="504" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A504" t="s">
-        <v>1007</v>
+        <v>1009</v>
       </c>
       <c r="B504">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="D504" t="s">
-        <v>1008</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="505" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A505" t="s">
-        <v>1009</v>
+        <v>1011</v>
       </c>
       <c r="B505">
-        <v>1985</v>
+        <v>2009</v>
       </c>
       <c r="D505" t="s">
-        <v>1010</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="506" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A506" t="s">
-        <v>1011</v>
+        <v>1013</v>
       </c>
       <c r="B506">
-        <v>2019</v>
+        <v>2012</v>
       </c>
       <c r="D506" t="s">
-        <v>1012</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="507" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A507" t="s">
-        <v>1013</v>
+        <v>1015</v>
       </c>
       <c r="B507">
-        <v>2015</v>
+        <v>1940</v>
       </c>
       <c r="D507" t="s">
-        <v>1014</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="508" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A508" t="s">
-        <v>1015</v>
+        <v>1017</v>
       </c>
       <c r="B508">
-        <v>2009</v>
+        <v>2004</v>
       </c>
       <c r="D508" t="s">
-        <v>1016</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="509" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A509" t="s">
-        <v>1017</v>
+        <v>1019</v>
       </c>
       <c r="B509">
-        <v>2012</v>
+        <v>1964</v>
       </c>
       <c r="D509" t="s">
-        <v>1018</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="510" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A510" t="s">
-        <v>1019</v>
+        <v>1021</v>
       </c>
       <c r="B510">
-        <v>1940</v>
+        <v>2004</v>
       </c>
       <c r="D510" t="s">
-        <v>1020</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="511" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A511" t="s">
-        <v>1021</v>
+        <v>1023</v>
       </c>
       <c r="B511">
-        <v>2004</v>
+        <v>2024</v>
       </c>
       <c r="D511" t="s">
-        <v>1022</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="512" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A512" t="s">
-        <v>1023</v>
+        <v>1025</v>
       </c>
       <c r="B512">
-        <v>1964</v>
+        <v>1972</v>
       </c>
       <c r="D512" t="s">
-        <v>1024</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="513" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A513" t="s">
-        <v>1025</v>
+        <v>1027</v>
       </c>
       <c r="B513">
-        <v>2004</v>
+        <v>1992</v>
       </c>
       <c r="D513" t="s">
-        <v>1026</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="514" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A514" t="s">
-        <v>1027</v>
+        <v>1029</v>
       </c>
       <c r="B514">
-        <v>2024</v>
+        <v>2009</v>
       </c>
       <c r="D514" t="s">
-        <v>1028</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="515" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A515" t="s">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="B515">
-        <v>1972</v>
+        <v>1984</v>
       </c>
       <c r="D515" t="s">
-        <v>1030</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="516" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A516" t="s">
-        <v>1031</v>
+        <v>511</v>
       </c>
       <c r="B516">
-        <v>1992</v>
+        <v>1980</v>
       </c>
       <c r="D516" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="517" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A517" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="B517">
-        <v>2009</v>
+        <v>2003</v>
       </c>
       <c r="D517" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="518" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A518" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="B518">
-        <v>1984</v>
+        <v>2008</v>
       </c>
       <c r="D518" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="519" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A519" t="s">
-        <v>513</v>
+        <v>1038</v>
       </c>
       <c r="B519">
-        <v>1980</v>
+        <v>2003</v>
       </c>
       <c r="D519" t="s">
-        <v>1037</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="520" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A520" t="s">
-        <v>1038</v>
+        <v>1040</v>
       </c>
       <c r="B520">
-        <v>2003</v>
+        <v>1998</v>
       </c>
       <c r="D520" t="s">
-        <v>1039</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="521" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A521" t="s">
-        <v>1040</v>
+        <v>1042</v>
       </c>
       <c r="B521">
-        <v>2008</v>
+        <v>2012</v>
       </c>
       <c r="D521" t="s">
-        <v>1041</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="522" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A522" t="s">
-        <v>1042</v>
+        <v>1044</v>
       </c>
       <c r="B522">
-        <v>2003</v>
+        <v>1985</v>
       </c>
       <c r="D522" t="s">
-        <v>1043</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="523" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A523" t="s">
-        <v>1044</v>
+        <v>1046</v>
       </c>
       <c r="B523">
-        <v>1998</v>
+        <v>1928</v>
       </c>
       <c r="D523" t="s">
-        <v>1045</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="524" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A524" t="s">
-        <v>1046</v>
+        <v>1048</v>
       </c>
       <c r="B524">
-        <v>2012</v>
-      </c>
-      <c r="D524" t="s">
-        <v>1047</v>
+        <v>1969</v>
+      </c>
+      <c r="D524" s="2" t="s">
+        <v>1049</v>
       </c>
     </row>
     <row r="525" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A525" t="s">
-        <v>1048</v>
+        <v>1050</v>
       </c>
       <c r="B525">
-        <v>1985</v>
+        <v>1982</v>
       </c>
       <c r="D525" t="s">
-        <v>1049</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="526" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A526" t="s">
-        <v>1050</v>
+        <v>1052</v>
       </c>
       <c r="B526">
-        <v>1928</v>
+        <v>1948</v>
       </c>
       <c r="D526" t="s">
-        <v>1051</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="527" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A527" t="s">
-        <v>1052</v>
+        <v>1054</v>
       </c>
       <c r="B527">
-        <v>1969</v>
-      </c>
-      <c r="D527" s="2" t="s">
-        <v>1053</v>
+        <v>1968</v>
+      </c>
+      <c r="D527" t="s">
+        <v>1055</v>
       </c>
     </row>
     <row r="528" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A528" t="s">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="B528">
-        <v>1982</v>
+        <v>1971</v>
       </c>
       <c r="D528" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="529" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A529" t="s">
-        <v>1056</v>
+        <v>1058</v>
       </c>
       <c r="B529">
-        <v>1948</v>
+        <v>2025</v>
       </c>
       <c r="D529" t="s">
-        <v>1057</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="530" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A530" t="s">
-        <v>1058</v>
+        <v>1060</v>
       </c>
       <c r="B530">
-        <v>1968</v>
+        <v>2004</v>
       </c>
       <c r="D530" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="531" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A531" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="B531">
-        <v>1971</v>
+        <v>2025</v>
       </c>
       <c r="D531" t="s">
-        <v>1061</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="532" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A532" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="B532">
-        <v>2025</v>
+        <v>1992</v>
       </c>
       <c r="D532" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="533" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A533" t="s">
-        <v>1064</v>
+        <v>1066</v>
       </c>
       <c r="B533">
-        <v>2004</v>
+        <v>1990</v>
       </c>
       <c r="D533" t="s">
-        <v>1065</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="534" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A534" t="s">
-        <v>1066</v>
+        <v>1068</v>
       </c>
       <c r="B534">
-        <v>2025</v>
+        <v>1949</v>
       </c>
       <c r="D534" t="s">
-        <v>1067</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="535" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A535" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="B535">
-        <v>1992</v>
+        <v>2023</v>
       </c>
       <c r="D535" t="s">
-        <v>1069</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="536" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A536" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="B536">
-        <v>1990</v>
+        <v>1964</v>
       </c>
       <c r="D536" t="s">
-        <v>1071</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="537" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A537" t="s">
-        <v>1072</v>
+        <v>1074</v>
       </c>
       <c r="B537">
-        <v>1949</v>
+        <v>1986</v>
       </c>
       <c r="D537" t="s">
-        <v>1073</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="538" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A538" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="B538">
-        <v>2023</v>
+        <v>1977</v>
       </c>
       <c r="D538" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="539" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A539" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="B539">
-        <v>1964</v>
+        <v>1972</v>
       </c>
       <c r="D539" t="s">
-        <v>1077</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="540" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A540" t="s">
-        <v>1078</v>
+        <v>1080</v>
       </c>
       <c r="B540">
-        <v>1986</v>
+        <v>2000</v>
       </c>
       <c r="D540" t="s">
-        <v>1079</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="541" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A541" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="B541">
-        <v>1977</v>
+        <v>1994</v>
       </c>
       <c r="D541" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="542" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A542" t="s">
-        <v>1082</v>
+        <v>1084</v>
       </c>
       <c r="B542">
-        <v>1972</v>
+        <v>1990</v>
       </c>
       <c r="D542" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="543" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A543" t="s">
-        <v>1084</v>
+        <v>1086</v>
       </c>
       <c r="B543">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="D543" t="s">
-        <v>1085</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="544" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A544" t="s">
-        <v>1086</v>
+        <v>1088</v>
       </c>
       <c r="B544">
-        <v>1994</v>
+        <v>2011</v>
       </c>
       <c r="D544" t="s">
-        <v>1087</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="545" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A545" t="s">
-        <v>1088</v>
+        <v>1090</v>
       </c>
       <c r="B545">
-        <v>1990</v>
+        <v>2004</v>
       </c>
       <c r="D545" t="s">
-        <v>1089</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="546" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A546" t="s">
-        <v>1090</v>
+        <v>1092</v>
       </c>
       <c r="B546">
-        <v>1999</v>
+        <v>1987</v>
       </c>
       <c r="D546" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="547" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A547" t="s">
-        <v>1092</v>
+        <v>1094</v>
       </c>
       <c r="B547">
-        <v>2011</v>
+        <v>2024</v>
       </c>
       <c r="D547" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="548" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A548" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="B548">
-        <v>2004</v>
-      </c>
-      <c r="D548" t="s">
-        <v>1095</v>
+        <v>1984</v>
+      </c>
+      <c r="D548" s="2" t="s">
+        <v>1097</v>
       </c>
     </row>
     <row r="549" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A549" t="s">
-        <v>1096</v>
+        <v>1098</v>
       </c>
       <c r="B549">
-        <v>1987</v>
-      </c>
-      <c r="D549" t="s">
-        <v>1097</v>
+        <v>2018</v>
+      </c>
+      <c r="D549" s="2" t="s">
+        <v>1099</v>
       </c>
     </row>
     <row r="550" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A550" t="s">
-        <v>1098</v>
+        <v>1100</v>
       </c>
       <c r="B550">
         <v>2024</v>
       </c>
-      <c r="D550" t="s">
-        <v>1099</v>
+      <c r="C550">
+        <v>1028769</v>
+      </c>
+      <c r="D550" s="2" t="s">
+        <v>1101</v>
       </c>
     </row>
     <row r="551" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A551" t="s">
-        <v>1100</v>
+        <v>1102</v>
       </c>
       <c r="B551">
-        <v>1984</v>
+        <v>2023</v>
+      </c>
+      <c r="C551">
+        <v>957863</v>
       </c>
       <c r="D551" s="2" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="552" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A552" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
       <c r="B552">
-        <v>2011</v>
+        <v>1964</v>
+      </c>
+      <c r="C552">
+        <v>27862</v>
       </c>
       <c r="D552" s="2" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="553" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A553" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="B553">
-        <v>1974</v>
-      </c>
-      <c r="D553" t="s">
-        <v>1105</v>
+        <v>1965</v>
+      </c>
+      <c r="C553">
+        <v>149465</v>
+      </c>
+      <c r="D553" s="2" t="s">
+        <v>1107</v>
       </c>
     </row>
     <row r="554" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A554" t="s">
-        <v>1106</v>
+        <v>1108</v>
       </c>
       <c r="B554">
-        <v>2018</v>
+        <v>2024</v>
+      </c>
+      <c r="C554">
+        <v>1243479</v>
       </c>
       <c r="D554" s="2" t="s">
-        <v>1107</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="555" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A555" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="B555">
-        <v>2024</v>
+        <v>1984</v>
       </c>
       <c r="C555">
-        <v>1028769</v>
+        <v>81</v>
       </c>
       <c r="D555" s="2" t="s">
-        <v>1109</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="556" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A556" t="s">
-        <v>1110</v>
+        <v>1112</v>
       </c>
       <c r="B556">
-        <v>2023</v>
+        <v>2008</v>
       </c>
       <c r="C556">
-        <v>957863</v>
+        <v>111188</v>
       </c>
       <c r="D556" s="2" t="s">
-        <v>1111</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="557" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A557" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="B557">
-        <v>1964</v>
+        <v>1975</v>
       </c>
       <c r="C557">
-        <v>27862</v>
+        <v>511</v>
       </c>
       <c r="D557" s="2" t="s">
-        <v>1113</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="558" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A558" t="s">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="B558">
-        <v>1965</v>
+        <v>1992</v>
       </c>
       <c r="C558">
-        <v>149465</v>
+        <v>66362</v>
       </c>
       <c r="D558" s="2" t="s">
-        <v>1115</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="559" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A559" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="B559">
-        <v>2024</v>
+        <v>1989</v>
       </c>
       <c r="C559">
-        <v>1243479</v>
-      </c>
-      <c r="D559" s="2" t="s">
-        <v>1117</v>
+        <v>237957</v>
+      </c>
+      <c r="D559" t="s">
+        <v>1119</v>
       </c>
     </row>
     <row r="560" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A560" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="B560">
-        <v>1984</v>
+        <v>2004</v>
       </c>
       <c r="C560">
-        <v>81</v>
+        <v>9470</v>
       </c>
       <c r="D560" s="2" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="561" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A561" t="s">
-        <v>1120</v>
+        <v>1122</v>
       </c>
       <c r="B561">
-        <v>2008</v>
+        <v>1987</v>
       </c>
       <c r="C561">
-        <v>111188</v>
-      </c>
-      <c r="D561" s="2" t="s">
-        <v>1121</v>
+        <v>275366</v>
+      </c>
+      <c r="D561" t="s">
+        <v>1123</v>
       </c>
     </row>
     <row r="562" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A562" t="s">
-        <v>1122</v>
+        <v>1124</v>
       </c>
       <c r="B562">
-        <v>1975</v>
+        <v>1969</v>
       </c>
       <c r="C562">
-        <v>511</v>
-      </c>
-      <c r="D562" s="2" t="s">
-        <v>1123</v>
+        <v>78117</v>
+      </c>
+      <c r="D562" t="s">
+        <v>1125</v>
       </c>
     </row>
     <row r="563" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A563" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="B563">
-        <v>1992</v>
+        <v>2016</v>
       </c>
       <c r="C563">
-        <v>66362</v>
+        <v>383367</v>
       </c>
       <c r="D563" s="2" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="564" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A564" t="s">
-        <v>1126</v>
+        <v>1128</v>
       </c>
       <c r="B564">
-        <v>1989</v>
+        <v>2026</v>
       </c>
       <c r="C564">
-        <v>237957</v>
-      </c>
-      <c r="D564" t="s">
-        <v>1127</v>
+        <v>1431068</v>
+      </c>
+      <c r="D564" s="2" t="s">
+        <v>1129</v>
       </c>
     </row>
     <row r="565" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A565" t="s">
-        <v>1128</v>
+        <v>1130</v>
       </c>
       <c r="B565">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="C565">
-        <v>9470</v>
-      </c>
-      <c r="D565" s="2" t="s">
-        <v>1129</v>
+        <v>14926</v>
+      </c>
+      <c r="D565" t="s">
+        <v>1131</v>
       </c>
     </row>
     <row r="566" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A566" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
       <c r="B566">
-        <v>1987</v>
+        <v>1993</v>
       </c>
       <c r="C566">
-        <v>275366</v>
+        <v>9702</v>
       </c>
       <c r="D566" t="s">
-        <v>1131</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="567" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A567" t="s">
-        <v>1132</v>
+        <v>1134</v>
       </c>
       <c r="B567">
-        <v>1969</v>
+        <v>2026</v>
       </c>
       <c r="C567">
-        <v>78117</v>
-      </c>
-      <c r="D567" t="s">
-        <v>1133</v>
+        <v>1155818</v>
+      </c>
+      <c r="D567" s="2" t="s">
+        <v>1135</v>
       </c>
     </row>
     <row r="568" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A568" t="s">
-        <v>1134</v>
+        <v>1136</v>
       </c>
       <c r="B568">
-        <v>2016</v>
+        <v>2001</v>
       </c>
       <c r="C568">
-        <v>383367</v>
+        <v>37280</v>
       </c>
       <c r="D568" s="2" t="s">
-        <v>1135</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="569" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A569" t="s">
-        <v>1136</v>
+        <v>1138</v>
       </c>
       <c r="B569">
-        <v>2026</v>
+        <v>1975</v>
       </c>
       <c r="C569">
-        <v>1431068</v>
+        <v>83651</v>
       </c>
       <c r="D569" s="2" t="s">
-        <v>1137</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="570" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A570" t="s">
-        <v>1138</v>
+        <v>1140</v>
       </c>
       <c r="B570">
-        <v>2003</v>
+        <v>2017</v>
       </c>
       <c r="C570">
-        <v>14926</v>
-      </c>
-      <c r="D570" t="s">
-        <v>1139</v>
+        <v>339877</v>
+      </c>
+      <c r="D570" s="2" t="s">
+        <v>1141</v>
+      </c>
+    </row>
+    <row r="571" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A571" t="s">
+        <v>1142</v>
+      </c>
+      <c r="B571">
+        <v>1999</v>
+      </c>
+      <c r="C571">
+        <v>17078</v>
+      </c>
+      <c r="D571" s="2" t="s">
+        <v>1143</v>
+      </c>
+    </row>
+    <row r="572" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A572" t="s">
+        <v>1144</v>
+      </c>
+      <c r="B572">
+        <v>2026</v>
+      </c>
+      <c r="C572">
+        <v>1368337</v>
+      </c>
+      <c r="D572" t="s">
+        <v>1145</v>
+      </c>
+    </row>
+    <row r="573" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A573" t="s">
+        <v>1146</v>
+      </c>
+      <c r="B573">
+        <v>2015</v>
+      </c>
+      <c r="C573">
+        <v>348892</v>
+      </c>
+      <c r="D573" s="2" t="s">
+        <v>1147</v>
+      </c>
+    </row>
+    <row r="574" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A574" t="s">
+        <v>43</v>
+      </c>
+      <c r="B574">
+        <v>1982</v>
+      </c>
+      <c r="D574" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="D376" r:id="rId1" xr:uid="{E845355F-2512-4FEA-8B22-7261DB0AEF68}"/>
-    <hyperlink ref="D377" r:id="rId2" xr:uid="{0BABEE8A-8F45-47E1-A57B-B9CD3AD6300A}"/>
-    <hyperlink ref="D378" r:id="rId3" xr:uid="{8C35DED6-55FB-4D0F-BC67-11555078D011}"/>
-    <hyperlink ref="D379" r:id="rId4" xr:uid="{6236F1CA-23A5-4253-A673-1D1AC489343F}"/>
-    <hyperlink ref="D380" r:id="rId5" xr:uid="{C86998E7-D40B-4095-B2C1-413E1E5982F6}"/>
-    <hyperlink ref="D381" r:id="rId6" xr:uid="{F938ED9A-6735-4A64-8558-B5829A874738}"/>
-    <hyperlink ref="D382" r:id="rId7" xr:uid="{4D495342-2395-4F7B-89F5-9893D9EC3A96}"/>
-    <hyperlink ref="D383" r:id="rId8" xr:uid="{0AF84B25-9FD2-451C-8DA3-4E0F17F12AC9}"/>
-    <hyperlink ref="D385" r:id="rId9" xr:uid="{776C9CEA-7871-4374-A43D-DFF17F3051B4}"/>
-    <hyperlink ref="D386" r:id="rId10" xr:uid="{454DB360-E518-429F-A862-554126EEE6A1}"/>
-    <hyperlink ref="D387" r:id="rId11" xr:uid="{368B7CDE-8355-4739-83B5-7B0ABB90B5B2}"/>
-    <hyperlink ref="D527" r:id="rId12" xr:uid="{A4301CC4-9A54-49C3-8360-6DD0E8DCE230}"/>
-    <hyperlink ref="D551" r:id="rId13" xr:uid="{16145F1C-6214-4749-8D8A-FDD477E08B28}"/>
-    <hyperlink ref="D552" r:id="rId14" xr:uid="{024C5F8B-8F81-420D-868D-5D8E76ABB1AE}"/>
-    <hyperlink ref="D554" r:id="rId15" xr:uid="{E70978B9-40E5-446D-987D-E57F6DB2DA9E}"/>
-    <hyperlink ref="D555" r:id="rId16" xr:uid="{A294FD8A-3D0D-4D2E-87BD-F10BABD32315}"/>
-    <hyperlink ref="D556" r:id="rId17" xr:uid="{F28C7628-2B4D-4FCE-8952-BFDD7C7F06CE}"/>
-    <hyperlink ref="D557" r:id="rId18" xr:uid="{193BDB09-EFD2-4937-8E49-91638F1A9791}"/>
-    <hyperlink ref="D558" r:id="rId19" xr:uid="{5C1D518D-E5D1-4FFF-A746-E8BAD67AEA01}"/>
-    <hyperlink ref="D559" r:id="rId20" xr:uid="{5D8CCB0C-6663-42F7-A44C-954C049BD83E}"/>
-    <hyperlink ref="D560" r:id="rId21" xr:uid="{4375E633-718C-4FF4-B551-501BADD47EFD}"/>
-    <hyperlink ref="D561" r:id="rId22" xr:uid="{946D4369-9E99-4934-BD8D-833824E29DAC}"/>
-    <hyperlink ref="D562" r:id="rId23" xr:uid="{B0DAA382-D612-4C52-92CC-60F966246E5A}"/>
-    <hyperlink ref="D563" r:id="rId24" xr:uid="{F1F98DA8-9B33-4768-A093-3D35DBF11836}"/>
-    <hyperlink ref="D565" r:id="rId25" xr:uid="{183D0A7D-6CE1-42F6-B6E1-4F9B48010CF2}"/>
-    <hyperlink ref="D568" r:id="rId26" xr:uid="{82067776-FBC4-42EE-8A1C-DC7F82929CE6}"/>
-    <hyperlink ref="D569" r:id="rId27" xr:uid="{749A53FD-F4AA-4550-B4EE-F7566180BD0B}"/>
+    <hyperlink ref="D373" r:id="rId1" xr:uid="{E845355F-2512-4FEA-8B22-7261DB0AEF68}"/>
+    <hyperlink ref="D374" r:id="rId2" xr:uid="{0BABEE8A-8F45-47E1-A57B-B9CD3AD6300A}"/>
+    <hyperlink ref="D375" r:id="rId3" xr:uid="{8C35DED6-55FB-4D0F-BC67-11555078D011}"/>
+    <hyperlink ref="D376" r:id="rId4" xr:uid="{6236F1CA-23A5-4253-A673-1D1AC489343F}"/>
+    <hyperlink ref="D377" r:id="rId5" xr:uid="{C86998E7-D40B-4095-B2C1-413E1E5982F6}"/>
+    <hyperlink ref="D378" r:id="rId6" xr:uid="{F938ED9A-6735-4A64-8558-B5829A874738}"/>
+    <hyperlink ref="D379" r:id="rId7" xr:uid="{4D495342-2395-4F7B-89F5-9893D9EC3A96}"/>
+    <hyperlink ref="D380" r:id="rId8" xr:uid="{0AF84B25-9FD2-451C-8DA3-4E0F17F12AC9}"/>
+    <hyperlink ref="D382" r:id="rId9" xr:uid="{776C9CEA-7871-4374-A43D-DFF17F3051B4}"/>
+    <hyperlink ref="D383" r:id="rId10" xr:uid="{454DB360-E518-429F-A862-554126EEE6A1}"/>
+    <hyperlink ref="D384" r:id="rId11" xr:uid="{368B7CDE-8355-4739-83B5-7B0ABB90B5B2}"/>
+    <hyperlink ref="D524" r:id="rId12" xr:uid="{A4301CC4-9A54-49C3-8360-6DD0E8DCE230}"/>
+    <hyperlink ref="D548" r:id="rId13" xr:uid="{16145F1C-6214-4749-8D8A-FDD477E08B28}"/>
+    <hyperlink ref="D549" r:id="rId14" xr:uid="{E70978B9-40E5-446D-987D-E57F6DB2DA9E}"/>
+    <hyperlink ref="D550" r:id="rId15" xr:uid="{A294FD8A-3D0D-4D2E-87BD-F10BABD32315}"/>
+    <hyperlink ref="D551" r:id="rId16" xr:uid="{F28C7628-2B4D-4FCE-8952-BFDD7C7F06CE}"/>
+    <hyperlink ref="D552" r:id="rId17" xr:uid="{193BDB09-EFD2-4937-8E49-91638F1A9791}"/>
+    <hyperlink ref="D553" r:id="rId18" xr:uid="{5C1D518D-E5D1-4FFF-A746-E8BAD67AEA01}"/>
+    <hyperlink ref="D554" r:id="rId19" xr:uid="{5D8CCB0C-6663-42F7-A44C-954C049BD83E}"/>
+    <hyperlink ref="D555" r:id="rId20" xr:uid="{4375E633-718C-4FF4-B551-501BADD47EFD}"/>
+    <hyperlink ref="D556" r:id="rId21" xr:uid="{946D4369-9E99-4934-BD8D-833824E29DAC}"/>
+    <hyperlink ref="D557" r:id="rId22" xr:uid="{B0DAA382-D612-4C52-92CC-60F966246E5A}"/>
+    <hyperlink ref="D558" r:id="rId23" xr:uid="{F1F98DA8-9B33-4768-A093-3D35DBF11836}"/>
+    <hyperlink ref="D560" r:id="rId24" xr:uid="{183D0A7D-6CE1-42F6-B6E1-4F9B48010CF2}"/>
+    <hyperlink ref="D563" r:id="rId25" xr:uid="{82067776-FBC4-42EE-8A1C-DC7F82929CE6}"/>
+    <hyperlink ref="D564" r:id="rId26" xr:uid="{749A53FD-F4AA-4550-B4EE-F7566180BD0B}"/>
+    <hyperlink ref="D567" r:id="rId27" xr:uid="{A616256D-507A-41E6-A5BF-A9DCC1BAE21C}"/>
+    <hyperlink ref="D568" r:id="rId28" xr:uid="{DFF48DF0-787B-4537-8529-ACF78B130BEC}"/>
+    <hyperlink ref="D569" r:id="rId29" xr:uid="{A4C22B00-3DAA-4EB7-8CD5-6EB2EE9770BE}"/>
+    <hyperlink ref="D570" r:id="rId30" xr:uid="{27F4E0C5-9433-4949-9F98-19C89A574AD0}"/>
+    <hyperlink ref="D571" r:id="rId31" xr:uid="{F8FC90A4-B279-4685-8CC7-9EB2A608C18E}"/>
+    <hyperlink ref="D573" r:id="rId32" xr:uid="{8A7A993F-3BD4-440B-9D5B-F659B113CF37}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Official Whitelist.xlsx
+++ b/Official Whitelist.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bigba\aa Personal Projects\Letterboxd-List-Scraping\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66F15952-60E6-4F99-B680-DA3ACFFD371F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05F99AA6-A08B-4690-8646-0B0C30A0BEC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2080" yWindow="2080" windowWidth="14400" windowHeight="8170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1149" uniqueCount="1148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1169" uniqueCount="1168">
   <si>
     <t>Title</t>
   </si>
@@ -3469,6 +3469,66 @@
   </si>
   <si>
     <t>https://letterboxd.com/film/bajrangi-bhaijaan/</t>
+  </si>
+  <si>
+    <t>War And Peace Part Iii The Year 1812</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/war-and-peace-part-iii-the-year-1812/</t>
+  </si>
+  <si>
+    <t>It&amp;#039;s Such a Beautiful Day</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/its-such-a-beautiful-day/</t>
+  </si>
+  <si>
+    <t>The Cure</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/the-cure-1995/</t>
+  </si>
+  <si>
+    <t>Scenes From A Marriage</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/scenes-from-a-marriage/</t>
+  </si>
+  <si>
+    <t>Edvard Munch</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/edvard-munch/</t>
+  </si>
+  <si>
+    <t>A Story of Yonosuke</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/a-story-of-yonosuke/</t>
+  </si>
+  <si>
+    <t>All Of A Sudden</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/all-of-a-sudden-2026/</t>
+  </si>
+  <si>
+    <t>There Is No Evil</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/there-is-no-evil/</t>
+  </si>
+  <si>
+    <t>La Bola Negra</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/la-bola-negra/</t>
+  </si>
+  <si>
+    <t>Bethlehem Kudumba Unit</t>
+  </si>
+  <si>
+    <t>https://letterboxd.com/film/bethlehem-kudumba-unit/</t>
   </si>
 </sst>
 </file>
@@ -3820,7 +3880,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D574"/>
+  <dimension ref="A1:D584"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="46.36328125" bestFit="1" customWidth="1"/>
@@ -10216,6 +10276,146 @@
       </c>
       <c r="D574" t="s">
         <v>44</v>
+      </c>
+    </row>
+    <row r="575" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A575" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B575">
+        <v>1967</v>
+      </c>
+      <c r="C575">
+        <v>149467</v>
+      </c>
+      <c r="D575" s="2" t="s">
+        <v>1149</v>
+      </c>
+    </row>
+    <row r="576" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A576" t="s">
+        <v>1150</v>
+      </c>
+      <c r="B576">
+        <v>2012</v>
+      </c>
+      <c r="C576">
+        <v>489412</v>
+      </c>
+      <c r="D576" s="2" t="s">
+        <v>1151</v>
+      </c>
+    </row>
+    <row r="577" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A577" t="s">
+        <v>1152</v>
+      </c>
+      <c r="B577">
+        <v>1995</v>
+      </c>
+      <c r="C577">
+        <v>6715</v>
+      </c>
+      <c r="D577" s="2" t="s">
+        <v>1153</v>
+      </c>
+    </row>
+    <row r="578" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A578" t="s">
+        <v>1154</v>
+      </c>
+      <c r="B578">
+        <v>1974</v>
+      </c>
+      <c r="C578">
+        <v>133919</v>
+      </c>
+      <c r="D578" t="s">
+        <v>1155</v>
+      </c>
+    </row>
+    <row r="579" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A579" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B579">
+        <v>1974</v>
+      </c>
+      <c r="C579">
+        <v>50254</v>
+      </c>
+      <c r="D579" t="s">
+        <v>1157</v>
+      </c>
+    </row>
+    <row r="580" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A580" t="s">
+        <v>1158</v>
+      </c>
+      <c r="B580">
+        <v>2013</v>
+      </c>
+      <c r="C580">
+        <v>200145</v>
+      </c>
+      <c r="D580" s="2" t="s">
+        <v>1159</v>
+      </c>
+    </row>
+    <row r="581" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A581" t="s">
+        <v>1160</v>
+      </c>
+      <c r="B581">
+        <v>2026</v>
+      </c>
+      <c r="C581">
+        <v>1476614</v>
+      </c>
+      <c r="D581" t="s">
+        <v>1161</v>
+      </c>
+    </row>
+    <row r="582" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A582" t="s">
+        <v>1162</v>
+      </c>
+      <c r="B582">
+        <v>2020</v>
+      </c>
+      <c r="C582">
+        <v>667935</v>
+      </c>
+      <c r="D582" s="2" t="s">
+        <v>1163</v>
+      </c>
+    </row>
+    <row r="583" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A583" t="s">
+        <v>1164</v>
+      </c>
+      <c r="B583">
+        <v>2026</v>
+      </c>
+      <c r="C583">
+        <v>1422041</v>
+      </c>
+      <c r="D583" s="2" t="s">
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="584" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A584" t="s">
+        <v>1166</v>
+      </c>
+      <c r="B584">
+        <v>2026</v>
+      </c>
+      <c r="C584">
+        <v>1508168</v>
+      </c>
+      <c r="D584" t="s">
+        <v>1167</v>
       </c>
     </row>
   </sheetData>
@@ -10252,6 +10452,12 @@
     <hyperlink ref="D570" r:id="rId30" xr:uid="{27F4E0C5-9433-4949-9F98-19C89A574AD0}"/>
     <hyperlink ref="D571" r:id="rId31" xr:uid="{F8FC90A4-B279-4685-8CC7-9EB2A608C18E}"/>
     <hyperlink ref="D573" r:id="rId32" xr:uid="{8A7A993F-3BD4-440B-9D5B-F659B113CF37}"/>
+    <hyperlink ref="D575" r:id="rId33" xr:uid="{620E6518-AC03-4C2D-8B03-C4D832A34FFB}"/>
+    <hyperlink ref="D576" r:id="rId34" xr:uid="{EFE883DE-5C48-4F0C-BE6D-EB603BD7B1C2}"/>
+    <hyperlink ref="D577" r:id="rId35" xr:uid="{528CF979-E4A0-42E1-AEEE-9C1A79A48DCA}"/>
+    <hyperlink ref="D580" r:id="rId36" xr:uid="{28B0537F-268D-45E0-A8C6-5C80DC289D3F}"/>
+    <hyperlink ref="D582" r:id="rId37" xr:uid="{DA526506-8F63-4272-9038-4DC447CD9688}"/>
+    <hyperlink ref="D583" r:id="rId38" xr:uid="{DB074FD6-73BB-4903-AB26-82303258FC31}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
